--- a/defense.xlsx
+++ b/defense.xlsx
@@ -998,16 +998,16 @@
         <v>8</v>
       </c>
       <c r="M2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N2" t="n">
         <v>8</v>
       </c>
       <c r="O2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q2" t="n">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>8</v>
       </c>
       <c r="T2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="U2" t="n">
         <v>3</v>
@@ -1075,7 +1075,7 @@
         <v>20</v>
       </c>
       <c r="BB2" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="BC2" t="n">
         <v>1</v>
@@ -1110,16 +1110,16 @@
         <v>0.4</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="CD2" t="n">
         <v>0.4</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.95</v>
+        <v>1.1</v>
       </c>
       <c r="CG2" t="n">
         <v>0.4</v>
@@ -1131,7 +1131,7 @@
         <v>0.4</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.25</v>
+        <v>1.181818181818182</v>
       </c>
       <c r="CK2" t="n">
         <v>3</v>
@@ -1166,10 +1166,10 @@
         <v>108</v>
       </c>
       <c r="DK2" t="n">
-        <v>456</v>
+        <v>553</v>
       </c>
       <c r="DL2" t="n">
-        <v>4.222222222222222</v>
+        <v>5.12037037037037</v>
       </c>
     </row>
     <row r="3">
@@ -1223,28 +1223,28 @@
         <v>12</v>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R3" t="n">
         <v>12</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T3" t="n">
         <v>4</v>
@@ -1307,7 +1307,7 @@
         <v>20</v>
       </c>
       <c r="BB3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
@@ -1343,31 +1343,31 @@
         <v>3</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.35</v>
+        <v>0.75</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.35</v>
+        <v>0.95</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="CH3" t="n">
         <v>0.6</v>
       </c>
       <c r="CI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ3" t="n">
         <v>0.2</v>
-      </c>
-      <c r="CJ3" t="n">
-        <v>0.3636363636363636</v>
       </c>
       <c r="CK3" t="n">
         <v>0</v>
@@ -1406,10 +1406,10 @@
         <v>113</v>
       </c>
       <c r="DK3" t="n">
-        <v>348</v>
+        <v>556</v>
       </c>
       <c r="DL3" t="n">
-        <v>3.079646017699115</v>
+        <v>4.920353982300885</v>
       </c>
     </row>
     <row r="4">
@@ -1463,31 +1463,31 @@
         <v>23</v>
       </c>
       <c r="L4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="M4" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Q4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R4" t="n">
         <v>22</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="T4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="U4" t="n">
         <v>3</v>
@@ -1583,31 +1583,31 @@
         <v>4</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.375</v>
+        <v>0.575</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.425</v>
+        <v>0.8</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.325</v>
+        <v>0.45</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.525</v>
+        <v>0.575</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="CH4" t="n">
         <v>0.55</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.2903225806451613</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="CK4" t="n">
         <v>1.5</v>
@@ -1646,10 +1646,10 @@
         <v>221</v>
       </c>
       <c r="DK4" t="n">
-        <v>804</v>
+        <v>1109</v>
       </c>
       <c r="DL4" t="n">
-        <v>3.638009049773756</v>
+        <v>5.018099547511312</v>
       </c>
     </row>
     <row r="5">
@@ -1727,7 +1727,7 @@
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U5" t="n">
         <v>2</v>
@@ -1783,7 +1783,7 @@
         <v>18</v>
       </c>
       <c r="BB5" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BC5" t="n">
         <v>2</v>
@@ -1874,10 +1874,10 @@
         <v>69</v>
       </c>
       <c r="DK5" t="n">
-        <v>360</v>
+        <v>333</v>
       </c>
       <c r="DL5" t="n">
-        <v>5.217391304347826</v>
+        <v>4.826086956521739</v>
       </c>
     </row>
     <row r="6">
@@ -1931,25 +1931,25 @@
         <v>11</v>
       </c>
       <c r="L6" t="n">
+        <v>18</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" t="n">
+        <v>12</v>
+      </c>
+      <c r="O6" t="n">
         <v>7</v>
       </c>
-      <c r="M6" t="n">
-        <v>4</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4</v>
-      </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="Q6" t="n">
+        <v>11</v>
+      </c>
+      <c r="R6" t="n">
         <v>6</v>
-      </c>
-      <c r="R6" t="n">
-        <v>10</v>
       </c>
       <c r="S6" t="n">
         <v>7</v>
@@ -2013,7 +2013,7 @@
         <v>21</v>
       </c>
       <c r="BB6" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -2047,31 +2047,31 @@
         <v>2</v>
       </c>
       <c r="CB6" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="CE6" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="CC6" t="n">
-        <v>0.1904761904761905</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>0.1904761904761905</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>0.1904761904761905</v>
-      </c>
       <c r="CF6" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="CG6" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="CH6" t="n">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="CH6" t="n">
-        <v>0.4761904761904762</v>
       </c>
       <c r="CI6" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -2108,10 +2108,10 @@
         <v>95</v>
       </c>
       <c r="DK6" t="n">
-        <v>277</v>
+        <v>405</v>
       </c>
       <c r="DL6" t="n">
-        <v>2.915789473684211</v>
+        <v>4.263157894736842</v>
       </c>
     </row>
     <row r="7">
@@ -2165,31 +2165,31 @@
         <v>22</v>
       </c>
       <c r="L7" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="M7" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O7" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P7" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q7" t="n">
         <v>17</v>
       </c>
-      <c r="Q7" t="n">
-        <v>12</v>
-      </c>
       <c r="R7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="S7" t="n">
         <v>12</v>
       </c>
       <c r="T7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="U7" t="n">
         <v>2</v>
@@ -2247,7 +2247,7 @@
         <v>39</v>
       </c>
       <c r="BB7" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="BC7" t="n">
         <v>3</v>
@@ -2281,31 +2281,31 @@
         <v>4</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.4102564102564102</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.2051282051282051</v>
+        <v>0.4102564102564102</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.5641025641025641</v>
       </c>
       <c r="CF7" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="CG7" t="n">
         <v>0.4358974358974359</v>
       </c>
-      <c r="CG7" t="n">
-        <v>0.3076923076923077</v>
-      </c>
       <c r="CH7" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="CI7" t="n">
         <v>0.3076923076923077</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.4482758620689655</v>
+        <v>0.303030303030303</v>
       </c>
       <c r="CK7" t="n">
         <v>0.6666666666666666</v>
@@ -2342,10 +2342,10 @@
         <v>164</v>
       </c>
       <c r="DK7" t="n">
-        <v>637</v>
+        <v>738</v>
       </c>
       <c r="DL7" t="n">
-        <v>3.884146341463415</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="8">
@@ -2419,7 +2419,7 @@
         <v>14</v>
       </c>
       <c r="T8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
@@ -2471,7 +2471,7 @@
         <v>20</v>
       </c>
       <c r="BB8" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr"/>
@@ -2525,7 +2525,7 @@
         <v>0.7</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="CK8" t="inlineStr"/>
       <c r="CL8" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         <v>83</v>
       </c>
       <c r="DK8" t="n">
-        <v>415</v>
+        <v>379</v>
       </c>
       <c r="DL8" t="n">
-        <v>5</v>
+        <v>4.566265060240964</v>
       </c>
     </row>
     <row r="9">
@@ -2609,25 +2609,25 @@
         <v>8</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M9" t="n">
+        <v>11</v>
+      </c>
+      <c r="N9" t="n">
         <v>4</v>
       </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
       <c r="O9" t="n">
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -2689,7 +2689,7 @@
         <v>20</v>
       </c>
       <c r="BB9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="BC9" t="n">
         <v>2</v>
@@ -2721,31 +2721,31 @@
         <v>2</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="CC9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="CD9" t="n">
         <v>0.2</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>0.05</v>
       </c>
       <c r="CE9" t="n">
         <v>0.05</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="CI9" t="n">
         <v>0.25</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.35</v>
       </c>
       <c r="CK9" t="n">
         <v>2</v>
@@ -2780,10 +2780,10 @@
         <v>55</v>
       </c>
       <c r="DK9" t="n">
-        <v>226</v>
+        <v>290</v>
       </c>
       <c r="DL9" t="n">
-        <v>4.109090909090909</v>
+        <v>5.272727272727272</v>
       </c>
     </row>
     <row r="10">
@@ -2833,31 +2833,31 @@
         <v>14</v>
       </c>
       <c r="L10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M10" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="N10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O10" t="n">
         <v>15</v>
       </c>
       <c r="P10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S10" t="n">
         <v>19</v>
       </c>
       <c r="T10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="U10" t="n">
         <v>4</v>
@@ -2913,7 +2913,7 @@
         <v>40</v>
       </c>
       <c r="BB10" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="BC10" t="n">
         <v>2</v>
@@ -2945,31 +2945,31 @@
         <v>2</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.4</v>
+        <v>0.475</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.15</v>
+        <v>0.325</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.25</v>
+        <v>0.325</v>
       </c>
       <c r="CE10" t="n">
         <v>0.375</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.15</v>
+        <v>0.275</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.425</v>
+        <v>0.45</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.325</v>
+        <v>0.35</v>
       </c>
       <c r="CI10" t="n">
         <v>0.475</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.3428571428571429</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CK10" t="n">
         <v>2</v>
@@ -3004,10 +3004,10 @@
         <v>138</v>
       </c>
       <c r="DK10" t="n">
-        <v>641</v>
+        <v>669</v>
       </c>
       <c r="DL10" t="n">
-        <v>4.644927536231884</v>
+        <v>4.847826086956522</v>
       </c>
     </row>
     <row r="11">
@@ -3085,7 +3085,7 @@
         <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
         <v>1</v>
@@ -3141,7 +3141,7 @@
         <v>18</v>
       </c>
       <c r="BB11" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="BC11" t="n">
         <v>2</v>
@@ -3197,7 +3197,7 @@
         <v>0.2222222222222222</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.5</v>
       </c>
       <c r="CK11" t="n">
         <v>0.5</v>
@@ -3232,10 +3232,10 @@
         <v>60</v>
       </c>
       <c r="DK11" t="n">
-        <v>306</v>
+        <v>261</v>
       </c>
       <c r="DL11" t="n">
-        <v>5.1</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="12">
@@ -3289,28 +3289,28 @@
         <v>9</v>
       </c>
       <c r="L12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>6</v>
+      </c>
+      <c r="N12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O12" t="n">
+        <v>9</v>
+      </c>
+      <c r="P12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>16</v>
+      </c>
+      <c r="R12" t="n">
         <v>7</v>
       </c>
-      <c r="M12" t="n">
-        <v>5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>7</v>
-      </c>
-      <c r="O12" t="n">
-        <v>6</v>
-      </c>
-      <c r="P12" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>10</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="T12" t="n">
         <v>5</v>
@@ -3375,7 +3375,7 @@
         <v>20</v>
       </c>
       <c r="BB12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="BC12" t="n">
         <v>3</v>
@@ -3413,31 +3413,31 @@
         <v>6</v>
       </c>
       <c r="CB12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CH12" t="n">
         <v>0.35</v>
       </c>
-      <c r="CC12" t="n">
+      <c r="CI12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CJ12" t="n">
         <v>0.25</v>
-      </c>
-      <c r="CD12" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="CE12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="CF12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="CG12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="CH12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="CI12" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="CJ12" t="n">
-        <v>0.4166666666666667</v>
       </c>
       <c r="CK12" t="n">
         <v>0.6666666666666666</v>
@@ -3478,10 +3478,10 @@
         <v>90</v>
       </c>
       <c r="DK12" t="n">
-        <v>320</v>
+        <v>511</v>
       </c>
       <c r="DL12" t="n">
-        <v>3.555555555555555</v>
+        <v>5.677777777777778</v>
       </c>
     </row>
     <row r="13">
@@ -3535,31 +3535,31 @@
         <v>13</v>
       </c>
       <c r="L13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N13" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P13" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>25</v>
+      </c>
+      <c r="R13" t="n">
         <v>15</v>
       </c>
-      <c r="Q13" t="n">
-        <v>19</v>
-      </c>
-      <c r="R13" t="n">
-        <v>9</v>
-      </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T13" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="U13" t="n">
         <v>3</v>
@@ -3621,7 +3621,7 @@
         <v>38</v>
       </c>
       <c r="BB13" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BC13" t="n">
         <v>5</v>
@@ -3659,31 +3659,31 @@
         <v>8</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.3421052631578947</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.2894736842105263</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.2368421052631579</v>
       </c>
       <c r="CF13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.6578947368421053</v>
+      </c>
+      <c r="CH13" t="n">
         <v>0.3947368421052632</v>
       </c>
-      <c r="CG13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="CH13" t="n">
-        <v>0.2368421052631579</v>
-      </c>
       <c r="CI13" t="n">
-        <v>0.3421052631578947</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="CK13" t="n">
         <v>0.6</v>
@@ -3724,10 +3724,10 @@
         <v>150</v>
       </c>
       <c r="DK13" t="n">
-        <v>626</v>
+        <v>772</v>
       </c>
       <c r="DL13" t="n">
-        <v>4.173333333333333</v>
+        <v>5.146666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -3805,7 +3805,7 @@
         <v>8</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
         <v>2</v>
@@ -3863,7 +3863,7 @@
         <v>20</v>
       </c>
       <c r="BB14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="BC14" t="n">
         <v>2</v>
@@ -3921,7 +3921,7 @@
         <v>0.4</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="CK14" t="n">
         <v>1</v>
@@ -3958,10 +3958,10 @@
         <v>88</v>
       </c>
       <c r="DK14" t="n">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="DL14" t="n">
-        <v>4.863636363636363</v>
+        <v>4.761363636363637</v>
       </c>
     </row>
     <row r="15">
@@ -4015,28 +4015,28 @@
         <v>13</v>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T15" t="n">
         <v>3</v>
@@ -4095,7 +4095,7 @@
         <v>19</v>
       </c>
       <c r="BB15" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="BC15" t="n">
         <v>2</v>
@@ -4127,31 +4127,31 @@
         <v>2</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="CF15" t="n">
+        <v>0.4736842105263158</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.4210526315789473</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.5789473684210527</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="CJ15" t="n">
         <v>0.1578947368421053</v>
-      </c>
-      <c r="CG15" t="n">
-        <v>0.3157894736842105</v>
-      </c>
-      <c r="CH15" t="n">
-        <v>0.4210526315789473</v>
-      </c>
-      <c r="CI15" t="n">
-        <v>0.05263157894736842</v>
-      </c>
-      <c r="CJ15" t="n">
-        <v>0.4285714285714285</v>
       </c>
       <c r="CK15" t="n">
         <v>1.5</v>
@@ -4186,10 +4186,10 @@
         <v>82</v>
       </c>
       <c r="DK15" t="n">
-        <v>227</v>
+        <v>435</v>
       </c>
       <c r="DL15" t="n">
-        <v>2.768292682926829</v>
+        <v>5.304878048780488</v>
       </c>
     </row>
     <row r="16">
@@ -4243,31 +4243,31 @@
         <v>21</v>
       </c>
       <c r="L16" t="n">
+        <v>21</v>
+      </c>
+      <c r="M16" t="n">
+        <v>6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>28</v>
+      </c>
+      <c r="O16" t="n">
+        <v>18</v>
+      </c>
+      <c r="P16" t="n">
         <v>17</v>
       </c>
-      <c r="M16" t="n">
-        <v>7</v>
-      </c>
-      <c r="N16" t="n">
-        <v>27</v>
-      </c>
-      <c r="O16" t="n">
-        <v>11</v>
-      </c>
-      <c r="P16" t="n">
-        <v>11</v>
-      </c>
       <c r="Q16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R16" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="T16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16" t="n">
         <v>5</v>
@@ -4325,7 +4325,7 @@
         <v>39</v>
       </c>
       <c r="BB16" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BC16" t="n">
         <v>4</v>
@@ -4359,31 +4359,31 @@
         <v>5</v>
       </c>
       <c r="CB16" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0.717948717948718</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="CF16" t="n">
         <v>0.4358974358974359</v>
       </c>
-      <c r="CC16" t="n">
-        <v>0.1794871794871795</v>
-      </c>
-      <c r="CD16" t="n">
-        <v>0.6923076923076923</v>
-      </c>
-      <c r="CE16" t="n">
-        <v>0.282051282051282</v>
-      </c>
-      <c r="CF16" t="n">
-        <v>0.282051282051282</v>
-      </c>
       <c r="CG16" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.5641025641025641</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0.2592592592592592</v>
+        <v>0.2068965517241379</v>
       </c>
       <c r="CK16" t="n">
         <v>1.25</v>
@@ -4420,10 +4420,10 @@
         <v>170</v>
       </c>
       <c r="DK16" t="n">
-        <v>655</v>
+        <v>854</v>
       </c>
       <c r="DL16" t="n">
-        <v>3.852941176470588</v>
+        <v>5.023529411764706</v>
       </c>
     </row>
     <row r="17">
@@ -4497,7 +4497,7 @@
         <v>10</v>
       </c>
       <c r="T17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U17" t="n">
         <v>7</v>
@@ -4553,7 +4553,7 @@
         <v>17</v>
       </c>
       <c r="BB17" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BC17" t="n">
         <v>4</v>
@@ -4609,7 +4609,7 @@
         <v>0.5882352941176471</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CK17" t="n">
         <v>1.75</v>
@@ -4644,10 +4644,10 @@
         <v>75</v>
       </c>
       <c r="DK17" t="n">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="DL17" t="n">
-        <v>5.92</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="18">
@@ -4697,28 +4697,28 @@
         <v>12</v>
       </c>
       <c r="L18" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="N18" t="n">
+        <v>8</v>
+      </c>
+      <c r="O18" t="n">
+        <v>20</v>
+      </c>
+      <c r="P18" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q18" t="n">
         <v>9</v>
       </c>
-      <c r="O18" t="n">
-        <v>8</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
       <c r="R18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="T18" t="n">
         <v>3</v>
@@ -4779,7 +4779,7 @@
         <v>22</v>
       </c>
       <c r="BB18" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="BC18" t="n">
         <v>1</v>
@@ -4813,31 +4813,31 @@
         <v>2</v>
       </c>
       <c r="CB18" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="CC18" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="CD18" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0.3181818181818182</v>
+      </c>
+      <c r="CG18" t="n">
         <v>0.4090909090909091</v>
       </c>
-      <c r="CE18" t="n">
-        <v>0.3636363636363636</v>
-      </c>
-      <c r="CF18" t="n">
+      <c r="CH18" t="n">
+        <v>0.5909090909090909</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="CJ18" t="n">
         <v>0.1363636363636364</v>
-      </c>
-      <c r="CG18" t="n">
-        <v>0.09090909090909091</v>
-      </c>
-      <c r="CH18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="CI18" t="n">
-        <v>0.1818181818181818</v>
-      </c>
-      <c r="CJ18" t="n">
-        <v>0.2727272727272727</v>
       </c>
       <c r="CK18" t="n">
         <v>0</v>
@@ -4874,10 +4874,10 @@
         <v>109</v>
       </c>
       <c r="DK18" t="n">
-        <v>253</v>
+        <v>507</v>
       </c>
       <c r="DL18" t="n">
-        <v>2.321100917431193</v>
+        <v>4.651376146788991</v>
       </c>
     </row>
     <row r="19">
@@ -4927,31 +4927,31 @@
         <v>21</v>
       </c>
       <c r="L19" t="n">
+        <v>17</v>
+      </c>
+      <c r="M19" t="n">
+        <v>23</v>
+      </c>
+      <c r="N19" t="n">
+        <v>16</v>
+      </c>
+      <c r="O19" t="n">
+        <v>27</v>
+      </c>
+      <c r="P19" t="n">
         <v>14</v>
       </c>
-      <c r="M19" t="n">
-        <v>10</v>
-      </c>
-      <c r="N19" t="n">
+      <c r="Q19" t="n">
         <v>17</v>
       </c>
-      <c r="O19" t="n">
-        <v>15</v>
-      </c>
-      <c r="P19" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>10</v>
-      </c>
       <c r="R19" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="S19" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="T19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U19" t="n">
         <v>7</v>
@@ -5009,7 +5009,7 @@
         <v>39</v>
       </c>
       <c r="BB19" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="BC19" t="n">
         <v>5</v>
@@ -5043,31 +5043,31 @@
         <v>6</v>
       </c>
       <c r="CB19" t="n">
+        <v>0.4358974358974359</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>0.5897435897435898</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>0.4102564102564102</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="CF19" t="n">
         <v>0.358974358974359</v>
       </c>
-      <c r="CC19" t="n">
-        <v>0.2564102564102564</v>
-      </c>
-      <c r="CD19" t="n">
+      <c r="CG19" t="n">
         <v>0.4358974358974359</v>
       </c>
-      <c r="CE19" t="n">
-        <v>0.3846153846153846</v>
-      </c>
-      <c r="CF19" t="n">
-        <v>0.2564102564102564</v>
-      </c>
-      <c r="CG19" t="n">
-        <v>0.2564102564102564</v>
-      </c>
       <c r="CH19" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CI19" t="n">
-        <v>0.358974358974359</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="CJ19" t="n">
-        <v>0.3214285714285715</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="CK19" t="n">
         <v>1.4</v>
@@ -5104,10 +5104,10 @@
         <v>184</v>
       </c>
       <c r="DK19" t="n">
-        <v>697</v>
+        <v>933</v>
       </c>
       <c r="DL19" t="n">
-        <v>3.78804347826087</v>
+        <v>5.070652173913044</v>
       </c>
     </row>
     <row r="20">
@@ -5185,7 +5185,7 @@
         <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -5243,7 +5243,7 @@
         <v>18</v>
       </c>
       <c r="BB20" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="BC20" t="n">
         <v>1</v>
@@ -5301,7 +5301,7 @@
         <v>0.7222222222222222</v>
       </c>
       <c r="CJ20" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="CK20" t="n">
         <v>0</v>
@@ -5338,10 +5338,10 @@
         <v>55</v>
       </c>
       <c r="DK20" t="n">
-        <v>325</v>
+        <v>280</v>
       </c>
       <c r="DL20" t="n">
-        <v>5.909090909090909</v>
+        <v>5.090909090909091</v>
       </c>
     </row>
     <row r="21">
@@ -5395,28 +5395,28 @@
         <v>12</v>
       </c>
       <c r="L21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N21" t="n">
         <v>3</v>
       </c>
       <c r="O21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="P21" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q21" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="R21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T21" t="n">
         <v>5</v>
@@ -5475,7 +5475,7 @@
         <v>23</v>
       </c>
       <c r="BB21" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="BC21" t="n">
         <v>2</v>
@@ -5507,31 +5507,31 @@
         <v>2</v>
       </c>
       <c r="CB21" t="n">
-        <v>0.4782608695652174</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="CC21" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="CD21" t="n">
         <v>0.1304347826086956</v>
       </c>
       <c r="CE21" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.9130434782608695</v>
       </c>
       <c r="CF21" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="CG21" t="n">
-        <v>0.2608695652173913</v>
+        <v>1.217391304347826</v>
       </c>
       <c r="CH21" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="CI21" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="CJ21" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="CK21" t="n">
         <v>1.5</v>
@@ -5566,10 +5566,10 @@
         <v>117</v>
       </c>
       <c r="DK21" t="n">
-        <v>326</v>
+        <v>605</v>
       </c>
       <c r="DL21" t="n">
-        <v>2.786324786324786</v>
+        <v>5.170940170940171</v>
       </c>
     </row>
     <row r="22">
@@ -5623,31 +5623,31 @@
         <v>20</v>
       </c>
       <c r="L22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N22" t="n">
         <v>5</v>
       </c>
       <c r="O22" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="P22" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q22" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="R22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S22" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="T22" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="U22" t="n">
         <v>3</v>
@@ -5705,7 +5705,7 @@
         <v>41</v>
       </c>
       <c r="BB22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC22" t="n">
         <v>3</v>
@@ -5739,31 +5739,31 @@
         <v>4</v>
       </c>
       <c r="CB22" t="n">
-        <v>0.3902439024390244</v>
+        <v>0.4390243902439024</v>
       </c>
       <c r="CC22" t="n">
-        <v>0.1463414634146341</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="CD22" t="n">
         <v>0.1219512195121951</v>
       </c>
       <c r="CE22" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.6829268292682927</v>
       </c>
       <c r="CF22" t="n">
-        <v>0.4390243902439024</v>
+        <v>0.5609756097560976</v>
       </c>
       <c r="CG22" t="n">
-        <v>0.2682926829268293</v>
+        <v>0.8048780487804879</v>
       </c>
       <c r="CH22" t="n">
-        <v>0.2926829268292683</v>
+        <v>0.3414634146341464</v>
       </c>
       <c r="CI22" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.6585365853658537</v>
       </c>
       <c r="CJ22" t="n">
-        <v>0.3666666666666666</v>
+        <v>0.1875</v>
       </c>
       <c r="CK22" t="n">
         <v>1</v>
@@ -5800,10 +5800,10 @@
         <v>172</v>
       </c>
       <c r="DK22" t="n">
-        <v>651</v>
+        <v>885</v>
       </c>
       <c r="DL22" t="n">
-        <v>3.784883720930233</v>
+        <v>5.145348837209302</v>
       </c>
     </row>
     <row r="23">
@@ -5881,7 +5881,7 @@
         <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
@@ -5933,7 +5933,7 @@
         <v>17</v>
       </c>
       <c r="BB23" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="BC23" t="inlineStr"/>
       <c r="BD23" t="inlineStr"/>
@@ -5987,7 +5987,7 @@
         <v>0.5882352941176471</v>
       </c>
       <c r="CJ23" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.125</v>
       </c>
       <c r="CK23" t="inlineStr"/>
       <c r="CL23" t="inlineStr"/>
@@ -6018,10 +6018,10 @@
         <v>63</v>
       </c>
       <c r="DK23" t="n">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="DL23" t="n">
-        <v>5.26984126984127</v>
+        <v>5.126984126984127</v>
       </c>
     </row>
     <row r="24">
@@ -6075,28 +6075,28 @@
         <v>16</v>
       </c>
       <c r="L24" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N24" t="n">
+        <v>8</v>
+      </c>
+      <c r="O24" t="n">
+        <v>10</v>
+      </c>
+      <c r="P24" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q24" t="n">
         <v>7</v>
       </c>
-      <c r="O24" t="n">
-        <v>7</v>
-      </c>
-      <c r="P24" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>6</v>
-      </c>
       <c r="R24" t="n">
+        <v>10</v>
+      </c>
+      <c r="S24" t="n">
         <v>17</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3</v>
       </c>
       <c r="T24" t="n">
         <v>6</v>
@@ -6155,7 +6155,7 @@
         <v>22</v>
       </c>
       <c r="BB24" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="BC24" t="n">
         <v>1</v>
@@ -6187,31 +6187,31 @@
         <v>1</v>
       </c>
       <c r="CB24" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="CC24" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="CD24" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="CE24" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="CF24" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="CG24" t="n">
         <v>0.3181818181818182</v>
       </c>
-      <c r="CE24" t="n">
-        <v>0.3181818181818182</v>
-      </c>
-      <c r="CF24" t="n">
-        <v>0.1818181818181818</v>
-      </c>
-      <c r="CG24" t="n">
+      <c r="CH24" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="CI24" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="CJ24" t="n">
         <v>0.2727272727272727</v>
-      </c>
-      <c r="CH24" t="n">
-        <v>0.7727272727272727</v>
-      </c>
-      <c r="CI24" t="n">
-        <v>0.1363636363636364</v>
-      </c>
-      <c r="CJ24" t="n">
-        <v>0.6</v>
       </c>
       <c r="CK24" t="n">
         <v>1</v>
@@ -6246,10 +6246,10 @@
         <v>99</v>
       </c>
       <c r="DK24" t="n">
-        <v>322</v>
+        <v>474</v>
       </c>
       <c r="DL24" t="n">
-        <v>3.252525252525253</v>
+        <v>4.787878787878788</v>
       </c>
     </row>
     <row r="25">
@@ -6303,31 +6303,31 @@
         <v>22</v>
       </c>
       <c r="L25" t="n">
+        <v>22</v>
+      </c>
+      <c r="M25" t="n">
+        <v>14</v>
+      </c>
+      <c r="N25" t="n">
+        <v>19</v>
+      </c>
+      <c r="O25" t="n">
+        <v>18</v>
+      </c>
+      <c r="P25" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q25" t="n">
         <v>8</v>
       </c>
-      <c r="M25" t="n">
+      <c r="R25" t="n">
+        <v>28</v>
+      </c>
+      <c r="S25" t="n">
+        <v>27</v>
+      </c>
+      <c r="T25" t="n">
         <v>7</v>
-      </c>
-      <c r="N25" t="n">
-        <v>18</v>
-      </c>
-      <c r="O25" t="n">
-        <v>15</v>
-      </c>
-      <c r="P25" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>7</v>
-      </c>
-      <c r="R25" t="n">
-        <v>35</v>
-      </c>
-      <c r="S25" t="n">
-        <v>13</v>
-      </c>
-      <c r="T25" t="n">
-        <v>8</v>
       </c>
       <c r="U25" t="n">
         <v>1</v>
@@ -6383,7 +6383,7 @@
         <v>39</v>
       </c>
       <c r="BB25" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BC25" t="n">
         <v>1</v>
@@ -6415,31 +6415,31 @@
         <v>1</v>
       </c>
       <c r="CB25" t="n">
+        <v>0.5641025641025641</v>
+      </c>
+      <c r="CC25" t="n">
+        <v>0.358974358974359</v>
+      </c>
+      <c r="CD25" t="n">
+        <v>0.4871794871794872</v>
+      </c>
+      <c r="CE25" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="CF25" t="n">
+        <v>0.4358974358974359</v>
+      </c>
+      <c r="CG25" t="n">
         <v>0.2051282051282051</v>
       </c>
-      <c r="CC25" t="n">
-        <v>0.1794871794871795</v>
-      </c>
-      <c r="CD25" t="n">
-        <v>0.4615384615384616</v>
-      </c>
-      <c r="CE25" t="n">
-        <v>0.3846153846153846</v>
-      </c>
-      <c r="CF25" t="n">
-        <v>0.2307692307692308</v>
-      </c>
-      <c r="CG25" t="n">
-        <v>0.1794871794871795</v>
-      </c>
       <c r="CH25" t="n">
-        <v>0.8974358974358975</v>
+        <v>0.717948717948718</v>
       </c>
       <c r="CI25" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="CJ25" t="n">
-        <v>0.2962962962962963</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="CK25" t="n">
         <v>1</v>
@@ -6474,10 +6474,10 @@
         <v>162</v>
       </c>
       <c r="DK25" t="n">
-        <v>654</v>
+        <v>797</v>
       </c>
       <c r="DL25" t="n">
-        <v>4.037037037037037</v>
+        <v>4.919753086419753</v>
       </c>
     </row>
     <row r="26">
@@ -6551,7 +6551,7 @@
         <v>7</v>
       </c>
       <c r="T26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U26" t="n">
         <v>1</v>
@@ -6611,7 +6611,7 @@
         <v>22</v>
       </c>
       <c r="BB26" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="BC26" t="n">
         <v>2</v>
@@ -6671,7 +6671,7 @@
         <v>0.3181818181818182</v>
       </c>
       <c r="CJ26" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="CK26" t="n">
         <v>0.5</v>
@@ -6710,10 +6710,10 @@
         <v>91</v>
       </c>
       <c r="DK26" t="n">
-        <v>490</v>
+        <v>463</v>
       </c>
       <c r="DL26" t="n">
-        <v>5.384615384615385</v>
+        <v>5.087912087912088</v>
       </c>
     </row>
     <row r="27">
@@ -6763,28 +6763,28 @@
         <v>12</v>
       </c>
       <c r="L27" t="n">
+        <v>11</v>
+      </c>
+      <c r="M27" t="n">
+        <v>9</v>
+      </c>
+      <c r="N27" t="n">
+        <v>9</v>
+      </c>
+      <c r="O27" t="n">
+        <v>10</v>
+      </c>
+      <c r="P27" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q27" t="n">
         <v>5</v>
       </c>
-      <c r="M27" t="n">
-        <v>4</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2</v>
-      </c>
-      <c r="P27" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2</v>
-      </c>
       <c r="R27" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T27" t="n">
         <v>10</v>
@@ -6843,7 +6843,7 @@
         <v>18</v>
       </c>
       <c r="BB27" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="BC27" t="n">
         <v>2</v>
@@ -6875,31 +6875,31 @@
         <v>2</v>
       </c>
       <c r="CB27" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="CC27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CD27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CE27" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="CF27" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="CG27" t="n">
         <v>0.2777777777777778</v>
       </c>
-      <c r="CC27" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="CD27" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="CE27" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="CF27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="CG27" t="n">
-        <v>0.1111111111111111</v>
-      </c>
       <c r="CH27" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="CI27" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="CJ27" t="n">
-        <v>1.111111111111111</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="CK27" t="n">
         <v>0</v>
@@ -6934,10 +6934,10 @@
         <v>86</v>
       </c>
       <c r="DK27" t="n">
-        <v>241</v>
+        <v>431</v>
       </c>
       <c r="DL27" t="n">
-        <v>2.802325581395349</v>
+        <v>5.011627906976744</v>
       </c>
     </row>
     <row r="28">
@@ -6987,31 +6987,31 @@
         <v>21</v>
       </c>
       <c r="L28" t="n">
+        <v>23</v>
+      </c>
+      <c r="M28" t="n">
+        <v>23</v>
+      </c>
+      <c r="N28" t="n">
+        <v>15</v>
+      </c>
+      <c r="O28" t="n">
+        <v>18</v>
+      </c>
+      <c r="P28" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>15</v>
+      </c>
+      <c r="R28" t="n">
+        <v>22</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="n">
         <v>17</v>
-      </c>
-      <c r="M28" t="n">
-        <v>18</v>
-      </c>
-      <c r="N28" t="n">
-        <v>8</v>
-      </c>
-      <c r="O28" t="n">
-        <v>10</v>
-      </c>
-      <c r="P28" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>12</v>
-      </c>
-      <c r="R28" t="n">
-        <v>19</v>
-      </c>
-      <c r="S28" t="n">
-        <v>11</v>
-      </c>
-      <c r="T28" t="n">
-        <v>20</v>
       </c>
       <c r="U28" t="n">
         <v>1</v>
@@ -7071,7 +7071,7 @@
         <v>40</v>
       </c>
       <c r="BB28" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="BC28" t="n">
         <v>4</v>
@@ -7107,31 +7107,31 @@
         <v>6</v>
       </c>
       <c r="CB28" t="n">
-        <v>0.425</v>
+        <v>0.575</v>
       </c>
       <c r="CC28" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="CD28" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CE28" t="n">
         <v>0.45</v>
       </c>
-      <c r="CD28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="CE28" t="n">
-        <v>0.25</v>
-      </c>
       <c r="CF28" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="CG28" t="n">
-        <v>0.3</v>
+        <v>0.375</v>
       </c>
       <c r="CH28" t="n">
-        <v>0.475</v>
+        <v>0.55</v>
       </c>
       <c r="CI28" t="n">
-        <v>0.275</v>
+        <v>0.5</v>
       </c>
       <c r="CJ28" t="n">
-        <v>0.6451612903225806</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="CK28" t="n">
         <v>0.25</v>
@@ -7170,10 +7170,10 @@
         <v>177</v>
       </c>
       <c r="DK28" t="n">
-        <v>731</v>
+        <v>894</v>
       </c>
       <c r="DL28" t="n">
-        <v>4.129943502824859</v>
+        <v>5.050847457627119</v>
       </c>
     </row>
     <row r="29">
@@ -7251,7 +7251,7 @@
         <v>16</v>
       </c>
       <c r="T29" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="U29" t="n">
         <v>6</v>
@@ -7307,7 +7307,7 @@
         <v>20</v>
       </c>
       <c r="BB29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="BC29" t="n">
         <v>2</v>
@@ -7363,7 +7363,7 @@
         <v>0.8</v>
       </c>
       <c r="CJ29" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="CK29" t="n">
         <v>3</v>
@@ -7398,10 +7398,10 @@
         <v>94</v>
       </c>
       <c r="DK29" t="n">
-        <v>564</v>
+        <v>537</v>
       </c>
       <c r="DL29" t="n">
-        <v>6</v>
+        <v>5.712765957446808</v>
       </c>
     </row>
     <row r="30">
@@ -7455,28 +7455,28 @@
         <v>13</v>
       </c>
       <c r="L30" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="P30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="R30" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T30" t="n">
         <v>2</v>
@@ -7537,7 +7537,7 @@
         <v>20</v>
       </c>
       <c r="BB30" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="BC30" t="n">
         <v>1</v>
@@ -7571,31 +7571,31 @@
         <v>2</v>
       </c>
       <c r="CB30" t="n">
-        <v>0.4</v>
+        <v>0.65</v>
       </c>
       <c r="CC30" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="CD30" t="n">
-        <v>0.2</v>
+        <v>0.55</v>
       </c>
       <c r="CE30" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="CF30" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="CG30" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="CH30" t="n">
-        <v>0.55</v>
+        <v>1</v>
       </c>
       <c r="CI30" t="n">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="CJ30" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.1</v>
       </c>
       <c r="CK30" t="n">
         <v>0</v>
@@ -7632,10 +7632,10 @@
         <v>108</v>
       </c>
       <c r="DK30" t="n">
-        <v>268</v>
+        <v>531</v>
       </c>
       <c r="DL30" t="n">
-        <v>2.481481481481481</v>
+        <v>4.916666666666667</v>
       </c>
     </row>
     <row r="31">
@@ -7689,31 +7689,31 @@
         <v>23</v>
       </c>
       <c r="L31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N31" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="O31" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="P31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q31" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="R31" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="T31" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="U31" t="n">
         <v>6</v>
@@ -7771,7 +7771,7 @@
         <v>40</v>
       </c>
       <c r="BB31" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BC31" t="n">
         <v>3</v>
@@ -7805,31 +7805,31 @@
         <v>4</v>
       </c>
       <c r="CB31" t="n">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="CC31" t="n">
-        <v>0.4</v>
+        <v>0.425</v>
       </c>
       <c r="CD31" t="n">
-        <v>0.35</v>
+        <v>0.525</v>
       </c>
       <c r="CE31" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="CF31" t="n">
-        <v>0.325</v>
+        <v>0.375</v>
       </c>
       <c r="CG31" t="n">
-        <v>0.3</v>
+        <v>0.575</v>
       </c>
       <c r="CH31" t="n">
-        <v>0.575</v>
+        <v>0.8</v>
       </c>
       <c r="CI31" t="n">
-        <v>0.625</v>
+        <v>0.775</v>
       </c>
       <c r="CJ31" t="n">
-        <v>0.5185185185185185</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="CK31" t="n">
         <v>2</v>
@@ -7866,10 +7866,10 @@
         <v>202</v>
       </c>
       <c r="DK31" t="n">
-        <v>832</v>
+        <v>1068</v>
       </c>
       <c r="DL31" t="n">
-        <v>4.118811881188119</v>
+        <v>5.287128712871287</v>
       </c>
     </row>
     <row r="32">
@@ -7947,7 +7947,7 @@
         <v>16</v>
       </c>
       <c r="T32" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U32" t="n">
         <v>4</v>
@@ -8005,7 +8005,7 @@
         <v>16</v>
       </c>
       <c r="BB32" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BC32" t="n">
         <v>3</v>
@@ -8063,7 +8063,7 @@
         <v>1</v>
       </c>
       <c r="CJ32" t="n">
-        <v>0.5625</v>
+        <v>0.6</v>
       </c>
       <c r="CK32" t="n">
         <v>1.333333333333333</v>
@@ -8100,10 +8100,10 @@
         <v>102</v>
       </c>
       <c r="DK32" t="n">
-        <v>556</v>
+        <v>529</v>
       </c>
       <c r="DL32" t="n">
-        <v>5.450980392156863</v>
+        <v>5.186274509803922</v>
       </c>
     </row>
     <row r="33">
@@ -8157,28 +8157,28 @@
         <v>10</v>
       </c>
       <c r="L33" t="n">
+        <v>11</v>
+      </c>
+      <c r="M33" t="n">
+        <v>4</v>
+      </c>
+      <c r="N33" t="n">
+        <v>8</v>
+      </c>
+      <c r="O33" t="n">
         <v>7</v>
       </c>
-      <c r="M33" t="n">
-        <v>2</v>
-      </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q33" t="n">
         <v>9</v>
       </c>
-      <c r="O33" t="n">
-        <v>4</v>
-      </c>
-      <c r="P33" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>7</v>
-      </c>
       <c r="R33" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T33" t="n">
         <v>5</v>
@@ -8239,7 +8239,7 @@
         <v>23</v>
       </c>
       <c r="BB33" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BC33" t="n">
         <v>1</v>
@@ -8273,31 +8273,31 @@
         <v>2</v>
       </c>
       <c r="CB33" t="n">
+        <v>0.4782608695652174</v>
+      </c>
+      <c r="CC33" t="n">
+        <v>0.1739130434782609</v>
+      </c>
+      <c r="CD33" t="n">
+        <v>0.3478260869565217</v>
+      </c>
+      <c r="CE33" t="n">
         <v>0.3043478260869565</v>
       </c>
-      <c r="CC33" t="n">
-        <v>0.08695652173913043</v>
-      </c>
-      <c r="CD33" t="n">
+      <c r="CF33" t="n">
+        <v>0.3478260869565217</v>
+      </c>
+      <c r="CG33" t="n">
         <v>0.391304347826087</v>
       </c>
-      <c r="CE33" t="n">
-        <v>0.1739130434782609</v>
-      </c>
-      <c r="CF33" t="n">
-        <v>0.391304347826087</v>
-      </c>
-      <c r="CG33" t="n">
-        <v>0.3043478260869565</v>
-      </c>
       <c r="CH33" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="CI33" t="n">
-        <v>0.1739130434782609</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="CJ33" t="n">
-        <v>0.3125</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="CK33" t="n">
         <v>1</v>
@@ -8334,10 +8334,10 @@
         <v>78</v>
       </c>
       <c r="DK33" t="n">
-        <v>260</v>
+        <v>415</v>
       </c>
       <c r="DL33" t="n">
-        <v>3.333333333333333</v>
+        <v>5.32051282051282</v>
       </c>
     </row>
     <row r="34">
@@ -8391,31 +8391,31 @@
         <v>18</v>
       </c>
       <c r="L34" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M34" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N34" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P34" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q34" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R34" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="T34" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="U34" t="n">
         <v>5</v>
@@ -8473,7 +8473,7 @@
         <v>39</v>
       </c>
       <c r="BB34" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BC34" t="n">
         <v>4</v>
@@ -8507,31 +8507,31 @@
         <v>6</v>
       </c>
       <c r="CB34" t="n">
-        <v>0.4358974358974359</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="CC34" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="CD34" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="CE34" t="n">
+        <v>0.2564102564102564</v>
+      </c>
+      <c r="CF34" t="n">
+        <v>0.6410256410256411</v>
+      </c>
+      <c r="CG34" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="CH34" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="CI34" t="n">
+        <v>0.8205128205128205</v>
+      </c>
+      <c r="CJ34" t="n">
         <v>0.3333333333333333</v>
-      </c>
-      <c r="CD34" t="n">
-        <v>0.4871794871794872</v>
-      </c>
-      <c r="CE34" t="n">
-        <v>0.1794871794871795</v>
-      </c>
-      <c r="CF34" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="CG34" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="CH34" t="n">
-        <v>0.4871794871794872</v>
-      </c>
-      <c r="CI34" t="n">
-        <v>0.5128205128205128</v>
-      </c>
-      <c r="CJ34" t="n">
-        <v>0.4375</v>
       </c>
       <c r="CK34" t="n">
         <v>1.25</v>
@@ -8568,10 +8568,10 @@
         <v>180</v>
       </c>
       <c r="DK34" t="n">
-        <v>816</v>
+        <v>944</v>
       </c>
       <c r="DL34" t="n">
-        <v>4.533333333333333</v>
+        <v>5.244444444444444</v>
       </c>
     </row>
     <row r="35">
@@ -8649,7 +8649,7 @@
         <v>9</v>
       </c>
       <c r="T35" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="U35" t="n">
         <v>3</v>
@@ -8705,7 +8705,7 @@
         <v>19</v>
       </c>
       <c r="BB35" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="BC35" t="n">
         <v>1</v>
@@ -8761,7 +8761,7 @@
         <v>0.4736842105263158</v>
       </c>
       <c r="CJ35" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.5</v>
       </c>
       <c r="CK35" t="n">
         <v>3</v>
@@ -8796,10 +8796,10 @@
         <v>110</v>
       </c>
       <c r="DK35" t="n">
-        <v>555</v>
+        <v>483</v>
       </c>
       <c r="DL35" t="n">
-        <v>5.045454545454546</v>
+        <v>4.390909090909091</v>
       </c>
     </row>
     <row r="36">
@@ -8853,28 +8853,28 @@
         <v>14</v>
       </c>
       <c r="L36" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M36" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N36" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O36" t="n">
+        <v>13</v>
+      </c>
+      <c r="P36" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q36" t="n">
         <v>4</v>
       </c>
-      <c r="P36" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
       <c r="R36" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T36" t="n">
         <v>2</v>
@@ -8933,7 +8933,7 @@
         <v>21</v>
       </c>
       <c r="BB36" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="BC36" t="n">
         <v>2</v>
@@ -8965,31 +8965,31 @@
         <v>2</v>
       </c>
       <c r="CB36" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CC36" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CD36" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CE36" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="CF36" t="n">
+        <v>1.571428571428571</v>
+      </c>
+      <c r="CG36" t="n">
         <v>0.1904761904761905</v>
       </c>
-      <c r="CF36" t="n">
-        <v>0.9523809523809523</v>
-      </c>
-      <c r="CG36" t="n">
-        <v>0.04761904761904762</v>
-      </c>
       <c r="CH36" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="CI36" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CJ36" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="CK36" t="n">
         <v>1.5</v>
@@ -9024,10 +9024,10 @@
         <v>115</v>
       </c>
       <c r="DK36" t="n">
-        <v>343</v>
+        <v>543</v>
       </c>
       <c r="DL36" t="n">
-        <v>2.982608695652174</v>
+        <v>4.721739130434782</v>
       </c>
     </row>
     <row r="37">
@@ -9081,31 +9081,31 @@
         <v>24</v>
       </c>
       <c r="L37" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="M37" t="n">
+        <v>20</v>
+      </c>
+      <c r="N37" t="n">
+        <v>31</v>
+      </c>
+      <c r="O37" t="n">
+        <v>22</v>
+      </c>
+      <c r="P37" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>9</v>
+      </c>
+      <c r="R37" t="n">
+        <v>33</v>
+      </c>
+      <c r="S37" t="n">
         <v>16</v>
       </c>
-      <c r="N37" t="n">
-        <v>23</v>
-      </c>
-      <c r="O37" t="n">
-        <v>13</v>
-      </c>
-      <c r="P37" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>6</v>
-      </c>
-      <c r="R37" t="n">
-        <v>25</v>
-      </c>
-      <c r="S37" t="n">
-        <v>18</v>
-      </c>
       <c r="T37" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="U37" t="n">
         <v>6</v>
@@ -9161,7 +9161,7 @@
         <v>40</v>
       </c>
       <c r="BB37" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="BC37" t="n">
         <v>3</v>
@@ -9193,31 +9193,31 @@
         <v>3</v>
       </c>
       <c r="CB37" t="n">
-        <v>0.375</v>
+        <v>0.6</v>
       </c>
       <c r="CC37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CD37" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="CE37" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="CF37" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="CG37" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="CH37" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="CI37" t="n">
         <v>0.4</v>
       </c>
-      <c r="CD37" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="CE37" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="CF37" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="CG37" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="CH37" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="CI37" t="n">
-        <v>0.45</v>
-      </c>
       <c r="CJ37" t="n">
-        <v>0.5357142857142857</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="CK37" t="n">
         <v>2</v>
@@ -9252,10 +9252,10 @@
         <v>225</v>
       </c>
       <c r="DK37" t="n">
-        <v>898</v>
+        <v>1026</v>
       </c>
       <c r="DL37" t="n">
-        <v>3.991111111111111</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="38">
@@ -9333,7 +9333,7 @@
         <v>10</v>
       </c>
       <c r="T38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U38" t="n">
         <v>4</v>
@@ -9391,7 +9391,7 @@
         <v>18</v>
       </c>
       <c r="BB38" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BC38" t="n">
         <v>3</v>
@@ -9449,7 +9449,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="CJ38" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.5</v>
       </c>
       <c r="CK38" t="n">
         <v>1.333333333333333</v>
@@ -9486,10 +9486,10 @@
         <v>68</v>
       </c>
       <c r="DK38" t="n">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="DL38" t="n">
-        <v>5.647058823529412</v>
+        <v>5.514705882352941</v>
       </c>
     </row>
     <row r="39">
@@ -9543,28 +9543,28 @@
         <v>15</v>
       </c>
       <c r="L39" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M39" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N39" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P39" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="Q39" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="R39" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="T39" t="n">
         <v>12</v>
@@ -9623,7 +9623,7 @@
         <v>22</v>
       </c>
       <c r="BB39" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="BC39" t="n">
         <v>2</v>
@@ -9655,31 +9655,31 @@
         <v>2</v>
       </c>
       <c r="CB39" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="CC39" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="CD39" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="CE39" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CF39" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="CG39" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="CH39" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="CI39" t="n">
-        <v>0.3181818181818182</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="CJ39" t="n">
-        <v>1.090909090909091</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="CK39" t="n">
         <v>2</v>
@@ -9714,10 +9714,10 @@
         <v>132</v>
       </c>
       <c r="DK39" t="n">
-        <v>422</v>
+        <v>711</v>
       </c>
       <c r="DL39" t="n">
-        <v>3.196969696969697</v>
+        <v>5.386363636363637</v>
       </c>
     </row>
     <row r="40">
@@ -9771,31 +9771,31 @@
         <v>25</v>
       </c>
       <c r="L40" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M40" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N40" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="O40" t="n">
+        <v>17</v>
+      </c>
+      <c r="P40" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>20</v>
+      </c>
+      <c r="R40" t="n">
+        <v>27</v>
+      </c>
+      <c r="S40" t="n">
+        <v>29</v>
+      </c>
+      <c r="T40" t="n">
         <v>18</v>
-      </c>
-      <c r="P40" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>12</v>
-      </c>
-      <c r="R40" t="n">
-        <v>18</v>
-      </c>
-      <c r="S40" t="n">
-        <v>17</v>
-      </c>
-      <c r="T40" t="n">
-        <v>19</v>
       </c>
       <c r="U40" t="n">
         <v>8</v>
@@ -9853,7 +9853,7 @@
         <v>40</v>
       </c>
       <c r="BB40" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BC40" t="n">
         <v>5</v>
@@ -9887,31 +9887,31 @@
         <v>6</v>
       </c>
       <c r="CB40" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="CC40" t="n">
-        <v>0.275</v>
+        <v>0.425</v>
       </c>
       <c r="CD40" t="n">
-        <v>0.375</v>
+        <v>0.525</v>
       </c>
       <c r="CE40" t="n">
-        <v>0.45</v>
+        <v>0.425</v>
       </c>
       <c r="CF40" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="CG40" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="CH40" t="n">
-        <v>0.45</v>
+        <v>0.675</v>
       </c>
       <c r="CI40" t="n">
-        <v>0.425</v>
+        <v>0.725</v>
       </c>
       <c r="CJ40" t="n">
-        <v>0.6551724137931034</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="CK40" t="n">
         <v>1.6</v>
@@ -9948,10 +9948,10 @@
         <v>200</v>
       </c>
       <c r="DK40" t="n">
-        <v>806</v>
+        <v>1086</v>
       </c>
       <c r="DL40" t="n">
-        <v>4.03</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="41">
@@ -10029,7 +10029,7 @@
         <v>8</v>
       </c>
       <c r="T41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U41" t="n">
         <v>4</v>
@@ -10085,7 +10085,7 @@
         <v>23</v>
       </c>
       <c r="BB41" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="BC41" t="n">
         <v>2</v>
@@ -10141,7 +10141,7 @@
         <v>0.3478260869565217</v>
       </c>
       <c r="CJ41" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="CK41" t="n">
         <v>2</v>
@@ -10176,10 +10176,10 @@
         <v>87</v>
       </c>
       <c r="DK41" t="n">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="DL41" t="n">
-        <v>5.275862068965517</v>
+        <v>5.068965517241379</v>
       </c>
     </row>
     <row r="42">
@@ -10233,28 +10233,28 @@
         <v>10</v>
       </c>
       <c r="L42" t="n">
+        <v>8</v>
+      </c>
+      <c r="M42" t="n">
         <v>6</v>
       </c>
-      <c r="M42" t="n">
-        <v>2</v>
-      </c>
       <c r="N42" t="n">
+        <v>19</v>
+      </c>
+      <c r="O42" t="n">
+        <v>8</v>
+      </c>
+      <c r="P42" t="n">
         <v>10</v>
-      </c>
-      <c r="O42" t="n">
-        <v>6</v>
-      </c>
-      <c r="P42" t="n">
-        <v>7</v>
       </c>
       <c r="Q42" t="n">
         <v>5</v>
       </c>
       <c r="R42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T42" t="n">
         <v>6</v>
@@ -10315,7 +10315,7 @@
         <v>17</v>
       </c>
       <c r="BB42" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="BC42" t="n">
         <v>2</v>
@@ -10349,31 +10349,31 @@
         <v>3</v>
       </c>
       <c r="CB42" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="CC42" t="n">
         <v>0.3529411764705883</v>
       </c>
-      <c r="CC42" t="n">
-        <v>0.1176470588235294</v>
-      </c>
       <c r="CD42" t="n">
+        <v>1.117647058823529</v>
+      </c>
+      <c r="CE42" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="CF42" t="n">
         <v>0.5882352941176471</v>
-      </c>
-      <c r="CE42" t="n">
-        <v>0.3529411764705883</v>
-      </c>
-      <c r="CF42" t="n">
-        <v>0.4117647058823529</v>
       </c>
       <c r="CG42" t="n">
         <v>0.2941176470588235</v>
       </c>
       <c r="CH42" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="CI42" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="CJ42" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="CK42" t="n">
         <v>1</v>
@@ -10410,10 +10410,10 @@
         <v>76</v>
       </c>
       <c r="DK42" t="n">
-        <v>268</v>
+        <v>359</v>
       </c>
       <c r="DL42" t="n">
-        <v>3.526315789473684</v>
+        <v>4.723684210526316</v>
       </c>
     </row>
     <row r="43">
@@ -10467,31 +10467,31 @@
         <v>21</v>
       </c>
       <c r="L43" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M43" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N43" t="n">
+        <v>25</v>
+      </c>
+      <c r="O43" t="n">
         <v>16</v>
       </c>
-      <c r="O43" t="n">
-        <v>14</v>
-      </c>
       <c r="P43" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q43" t="n">
         <v>23</v>
       </c>
       <c r="R43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S43" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T43" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U43" t="n">
         <v>6</v>
@@ -10549,7 +10549,7 @@
         <v>40</v>
       </c>
       <c r="BB43" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="BC43" t="n">
         <v>4</v>
@@ -10583,31 +10583,31 @@
         <v>5</v>
       </c>
       <c r="CB43" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="CC43" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="CD43" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CE43" t="n">
         <v>0.4</v>
       </c>
-      <c r="CE43" t="n">
-        <v>0.35</v>
-      </c>
       <c r="CF43" t="n">
-        <v>0.3</v>
+        <v>0.375</v>
       </c>
       <c r="CG43" t="n">
         <v>0.575</v>
       </c>
       <c r="CH43" t="n">
-        <v>0.25</v>
+        <v>0.275</v>
       </c>
       <c r="CI43" t="n">
-        <v>0.325</v>
+        <v>0.4</v>
       </c>
       <c r="CJ43" t="n">
-        <v>0.5</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="CK43" t="n">
         <v>1.5</v>
@@ -10644,10 +10644,10 @@
         <v>163</v>
       </c>
       <c r="DK43" t="n">
-        <v>727</v>
+        <v>800</v>
       </c>
       <c r="DL43" t="n">
-        <v>4.460122699386503</v>
+        <v>4.907975460122699</v>
       </c>
     </row>
     <row r="44">
@@ -10777,7 +10777,7 @@
         <v>17</v>
       </c>
       <c r="BB44" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="BC44" t="inlineStr"/>
       <c r="BD44" t="inlineStr"/>
@@ -10831,7 +10831,7 @@
         <v>0.05882352941176471</v>
       </c>
       <c r="CJ44" t="n">
-        <v>0.5294117647058824</v>
+        <v>1</v>
       </c>
       <c r="CK44" t="inlineStr"/>
       <c r="CL44" t="inlineStr"/>
@@ -10919,28 +10919,28 @@
         <v>12</v>
       </c>
       <c r="L45" t="n">
+        <v>16</v>
+      </c>
+      <c r="M45" t="n">
+        <v>10</v>
+      </c>
+      <c r="N45" t="n">
+        <v>5</v>
+      </c>
+      <c r="O45" t="n">
         <v>7</v>
       </c>
-      <c r="M45" t="n">
-        <v>1</v>
-      </c>
-      <c r="N45" t="n">
-        <v>3</v>
-      </c>
-      <c r="O45" t="n">
-        <v>8</v>
-      </c>
       <c r="P45" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="Q45" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="R45" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T45" t="n">
         <v>6</v>
@@ -10999,7 +10999,7 @@
         <v>22</v>
       </c>
       <c r="BB45" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="BC45" t="n">
         <v>1</v>
@@ -11031,31 +11031,31 @@
         <v>1</v>
       </c>
       <c r="CB45" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CC45" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="CD45" t="n">
+        <v>0.2272727272727273</v>
+      </c>
+      <c r="CE45" t="n">
         <v>0.3181818181818182</v>
       </c>
-      <c r="CC45" t="n">
-        <v>0.04545454545454546</v>
-      </c>
-      <c r="CD45" t="n">
-        <v>0.1363636363636364</v>
-      </c>
-      <c r="CE45" t="n">
-        <v>0.3636363636363636</v>
-      </c>
       <c r="CF45" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="CG45" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="CH45" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="CI45" t="n">
-        <v>0.5</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="CJ45" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="CK45" t="n">
         <v>1</v>
@@ -11090,10 +11090,10 @@
         <v>103</v>
       </c>
       <c r="DK45" t="n">
-        <v>323</v>
+        <v>509</v>
       </c>
       <c r="DL45" t="n">
-        <v>3.135922330097087</v>
+        <v>4.941747572815534</v>
       </c>
     </row>
     <row r="46">
@@ -11147,28 +11147,28 @@
         <v>21</v>
       </c>
       <c r="L46" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="N46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O46" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P46" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="Q46" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="R46" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="S46" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T46" t="n">
         <v>15</v>
@@ -11227,7 +11227,7 @@
         <v>39</v>
       </c>
       <c r="BB46" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="BC46" t="n">
         <v>1</v>
@@ -11259,31 +11259,31 @@
         <v>1</v>
       </c>
       <c r="CB46" t="n">
-        <v>0.5128205128205128</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="CC46" t="n">
-        <v>0.1025641025641026</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CD46" t="n">
-        <v>0.2051282051282051</v>
+        <v>0.2564102564102564</v>
       </c>
       <c r="CE46" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="CF46" t="n">
-        <v>0.4358974358974359</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CG46" t="n">
-        <v>0.2564102564102564</v>
+        <v>0.4871794871794872</v>
       </c>
       <c r="CH46" t="n">
-        <v>0.2051282051282051</v>
+        <v>0.358974358974359</v>
       </c>
       <c r="CI46" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.358974358974359</v>
       </c>
       <c r="CJ46" t="n">
-        <v>0.5357142857142857</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="CK46" t="n">
         <v>1</v>
@@ -11318,10 +11318,10 @@
         <v>152</v>
       </c>
       <c r="DK46" t="n">
-        <v>542</v>
+        <v>728</v>
       </c>
       <c r="DL46" t="n">
-        <v>3.565789473684211</v>
+        <v>4.789473684210527</v>
       </c>
     </row>
     <row r="47">
@@ -11399,7 +11399,7 @@
         <v>16</v>
       </c>
       <c r="T47" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U47" t="n">
         <v>4</v>
@@ -11455,7 +11455,7 @@
         <v>18</v>
       </c>
       <c r="BB47" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="BC47" t="n">
         <v>1</v>
@@ -11511,7 +11511,7 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="CJ47" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.625</v>
       </c>
       <c r="CK47" t="n">
         <v>4</v>
@@ -11546,10 +11546,10 @@
         <v>65</v>
       </c>
       <c r="DK47" t="n">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="DL47" t="n">
-        <v>5.8</v>
+        <v>5.523076923076923</v>
       </c>
     </row>
     <row r="48">
@@ -11603,28 +11603,28 @@
         <v>7</v>
       </c>
       <c r="L48" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N48" t="n">
         <v>6</v>
       </c>
       <c r="O48" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q48" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="R48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="n">
         <v>3</v>
@@ -11683,7 +11683,7 @@
         <v>22</v>
       </c>
       <c r="BB48" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="BC48" t="n">
         <v>1</v>
@@ -11715,31 +11715,31 @@
         <v>1</v>
       </c>
       <c r="CB48" t="n">
-        <v>0.9090909090909091</v>
+        <v>1</v>
       </c>
       <c r="CC48" t="n">
-        <v>0.3181818181818182</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CD48" t="n">
         <v>0.2727272727272727</v>
       </c>
       <c r="CE48" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="CF48" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="CG48" t="n">
-        <v>0.3181818181818182</v>
+        <v>0.5</v>
       </c>
       <c r="CH48" t="n">
-        <v>0.04545454545454546</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="CI48" t="n">
+        <v>0.2272727272727273</v>
+      </c>
+      <c r="CJ48" t="n">
         <v>0.1363636363636364</v>
-      </c>
-      <c r="CJ48" t="n">
-        <v>0.1875</v>
       </c>
       <c r="CK48" t="n">
         <v>1</v>
@@ -11774,10 +11774,10 @@
         <v>74</v>
       </c>
       <c r="DK48" t="n">
-        <v>196</v>
+        <v>288</v>
       </c>
       <c r="DL48" t="n">
-        <v>2.648648648648649</v>
+        <v>3.891891891891892</v>
       </c>
     </row>
     <row r="49">
@@ -11831,31 +11831,31 @@
         <v>13</v>
       </c>
       <c r="L49" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M49" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N49" t="n">
         <v>10</v>
       </c>
       <c r="O49" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="P49" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q49" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="R49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S49" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="T49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U49" t="n">
         <v>5</v>
@@ -11911,7 +11911,7 @@
         <v>40</v>
       </c>
       <c r="BB49" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BC49" t="n">
         <v>2</v>
@@ -11943,31 +11943,31 @@
         <v>2</v>
       </c>
       <c r="CB49" t="n">
-        <v>0.575</v>
+        <v>0.625</v>
       </c>
       <c r="CC49" t="n">
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="CD49" t="n">
         <v>0.25</v>
       </c>
       <c r="CE49" t="n">
-        <v>0.35</v>
+        <v>0.425</v>
       </c>
       <c r="CF49" t="n">
-        <v>0.25</v>
+        <v>0.325</v>
       </c>
       <c r="CG49" t="n">
-        <v>0.325</v>
+        <v>0.425</v>
       </c>
       <c r="CH49" t="n">
-        <v>0.05</v>
+        <v>0.125</v>
       </c>
       <c r="CI49" t="n">
-        <v>0.475</v>
+        <v>0.525</v>
       </c>
       <c r="CJ49" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="CK49" t="n">
         <v>2.5</v>
@@ -12002,10 +12002,10 @@
         <v>139</v>
       </c>
       <c r="DK49" t="n">
-        <v>573</v>
+        <v>647</v>
       </c>
       <c r="DL49" t="n">
-        <v>4.122302158273381</v>
+        <v>4.654676258992806</v>
       </c>
     </row>
     <row r="50">
@@ -12083,7 +12083,7 @@
         <v>5</v>
       </c>
       <c r="T50" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="U50" t="n">
         <v>7</v>
@@ -12139,7 +12139,7 @@
         <v>25</v>
       </c>
       <c r="BB50" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="BC50" t="n">
         <v>2</v>
@@ -12195,7 +12195,7 @@
         <v>0.2</v>
       </c>
       <c r="CJ50" t="n">
-        <v>0.36</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CK50" t="n">
         <v>3.5</v>
@@ -12230,10 +12230,10 @@
         <v>98</v>
       </c>
       <c r="DK50" t="n">
-        <v>448</v>
+        <v>403</v>
       </c>
       <c r="DL50" t="n">
-        <v>4.571428571428571</v>
+        <v>4.112244897959184</v>
       </c>
     </row>
     <row r="51">
@@ -12287,28 +12287,28 @@
         <v>10</v>
       </c>
       <c r="L51" t="n">
+        <v>12</v>
+      </c>
+      <c r="M51" t="n">
+        <v>7</v>
+      </c>
+      <c r="N51" t="n">
+        <v>7</v>
+      </c>
+      <c r="O51" t="n">
+        <v>3</v>
+      </c>
+      <c r="P51" t="n">
         <v>9</v>
       </c>
-      <c r="M51" t="n">
+      <c r="Q51" t="n">
+        <v>14</v>
+      </c>
+      <c r="R51" t="n">
         <v>8</v>
       </c>
-      <c r="N51" t="n">
-        <v>2</v>
-      </c>
-      <c r="O51" t="n">
-        <v>5</v>
-      </c>
-      <c r="P51" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>1</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1</v>
-      </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T51" t="n">
         <v>5</v>
@@ -12363,7 +12363,7 @@
         <v>15</v>
       </c>
       <c r="BB51" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="BC51" t="inlineStr"/>
       <c r="BD51" t="inlineStr"/>
@@ -12393,31 +12393,31 @@
         <v>0</v>
       </c>
       <c r="CB51" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CC51" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="CD51" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="CE51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CF51" t="n">
         <v>0.6</v>
       </c>
-      <c r="CC51" t="n">
+      <c r="CG51" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="CH51" t="n">
         <v>0.5333333333333333</v>
       </c>
-      <c r="CD51" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="CE51" t="n">
+      <c r="CI51" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="CJ51" t="n">
         <v>0.3333333333333333</v>
-      </c>
-      <c r="CF51" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="CG51" t="n">
-        <v>0.06666666666666667</v>
-      </c>
-      <c r="CH51" t="n">
-        <v>0.06666666666666667</v>
-      </c>
-      <c r="CI51" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="CJ51" t="n">
-        <v>0.8333333333333334</v>
       </c>
       <c r="CK51" t="inlineStr"/>
       <c r="CL51" t="inlineStr"/>
@@ -12448,10 +12448,10 @@
         <v>79</v>
       </c>
       <c r="DK51" t="n">
-        <v>198</v>
+        <v>401</v>
       </c>
       <c r="DL51" t="n">
-        <v>2.506329113924051</v>
+        <v>5.075949367088608</v>
       </c>
     </row>
     <row r="52">
@@ -12505,31 +12505,31 @@
         <v>22</v>
       </c>
       <c r="L52" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M52" t="n">
+        <v>8</v>
+      </c>
+      <c r="N52" t="n">
+        <v>20</v>
+      </c>
+      <c r="O52" t="n">
+        <v>22</v>
+      </c>
+      <c r="P52" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>20</v>
+      </c>
+      <c r="R52" t="n">
+        <v>13</v>
+      </c>
+      <c r="S52" t="n">
+        <v>19</v>
+      </c>
+      <c r="T52" t="n">
         <v>9</v>
-      </c>
-      <c r="N52" t="n">
-        <v>15</v>
-      </c>
-      <c r="O52" t="n">
-        <v>24</v>
-      </c>
-      <c r="P52" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>7</v>
-      </c>
-      <c r="R52" t="n">
-        <v>6</v>
-      </c>
-      <c r="S52" t="n">
-        <v>13</v>
-      </c>
-      <c r="T52" t="n">
-        <v>14</v>
       </c>
       <c r="U52" t="n">
         <v>7</v>
@@ -12585,7 +12585,7 @@
         <v>40</v>
       </c>
       <c r="BB52" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="BC52" t="n">
         <v>2</v>
@@ -12617,31 +12617,31 @@
         <v>2</v>
       </c>
       <c r="CB52" t="n">
-        <v>0.825</v>
+        <v>0.9</v>
       </c>
       <c r="CC52" t="n">
-        <v>0.225</v>
+        <v>0.2</v>
       </c>
       <c r="CD52" t="n">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
       <c r="CE52" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="CF52" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="CG52" t="n">
-        <v>0.175</v>
+        <v>0.5</v>
       </c>
       <c r="CH52" t="n">
-        <v>0.15</v>
+        <v>0.325</v>
       </c>
       <c r="CI52" t="n">
-        <v>0.325</v>
+        <v>0.475</v>
       </c>
       <c r="CJ52" t="n">
-        <v>0.4516129032258064</v>
+        <v>0.3103448275862069</v>
       </c>
       <c r="CK52" t="n">
         <v>3.5</v>
@@ -12676,10 +12676,10 @@
         <v>177</v>
       </c>
       <c r="DK52" t="n">
-        <v>646</v>
+        <v>804</v>
       </c>
       <c r="DL52" t="n">
-        <v>3.649717514124294</v>
+        <v>4.542372881355933</v>
       </c>
     </row>
     <row r="53">
@@ -12753,7 +12753,7 @@
         <v>15</v>
       </c>
       <c r="T53" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U53" t="n">
         <v>3</v>
@@ -12811,7 +12811,7 @@
         <v>18</v>
       </c>
       <c r="BB53" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BC53" t="n">
         <v>3</v>
@@ -12869,7 +12869,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="CJ53" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CK53" t="n">
         <v>1</v>
@@ -12906,10 +12906,10 @@
         <v>90</v>
       </c>
       <c r="DK53" t="n">
-        <v>493</v>
+        <v>466</v>
       </c>
       <c r="DL53" t="n">
-        <v>5.477777777777778</v>
+        <v>5.177777777777778</v>
       </c>
     </row>
     <row r="54">
@@ -12959,28 +12959,28 @@
         <v>12</v>
       </c>
       <c r="L54" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M54" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R54" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T54" t="n">
         <v>2</v>
@@ -13041,7 +13041,7 @@
         <v>21</v>
       </c>
       <c r="BB54" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="BC54" t="n">
         <v>4</v>
@@ -13075,31 +13075,31 @@
         <v>5</v>
       </c>
       <c r="CB54" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CC54" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CD54" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="CE54" t="n">
-        <v>0.09523809523809523</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CF54" t="n">
         <v>0.04761904761904762</v>
       </c>
       <c r="CG54" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="CH54" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="CI54" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="CJ54" t="n">
         <v>0.09523809523809523</v>
-      </c>
-      <c r="CI54" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="CJ54" t="n">
-        <v>0.1666666666666667</v>
       </c>
       <c r="CK54" t="n">
         <v>0.5</v>
@@ -13136,10 +13136,10 @@
         <v>75</v>
       </c>
       <c r="DK54" t="n">
-        <v>188</v>
+        <v>368</v>
       </c>
       <c r="DL54" t="n">
-        <v>2.506666666666667</v>
+        <v>4.906666666666666</v>
       </c>
     </row>
     <row r="55">
@@ -13189,31 +13189,31 @@
         <v>24</v>
       </c>
       <c r="L55" t="n">
+        <v>21</v>
+      </c>
+      <c r="M55" t="n">
+        <v>15</v>
+      </c>
+      <c r="N55" t="n">
+        <v>22</v>
+      </c>
+      <c r="O55" t="n">
         <v>14</v>
-      </c>
-      <c r="M55" t="n">
-        <v>18</v>
-      </c>
-      <c r="N55" t="n">
-        <v>13</v>
-      </c>
-      <c r="O55" t="n">
-        <v>12</v>
       </c>
       <c r="P55" t="n">
         <v>6</v>
       </c>
       <c r="Q55" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="R55" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="S55" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="T55" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="U55" t="n">
         <v>5</v>
@@ -13271,7 +13271,7 @@
         <v>39</v>
       </c>
       <c r="BB55" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="BC55" t="n">
         <v>7</v>
@@ -13305,31 +13305,31 @@
         <v>9</v>
       </c>
       <c r="CB55" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="CC55" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="CD55" t="n">
+        <v>0.5641025641025641</v>
+      </c>
+      <c r="CE55" t="n">
         <v>0.358974358974359</v>
-      </c>
-      <c r="CC55" t="n">
-        <v>0.4615384615384616</v>
-      </c>
-      <c r="CD55" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="CE55" t="n">
-        <v>0.3076923076923077</v>
       </c>
       <c r="CF55" t="n">
         <v>0.1538461538461539</v>
       </c>
       <c r="CG55" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="CH55" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4358974358974359</v>
       </c>
       <c r="CI55" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.717948717948718</v>
       </c>
       <c r="CJ55" t="n">
-        <v>0.3666666666666666</v>
+        <v>0.2285714285714286</v>
       </c>
       <c r="CK55" t="n">
         <v>0.7142857142857143</v>
@@ -13366,10 +13366,10 @@
         <v>165</v>
       </c>
       <c r="DK55" t="n">
-        <v>681</v>
+        <v>834</v>
       </c>
       <c r="DL55" t="n">
-        <v>4.127272727272727</v>
+        <v>5.054545454545455</v>
       </c>
     </row>
     <row r="56">
@@ -13443,7 +13443,7 @@
         <v>9</v>
       </c>
       <c r="T56" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="U56" t="n">
         <v>2</v>
@@ -13501,7 +13501,7 @@
         <v>23</v>
       </c>
       <c r="BB56" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="BC56" t="n">
         <v>4</v>
@@ -13559,7 +13559,7 @@
         <v>0.391304347826087</v>
       </c>
       <c r="CJ56" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CK56" t="n">
         <v>0.5</v>
@@ -13596,10 +13596,10 @@
         <v>127</v>
       </c>
       <c r="DK56" t="n">
-        <v>635</v>
+        <v>599</v>
       </c>
       <c r="DL56" t="n">
-        <v>5</v>
+        <v>4.716535433070866</v>
       </c>
     </row>
     <row r="57">
@@ -13649,28 +13649,28 @@
         <v>10</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M57" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N57" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P57" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q57" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="R57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T57" t="n">
         <v>1</v>
@@ -13729,7 +13729,7 @@
         <v>17</v>
       </c>
       <c r="BB57" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="BC57" t="n">
         <v>2</v>
@@ -13761,31 +13761,31 @@
         <v>2</v>
       </c>
       <c r="CB57" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="CC57" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="CD57" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="CE57" t="n">
+        <v>0.2941176470588235</v>
+      </c>
+      <c r="CF57" t="n">
+        <v>0.4117647058823529</v>
+      </c>
+      <c r="CG57" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="CH57" t="n">
+        <v>0.2941176470588235</v>
+      </c>
+      <c r="CI57" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="CJ57" t="n">
         <v>0.05882352941176471</v>
-      </c>
-      <c r="CC57" t="n">
-        <v>0.2352941176470588</v>
-      </c>
-      <c r="CD57" t="n">
-        <v>0.5294117647058824</v>
-      </c>
-      <c r="CE57" t="n">
-        <v>0.3529411764705883</v>
-      </c>
-      <c r="CF57" t="n">
-        <v>0.05882352941176471</v>
-      </c>
-      <c r="CG57" t="n">
-        <v>0.2352941176470588</v>
-      </c>
-      <c r="CH57" t="n">
-        <v>0.1176470588235294</v>
-      </c>
-      <c r="CI57" t="n">
-        <v>0.4705882352941176</v>
-      </c>
-      <c r="CJ57" t="n">
-        <v>0.125</v>
       </c>
       <c r="CK57" t="n">
         <v>1</v>
@@ -13820,10 +13820,10 @@
         <v>75</v>
       </c>
       <c r="DK57" t="n">
-        <v>196</v>
+        <v>346</v>
       </c>
       <c r="DL57" t="n">
-        <v>2.613333333333333</v>
+        <v>4.613333333333333</v>
       </c>
     </row>
     <row r="58">
@@ -13873,31 +13873,31 @@
         <v>22</v>
       </c>
       <c r="L58" t="n">
+        <v>25</v>
+      </c>
+      <c r="M58" t="n">
         <v>17</v>
       </c>
-      <c r="M58" t="n">
-        <v>12</v>
-      </c>
       <c r="N58" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="O58" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P58" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Q58" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="R58" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="S58" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T58" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="U58" t="n">
         <v>4</v>
@@ -13955,7 +13955,7 @@
         <v>40</v>
       </c>
       <c r="BB58" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BC58" t="n">
         <v>6</v>
@@ -13989,31 +13989,31 @@
         <v>7</v>
       </c>
       <c r="CB58" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CC58" t="n">
         <v>0.425</v>
       </c>
-      <c r="CC58" t="n">
-        <v>0.3</v>
-      </c>
       <c r="CD58" t="n">
-        <v>0.725</v>
+        <v>0.85</v>
       </c>
       <c r="CE58" t="n">
-        <v>0.5</v>
+        <v>0.475</v>
       </c>
       <c r="CF58" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="CG58" t="n">
-        <v>0.525</v>
+        <v>0.75</v>
       </c>
       <c r="CH58" t="n">
-        <v>0.3</v>
+        <v>0.375</v>
       </c>
       <c r="CI58" t="n">
-        <v>0.425</v>
+        <v>0.475</v>
       </c>
       <c r="CJ58" t="n">
-        <v>0.4838709677419355</v>
+        <v>0.34375</v>
       </c>
       <c r="CK58" t="n">
         <v>0.6666666666666666</v>
@@ -14050,10 +14050,10 @@
         <v>202</v>
       </c>
       <c r="DK58" t="n">
-        <v>831</v>
+        <v>945</v>
       </c>
       <c r="DL58" t="n">
-        <v>4.113861386138614</v>
+        <v>4.678217821782178</v>
       </c>
     </row>
     <row r="59">
@@ -14131,7 +14131,7 @@
         <v>16</v>
       </c>
       <c r="T59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U59" t="n">
         <v>2</v>
@@ -14191,7 +14191,7 @@
         <v>19</v>
       </c>
       <c r="BB59" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BC59" t="n">
         <v>2</v>
@@ -14251,7 +14251,7 @@
         <v>0.8421052631578947</v>
       </c>
       <c r="CJ59" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="CK59" t="n">
         <v>1</v>
@@ -14290,10 +14290,10 @@
         <v>125</v>
       </c>
       <c r="DK59" t="n">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="DL59" t="n">
-        <v>5.032</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="60">
@@ -14347,28 +14347,28 @@
         <v>8</v>
       </c>
       <c r="L60" t="n">
+        <v>10</v>
+      </c>
+      <c r="M60" t="n">
+        <v>8</v>
+      </c>
+      <c r="N60" t="n">
+        <v>9</v>
+      </c>
+      <c r="O60" t="n">
+        <v>18</v>
+      </c>
+      <c r="P60" t="n">
         <v>11</v>
       </c>
-      <c r="M60" t="n">
-        <v>1</v>
-      </c>
-      <c r="N60" t="n">
+      <c r="Q60" t="n">
+        <v>19</v>
+      </c>
+      <c r="R60" t="n">
         <v>8</v>
       </c>
-      <c r="O60" t="n">
-        <v>7</v>
-      </c>
-      <c r="P60" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>4</v>
-      </c>
-      <c r="R60" t="n">
+      <c r="S60" t="n">
         <v>10</v>
-      </c>
-      <c r="S60" t="n">
-        <v>5</v>
       </c>
       <c r="T60" t="n">
         <v>4</v>
@@ -14427,7 +14427,7 @@
         <v>21</v>
       </c>
       <c r="BB60" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="BC60" t="n">
         <v>4</v>
@@ -14459,31 +14459,31 @@
         <v>4</v>
       </c>
       <c r="CB60" t="n">
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="CC60" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="CD60" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="CE60" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CF60" t="n">
         <v>0.5238095238095238</v>
       </c>
-      <c r="CC60" t="n">
-        <v>0.04761904761904762</v>
-      </c>
-      <c r="CD60" t="n">
+      <c r="CG60" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="CH60" t="n">
         <v>0.3809523809523809</v>
       </c>
-      <c r="CE60" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="CF60" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="CG60" t="n">
-        <v>0.1904761904761905</v>
-      </c>
-      <c r="CH60" t="n">
+      <c r="CI60" t="n">
         <v>0.4761904761904762</v>
       </c>
-      <c r="CI60" t="n">
-        <v>0.2380952380952381</v>
-      </c>
       <c r="CJ60" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2</v>
       </c>
       <c r="CK60" t="n">
         <v>0.75</v>
@@ -14518,10 +14518,10 @@
         <v>100</v>
       </c>
       <c r="DK60" t="n">
-        <v>325</v>
+        <v>496</v>
       </c>
       <c r="DL60" t="n">
-        <v>3.25</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="61">
@@ -14575,31 +14575,31 @@
         <v>21</v>
       </c>
       <c r="L61" t="n">
+        <v>19</v>
+      </c>
+      <c r="M61" t="n">
+        <v>28</v>
+      </c>
+      <c r="N61" t="n">
+        <v>22</v>
+      </c>
+      <c r="O61" t="n">
+        <v>33</v>
+      </c>
+      <c r="P61" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>31</v>
+      </c>
+      <c r="R61" t="n">
         <v>20</v>
       </c>
-      <c r="M61" t="n">
-        <v>21</v>
-      </c>
-      <c r="N61" t="n">
-        <v>21</v>
-      </c>
-      <c r="O61" t="n">
-        <v>22</v>
-      </c>
-      <c r="P61" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>16</v>
-      </c>
-      <c r="R61" t="n">
-        <v>22</v>
-      </c>
       <c r="S61" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="T61" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U61" t="n">
         <v>5</v>
@@ -14695,31 +14695,31 @@
         <v>8</v>
       </c>
       <c r="CB61" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="CC61" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CD61" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="CE61" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="CF61" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="CG61" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="CH61" t="n">
         <v>0.5</v>
       </c>
-      <c r="CC61" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="CD61" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="CE61" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="CF61" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="CG61" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="CH61" t="n">
-        <v>0.55</v>
-      </c>
       <c r="CI61" t="n">
-        <v>0.525</v>
+        <v>0.65</v>
       </c>
       <c r="CJ61" t="n">
-        <v>0.4242424242424243</v>
+        <v>0.3939393939393939</v>
       </c>
       <c r="CK61" t="n">
         <v>0.8333333333333334</v>
@@ -14758,10 +14758,10 @@
         <v>225</v>
       </c>
       <c r="DK61" t="n">
-        <v>954</v>
+        <v>1116</v>
       </c>
       <c r="DL61" t="n">
-        <v>4.24</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="62">
@@ -14839,7 +14839,7 @@
         <v>9</v>
       </c>
       <c r="T62" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -14897,7 +14897,7 @@
         <v>23</v>
       </c>
       <c r="BB62" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="BC62" t="n">
         <v>5</v>
@@ -14955,7 +14955,7 @@
         <v>0.391304347826087</v>
       </c>
       <c r="CJ62" t="n">
-        <v>0.4782608695652174</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="CK62" t="n">
         <v>0</v>
@@ -14992,10 +14992,10 @@
         <v>81</v>
       </c>
       <c r="DK62" t="n">
-        <v>421</v>
+        <v>385</v>
       </c>
       <c r="DL62" t="n">
-        <v>5.197530864197531</v>
+        <v>4.753086419753086</v>
       </c>
     </row>
     <row r="63">
@@ -15049,28 +15049,28 @@
         <v>8</v>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M63" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N63" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P63" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Q63" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S63" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
@@ -15125,7 +15125,7 @@
         <v>17</v>
       </c>
       <c r="BB63" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="BC63" t="inlineStr"/>
       <c r="BD63" t="inlineStr"/>
@@ -15155,31 +15155,31 @@
         <v>0</v>
       </c>
       <c r="CB63" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="CC63" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="CD63" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="CE63" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="CF63" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="CG63" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="CH63" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="CI63" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="CJ63" t="n">
         <v>0.05882352941176471</v>
-      </c>
-      <c r="CC63" t="n">
-        <v>0.4705882352941176</v>
-      </c>
-      <c r="CD63" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="CE63" t="n">
-        <v>0.2941176470588235</v>
-      </c>
-      <c r="CF63" t="n">
-        <v>0.2941176470588235</v>
-      </c>
-      <c r="CG63" t="n">
-        <v>0.2352941176470588</v>
-      </c>
-      <c r="CH63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI63" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="CJ63" t="n">
-        <v>0.1111111111111111</v>
       </c>
       <c r="CK63" t="inlineStr"/>
       <c r="CL63" t="inlineStr"/>
@@ -15210,10 +15210,10 @@
         <v>84</v>
       </c>
       <c r="DK63" t="n">
-        <v>216</v>
+        <v>391</v>
       </c>
       <c r="DL63" t="n">
-        <v>2.571428571428572</v>
+        <v>4.654761904761905</v>
       </c>
     </row>
     <row r="64">
@@ -15267,31 +15267,31 @@
         <v>13</v>
       </c>
       <c r="L64" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M64" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N64" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O64" t="n">
+        <v>21</v>
+      </c>
+      <c r="P64" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>27</v>
+      </c>
+      <c r="R64" t="n">
         <v>16</v>
       </c>
-      <c r="P64" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>17</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7</v>
-      </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="T64" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
@@ -15349,7 +15349,7 @@
         <v>40</v>
       </c>
       <c r="BB64" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BC64" t="n">
         <v>5</v>
@@ -15383,31 +15383,31 @@
         <v>6</v>
       </c>
       <c r="CB64" t="n">
-        <v>0.175</v>
+        <v>0.35</v>
       </c>
       <c r="CC64" t="n">
-        <v>0.575</v>
+        <v>0.625</v>
       </c>
       <c r="CD64" t="n">
-        <v>0.375</v>
+        <v>0.35</v>
       </c>
       <c r="CE64" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="CF64" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="CG64" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="CH64" t="n">
         <v>0.4</v>
       </c>
-      <c r="CF64" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="CG64" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="CH64" t="n">
-        <v>0.175</v>
-      </c>
       <c r="CI64" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="CJ64" t="n">
-        <v>0.375</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CK64" t="n">
         <v>0</v>
@@ -15444,10 +15444,10 @@
         <v>165</v>
       </c>
       <c r="DK64" t="n">
-        <v>637</v>
+        <v>776</v>
       </c>
       <c r="DL64" t="n">
-        <v>3.860606060606061</v>
+        <v>4.703030303030303</v>
       </c>
     </row>
     <row r="65">
@@ -15525,7 +15525,7 @@
         <v>12</v>
       </c>
       <c r="T65" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -15583,7 +15583,7 @@
         <v>20</v>
       </c>
       <c r="BB65" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="BC65" t="n">
         <v>1</v>
@@ -15641,7 +15641,7 @@
         <v>0.6</v>
       </c>
       <c r="CJ65" t="n">
-        <v>1.05</v>
+        <v>1.727272727272727</v>
       </c>
       <c r="CK65" t="n">
         <v>0</v>
@@ -15678,10 +15678,10 @@
         <v>103</v>
       </c>
       <c r="DK65" t="n">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="DL65" t="n">
-        <v>5.271844660194175</v>
+        <v>5.097087378640777</v>
       </c>
     </row>
     <row r="66">
@@ -15735,28 +15735,28 @@
         <v>10</v>
       </c>
       <c r="L66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M66" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N66" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O66" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="P66" t="n">
         <v>7</v>
       </c>
       <c r="Q66" t="n">
+        <v>4</v>
+      </c>
+      <c r="R66" t="n">
         <v>6</v>
       </c>
-      <c r="R66" t="n">
-        <v>3</v>
-      </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T66" t="n">
         <v>9</v>
@@ -15815,7 +15815,7 @@
         <v>20</v>
       </c>
       <c r="BB66" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="BC66" t="n">
         <v>4</v>
@@ -15847,31 +15847,31 @@
         <v>4</v>
       </c>
       <c r="CB66" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="CC66" t="n">
-        <v>0.15</v>
+        <v>0.65</v>
       </c>
       <c r="CD66" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="CE66" t="n">
-        <v>0.35</v>
+        <v>1.15</v>
       </c>
       <c r="CF66" t="n">
         <v>0.35</v>
       </c>
       <c r="CG66" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CH66" t="n">
         <v>0.3</v>
       </c>
-      <c r="CH66" t="n">
-        <v>0.15</v>
-      </c>
       <c r="CI66" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="CJ66" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.45</v>
       </c>
       <c r="CK66" t="n">
         <v>0.75</v>
@@ -15906,10 +15906,10 @@
         <v>94</v>
       </c>
       <c r="DK66" t="n">
-        <v>280</v>
+        <v>417</v>
       </c>
       <c r="DL66" t="n">
-        <v>2.978723404255319</v>
+        <v>4.436170212765957</v>
       </c>
     </row>
     <row r="67">
@@ -15963,31 +15963,31 @@
         <v>19</v>
       </c>
       <c r="L67" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="M67" t="n">
+        <v>26</v>
+      </c>
+      <c r="N67" t="n">
         <v>16</v>
       </c>
-      <c r="N67" t="n">
-        <v>11</v>
-      </c>
       <c r="O67" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="P67" t="n">
         <v>11</v>
       </c>
       <c r="Q67" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R67" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T67" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="U67" t="n">
         <v>3</v>
@@ -16045,7 +16045,7 @@
         <v>40</v>
       </c>
       <c r="BB67" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="BC67" t="n">
         <v>5</v>
@@ -16079,31 +16079,31 @@
         <v>6</v>
       </c>
       <c r="CB67" t="n">
-        <v>0.6</v>
+        <v>0.725</v>
       </c>
       <c r="CC67" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="CD67" t="n">
         <v>0.4</v>
       </c>
-      <c r="CD67" t="n">
-        <v>0.275</v>
-      </c>
       <c r="CE67" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="CF67" t="n">
         <v>0.275</v>
       </c>
       <c r="CG67" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="CH67" t="n">
-        <v>0.425</v>
+        <v>0.5</v>
       </c>
       <c r="CI67" t="n">
-        <v>0.375</v>
+        <v>0.45</v>
       </c>
       <c r="CJ67" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.9032258064516129</v>
       </c>
       <c r="CK67" t="n">
         <v>0.6</v>
@@ -16140,10 +16140,10 @@
         <v>197</v>
       </c>
       <c r="DK67" t="n">
-        <v>823</v>
+        <v>942</v>
       </c>
       <c r="DL67" t="n">
-        <v>4.177664974619289</v>
+        <v>4.781725888324873</v>
       </c>
     </row>
     <row r="68">
@@ -16221,7 +16221,7 @@
         <v>5</v>
       </c>
       <c r="T68" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U68" t="n">
         <v>7</v>
@@ -16277,7 +16277,7 @@
         <v>20</v>
       </c>
       <c r="BB68" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="BC68" t="n">
         <v>3</v>
@@ -16333,7 +16333,7 @@
         <v>0.25</v>
       </c>
       <c r="CJ68" t="n">
-        <v>0.6</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="CK68" t="n">
         <v>2.333333333333333</v>
@@ -16368,10 +16368,10 @@
         <v>70</v>
       </c>
       <c r="DK68" t="n">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="DL68" t="n">
-        <v>5.585714285714285</v>
+        <v>5.457142857142857</v>
       </c>
     </row>
     <row r="69">
@@ -16425,28 +16425,28 @@
         <v>8</v>
       </c>
       <c r="L69" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N69" t="n">
         <v>7</v>
       </c>
       <c r="O69" t="n">
+        <v>10</v>
+      </c>
+      <c r="P69" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>14</v>
+      </c>
+      <c r="R69" t="n">
+        <v>10</v>
+      </c>
+      <c r="S69" t="n">
         <v>5</v>
-      </c>
-      <c r="P69" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>5</v>
-      </c>
-      <c r="R69" t="n">
-        <v>8</v>
-      </c>
-      <c r="S69" t="n">
-        <v>6</v>
       </c>
       <c r="T69" t="n">
         <v>7</v>
@@ -16505,7 +16505,7 @@
         <v>17</v>
       </c>
       <c r="BB69" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="BC69" t="n">
         <v>1</v>
@@ -16537,31 +16537,31 @@
         <v>1</v>
       </c>
       <c r="CB69" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="CC69" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="CD69" t="n">
         <v>0.4117647058823529</v>
       </c>
       <c r="CE69" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="CF69" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="CG69" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="CH69" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="CI69" t="n">
         <v>0.2941176470588235</v>
       </c>
-      <c r="CF69" t="n">
-        <v>0.05882352941176471</v>
-      </c>
-      <c r="CG69" t="n">
-        <v>0.2941176470588235</v>
-      </c>
-      <c r="CH69" t="n">
-        <v>0.4705882352941176</v>
-      </c>
-      <c r="CI69" t="n">
-        <v>0.3529411764705883</v>
-      </c>
       <c r="CJ69" t="n">
-        <v>0.7</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="CK69" t="n">
         <v>1</v>
@@ -16596,10 +16596,10 @@
         <v>68</v>
       </c>
       <c r="DK69" t="n">
-        <v>258</v>
+        <v>362</v>
       </c>
       <c r="DL69" t="n">
-        <v>3.794117647058823</v>
+        <v>5.323529411764706</v>
       </c>
     </row>
     <row r="70">
@@ -16653,31 +16653,31 @@
         <v>16</v>
       </c>
       <c r="L70" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M70" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N70" t="n">
         <v>12</v>
       </c>
       <c r="O70" t="n">
+        <v>22</v>
+      </c>
+      <c r="P70" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q70" t="n">
         <v>17</v>
       </c>
-      <c r="P70" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>8</v>
-      </c>
       <c r="R70" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S70" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T70" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U70" t="n">
         <v>8</v>
@@ -16733,7 +16733,7 @@
         <v>37</v>
       </c>
       <c r="BB70" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BC70" t="n">
         <v>4</v>
@@ -16765,31 +16765,31 @@
         <v>4</v>
       </c>
       <c r="CB70" t="n">
-        <v>0.3783783783783784</v>
+        <v>0.4594594594594595</v>
       </c>
       <c r="CC70" t="n">
-        <v>0.08108108108108109</v>
+        <v>0.1621621621621622</v>
       </c>
       <c r="CD70" t="n">
         <v>0.3243243243243243</v>
       </c>
       <c r="CE70" t="n">
+        <v>0.5945945945945946</v>
+      </c>
+      <c r="CF70" t="n">
+        <v>0.2972972972972973</v>
+      </c>
+      <c r="CG70" t="n">
         <v>0.4594594594594595</v>
       </c>
-      <c r="CF70" t="n">
-        <v>0.2162162162162162</v>
-      </c>
-      <c r="CG70" t="n">
-        <v>0.2162162162162162</v>
-      </c>
       <c r="CH70" t="n">
-        <v>0.3783783783783784</v>
+        <v>0.4324324324324325</v>
       </c>
       <c r="CI70" t="n">
-        <v>0.2972972972972973</v>
+        <v>0.2702702702702703</v>
       </c>
       <c r="CJ70" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="CK70" t="n">
         <v>2</v>
@@ -16824,10 +16824,10 @@
         <v>138</v>
       </c>
       <c r="DK70" t="n">
-        <v>649</v>
+        <v>744</v>
       </c>
       <c r="DL70" t="n">
-        <v>4.702898550724638</v>
+        <v>5.391304347826087</v>
       </c>
     </row>
     <row r="71">
@@ -16901,7 +16901,7 @@
         <v>9</v>
       </c>
       <c r="T71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U71" t="n">
         <v>1</v>
@@ -16963,7 +16963,7 @@
         <v>20</v>
       </c>
       <c r="BB71" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="BC71" t="n">
         <v>2</v>
@@ -17025,7 +17025,7 @@
         <v>0.45</v>
       </c>
       <c r="CJ71" t="n">
-        <v>0.5</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="CK71" t="n">
         <v>0.5</v>
@@ -17066,10 +17066,10 @@
         <v>90</v>
       </c>
       <c r="DK71" t="n">
-        <v>529</v>
+        <v>511</v>
       </c>
       <c r="DL71" t="n">
-        <v>5.877777777777778</v>
+        <v>5.677777777777778</v>
       </c>
     </row>
     <row r="72">
@@ -17119,28 +17119,28 @@
         <v>9</v>
       </c>
       <c r="L72" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M72" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N72" t="n">
+        <v>6</v>
+      </c>
+      <c r="O72" t="n">
+        <v>16</v>
+      </c>
+      <c r="P72" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>10</v>
+      </c>
+      <c r="R72" t="n">
         <v>5</v>
       </c>
-      <c r="O72" t="n">
-        <v>3</v>
-      </c>
-      <c r="P72" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>4</v>
-      </c>
-      <c r="R72" t="n">
-        <v>2</v>
-      </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T72" t="n">
         <v>4</v>
@@ -17201,7 +17201,7 @@
         <v>20</v>
       </c>
       <c r="BB72" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="BC72" t="n">
         <v>4</v>
@@ -17235,31 +17235,31 @@
         <v>6</v>
       </c>
       <c r="CB72" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CC72" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CD72" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CE72" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CF72" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CG72" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CH72" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CI72" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CJ72" t="n">
         <v>0.2</v>
-      </c>
-      <c r="CC72" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="CD72" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="CE72" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="CF72" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="CG72" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="CH72" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="CI72" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="CJ72" t="n">
-        <v>0.3076923076923077</v>
       </c>
       <c r="CK72" t="n">
         <v>0.5</v>
@@ -17296,10 +17296,10 @@
         <v>78</v>
       </c>
       <c r="DK72" t="n">
-        <v>244</v>
+        <v>400</v>
       </c>
       <c r="DL72" t="n">
-        <v>3.128205128205128</v>
+        <v>5.128205128205129</v>
       </c>
     </row>
     <row r="73">
@@ -17349,31 +17349,31 @@
         <v>18</v>
       </c>
       <c r="L73" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M73" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O73" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="P73" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Q73" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R73" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T73" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="U73" t="n">
         <v>3</v>
@@ -17435,7 +17435,7 @@
         <v>40</v>
       </c>
       <c r="BB73" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="BC73" t="n">
         <v>6</v>
@@ -17473,31 +17473,31 @@
         <v>11</v>
       </c>
       <c r="CB73" t="n">
-        <v>0.325</v>
+        <v>0.425</v>
       </c>
       <c r="CC73" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="CD73" t="n">
-        <v>0.25</v>
+        <v>0.275</v>
       </c>
       <c r="CE73" t="n">
-        <v>0.2</v>
+        <v>0.525</v>
       </c>
       <c r="CF73" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="CG73" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="CH73" t="n">
-        <v>0.5</v>
+        <v>0.575</v>
       </c>
       <c r="CI73" t="n">
-        <v>0.375</v>
+        <v>0.425</v>
       </c>
       <c r="CJ73" t="n">
-        <v>0.4242424242424243</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="CK73" t="n">
         <v>0.5</v>
@@ -17538,10 +17538,10 @@
         <v>168</v>
       </c>
       <c r="DK73" t="n">
-        <v>773</v>
+        <v>911</v>
       </c>
       <c r="DL73" t="n">
-        <v>4.601190476190476</v>
+        <v>5.422619047619047</v>
       </c>
     </row>
     <row r="74">
@@ -17619,7 +17619,7 @@
         <v>11</v>
       </c>
       <c r="T74" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="U74" t="n">
         <v>1</v>
@@ -17677,7 +17677,7 @@
         <v>20</v>
       </c>
       <c r="BB74" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BC74" t="n">
         <v>3</v>
@@ -17735,7 +17735,7 @@
         <v>0.55</v>
       </c>
       <c r="CJ74" t="n">
-        <v>1.1</v>
+        <v>1.384615384615385</v>
       </c>
       <c r="CK74" t="n">
         <v>0.3333333333333333</v>
@@ -17772,10 +17772,10 @@
         <v>97</v>
       </c>
       <c r="DK74" t="n">
-        <v>534</v>
+        <v>498</v>
       </c>
       <c r="DL74" t="n">
-        <v>5.505154639175258</v>
+        <v>5.134020618556701</v>
       </c>
     </row>
     <row r="75">
@@ -17829,28 +17829,28 @@
         <v>5</v>
       </c>
       <c r="L75" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N75" t="n">
         <v>7</v>
       </c>
       <c r="O75" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P75" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q75" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R75" t="n">
         <v>3</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="T75" t="n">
         <v>5</v>
@@ -17909,7 +17909,7 @@
         <v>18</v>
       </c>
       <c r="BB75" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="BC75" t="n">
         <v>2</v>
@@ -17941,31 +17941,31 @@
         <v>2</v>
       </c>
       <c r="CB75" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="CC75" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="CD75" t="n">
         <v>0.3888888888888889</v>
       </c>
       <c r="CE75" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="CF75" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CG75" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.5</v>
       </c>
       <c r="CH75" t="n">
         <v>0.1666666666666667</v>
       </c>
       <c r="CI75" t="n">
-        <v>0.8333333333333334</v>
+        <v>1.055555555555556</v>
       </c>
       <c r="CJ75" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="CK75" t="n">
         <v>1</v>
@@ -18000,10 +18000,10 @@
         <v>72</v>
       </c>
       <c r="DK75" t="n">
-        <v>329</v>
+        <v>406</v>
       </c>
       <c r="DL75" t="n">
-        <v>4.569444444444445</v>
+        <v>5.638888888888889</v>
       </c>
     </row>
     <row r="76">
@@ -18057,31 +18057,31 @@
         <v>15</v>
       </c>
       <c r="L76" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M76" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N76" t="n">
         <v>7</v>
       </c>
       <c r="O76" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P76" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Q76" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R76" t="n">
         <v>6</v>
       </c>
       <c r="S76" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="T76" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="U76" t="n">
         <v>3</v>
@@ -18139,7 +18139,7 @@
         <v>38</v>
       </c>
       <c r="BB76" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="BC76" t="n">
         <v>5</v>
@@ -18173,31 +18173,31 @@
         <v>6</v>
       </c>
       <c r="CB76" t="n">
-        <v>0.4473684210526316</v>
+        <v>0.5</v>
       </c>
       <c r="CC76" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="CD76" t="n">
         <v>0.1842105263157895</v>
       </c>
       <c r="CE76" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="CF76" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.4473684210526316</v>
       </c>
       <c r="CG76" t="n">
-        <v>0.6052631578947368</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="CH76" t="n">
         <v>0.1578947368421053</v>
       </c>
       <c r="CI76" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="CJ76" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7419354838709677</v>
       </c>
       <c r="CK76" t="n">
         <v>0.6</v>
@@ -18234,10 +18234,10 @@
         <v>169</v>
       </c>
       <c r="DK76" t="n">
-        <v>863</v>
+        <v>904</v>
       </c>
       <c r="DL76" t="n">
-        <v>5.106508875739645</v>
+        <v>5.349112426035503</v>
       </c>
     </row>
     <row r="77">
@@ -18367,7 +18367,7 @@
         <v>20</v>
       </c>
       <c r="BB77" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="BC77" t="n">
         <v>2</v>
@@ -18423,7 +18423,7 @@
         <v>0.05</v>
       </c>
       <c r="CJ77" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="CK77" t="n">
         <v>1</v>
@@ -18511,28 +18511,28 @@
         <v>11</v>
       </c>
       <c r="L78" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M78" t="n">
         <v>6</v>
       </c>
       <c r="N78" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="O78" t="n">
         <v>7</v>
       </c>
       <c r="P78" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Q78" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="R78" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T78" t="n">
         <v>0</v>
@@ -18591,7 +18591,7 @@
         <v>18</v>
       </c>
       <c r="BB78" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="BC78" t="n">
         <v>2</v>
@@ -18623,28 +18623,28 @@
         <v>2</v>
       </c>
       <c r="CB78" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="CC78" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="CD78" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="CE78" t="n">
         <v>0.3888888888888889</v>
       </c>
       <c r="CF78" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="CG78" t="n">
-        <v>0.6111111111111112</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="CH78" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="CI78" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.5</v>
       </c>
       <c r="CJ78" t="n">
         <v>0</v>
@@ -18682,10 +18682,10 @@
         <v>95</v>
       </c>
       <c r="DK78" t="n">
-        <v>207</v>
+        <v>437</v>
       </c>
       <c r="DL78" t="n">
-        <v>2.178947368421053</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="79">
@@ -18735,28 +18735,28 @@
         <v>20</v>
       </c>
       <c r="L79" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M79" t="n">
         <v>13</v>
       </c>
       <c r="N79" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="O79" t="n">
         <v>10</v>
       </c>
       <c r="P79" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="Q79" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="R79" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="n">
         <v>15</v>
@@ -18847,28 +18847,28 @@
         <v>4</v>
       </c>
       <c r="CB79" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="CC79" t="n">
         <v>0.3421052631578947</v>
       </c>
       <c r="CD79" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="CE79" t="n">
         <v>0.2631578947368421</v>
       </c>
       <c r="CF79" t="n">
-        <v>0.5526315789473685</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="CG79" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="CH79" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.6052631578947368</v>
       </c>
       <c r="CI79" t="n">
-        <v>0.131578947368421</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="CJ79" t="n">
         <v>0.5357142857142857</v>
@@ -18906,10 +18906,10 @@
         <v>190</v>
       </c>
       <c r="DK79" t="n">
-        <v>666</v>
+        <v>896</v>
       </c>
       <c r="DL79" t="n">
-        <v>3.505263157894737</v>
+        <v>4.71578947368421</v>
       </c>
     </row>
     <row r="80">
@@ -18985,7 +18985,7 @@
         <v>9</v>
       </c>
       <c r="T80" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
@@ -19037,7 +19037,7 @@
         <v>19</v>
       </c>
       <c r="BB80" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="BC80" t="inlineStr"/>
       <c r="BD80" t="inlineStr"/>
@@ -19091,7 +19091,7 @@
         <v>0.4736842105263158</v>
       </c>
       <c r="CJ80" t="n">
-        <v>1</v>
+        <v>1.454545454545455</v>
       </c>
       <c r="CK80" t="inlineStr"/>
       <c r="CL80" t="inlineStr"/>
@@ -19122,10 +19122,10 @@
         <v>108</v>
       </c>
       <c r="DK80" t="n">
-        <v>523</v>
+        <v>496</v>
       </c>
       <c r="DL80" t="n">
-        <v>4.842592592592593</v>
+        <v>4.592592592592593</v>
       </c>
     </row>
     <row r="81">
@@ -19177,28 +19177,28 @@
         <v>13</v>
       </c>
       <c r="L81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M81" t="n">
         <v>7</v>
       </c>
       <c r="N81" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="O81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P81" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q81" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S81" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="T81" t="n">
         <v>8</v>
@@ -19261,7 +19261,7 @@
         <v>21</v>
       </c>
       <c r="BB81" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="BC81" t="n">
         <v>3</v>
@@ -19297,31 +19297,31 @@
         <v>6</v>
       </c>
       <c r="CB81" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CC81" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="CD81" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="CE81" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="CF81" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CG81" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CH81" t="n">
-        <v>0</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CI81" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="CJ81" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CK81" t="n">
         <v>0.3333333333333333</v>
@@ -19360,10 +19360,10 @@
         <v>96</v>
       </c>
       <c r="DK81" t="n">
-        <v>354</v>
+        <v>519</v>
       </c>
       <c r="DL81" t="n">
-        <v>3.6875</v>
+        <v>5.40625</v>
       </c>
     </row>
     <row r="82">
@@ -19415,31 +19415,31 @@
         <v>24</v>
       </c>
       <c r="L82" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M82" t="n">
         <v>23</v>
       </c>
       <c r="N82" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="O82" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P82" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q82" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="R82" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S82" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="T82" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="U82" t="n">
         <v>1</v>
@@ -19499,7 +19499,7 @@
         <v>40</v>
       </c>
       <c r="BB82" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC82" t="n">
         <v>3</v>
@@ -19535,31 +19535,31 @@
         <v>6</v>
       </c>
       <c r="CB82" t="n">
-        <v>0.625</v>
+        <v>0.65</v>
       </c>
       <c r="CC82" t="n">
         <v>0.575</v>
       </c>
       <c r="CD82" t="n">
-        <v>0.325</v>
+        <v>0.675</v>
       </c>
       <c r="CE82" t="n">
-        <v>0.45</v>
+        <v>0.425</v>
       </c>
       <c r="CF82" t="n">
-        <v>0.425</v>
+        <v>0.525</v>
       </c>
       <c r="CG82" t="n">
-        <v>0.425</v>
+        <v>0.55</v>
       </c>
       <c r="CH82" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="CI82" t="n">
-        <v>0.525</v>
+        <v>0.675</v>
       </c>
       <c r="CJ82" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="CK82" t="n">
         <v>0.3333333333333333</v>
@@ -19598,10 +19598,10 @@
         <v>204</v>
       </c>
       <c r="DK82" t="n">
-        <v>877</v>
+        <v>1015</v>
       </c>
       <c r="DL82" t="n">
-        <v>4.299019607843137</v>
+        <v>4.975490196078431</v>
       </c>
     </row>
     <row r="83">
@@ -19675,7 +19675,7 @@
         <v>7</v>
       </c>
       <c r="T83" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U83" t="inlineStr"/>
       <c r="V83" t="inlineStr"/>
@@ -19727,7 +19727,7 @@
         <v>20</v>
       </c>
       <c r="BB83" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="BC83" t="inlineStr"/>
       <c r="BD83" t="inlineStr"/>
@@ -19781,7 +19781,7 @@
         <v>0.35</v>
       </c>
       <c r="CJ83" t="n">
-        <v>0.35</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="CK83" t="inlineStr"/>
       <c r="CL83" t="inlineStr"/>
@@ -19812,10 +19812,10 @@
         <v>62</v>
       </c>
       <c r="DK83" t="n">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="DL83" t="n">
-        <v>4.887096774193548</v>
+        <v>4.596774193548387</v>
       </c>
     </row>
     <row r="84">
@@ -19865,28 +19865,28 @@
         <v>8</v>
       </c>
       <c r="L84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M84" t="n">
         <v>2</v>
       </c>
       <c r="N84" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O84" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R84" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="S84" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T84" t="n">
         <v>3</v>
@@ -19941,7 +19941,7 @@
         <v>19</v>
       </c>
       <c r="BB84" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="BC84" t="inlineStr"/>
       <c r="BD84" t="inlineStr"/>
@@ -19971,31 +19971,31 @@
         <v>0</v>
       </c>
       <c r="CB84" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="CC84" t="n">
         <v>0.1052631578947368</v>
       </c>
       <c r="CD84" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="CE84" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="CF84" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="CG84" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="CH84" t="n">
-        <v>0.1052631578947368</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="CI84" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="CJ84" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="CK84" t="inlineStr"/>
       <c r="CL84" t="inlineStr"/>
@@ -20026,10 +20026,10 @@
         <v>65</v>
       </c>
       <c r="DK84" t="n">
-        <v>194</v>
+        <v>301</v>
       </c>
       <c r="DL84" t="n">
-        <v>2.984615384615385</v>
+        <v>4.630769230769231</v>
       </c>
     </row>
     <row r="85">
@@ -20079,31 +20079,31 @@
         <v>15</v>
       </c>
       <c r="L85" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M85" t="n">
         <v>11</v>
       </c>
       <c r="N85" t="n">
+        <v>21</v>
+      </c>
+      <c r="O85" t="n">
+        <v>13</v>
+      </c>
+      <c r="P85" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>6</v>
+      </c>
+      <c r="R85" t="n">
+        <v>18</v>
+      </c>
+      <c r="S85" t="n">
         <v>17</v>
       </c>
-      <c r="O85" t="n">
-        <v>15</v>
-      </c>
-      <c r="P85" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>7</v>
-      </c>
-      <c r="R85" t="n">
+      <c r="T85" t="n">
         <v>8</v>
-      </c>
-      <c r="S85" t="n">
-        <v>14</v>
-      </c>
-      <c r="T85" t="n">
-        <v>10</v>
       </c>
       <c r="U85" t="inlineStr"/>
       <c r="V85" t="inlineStr"/>
@@ -20155,7 +20155,7 @@
         <v>39</v>
       </c>
       <c r="BB85" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="BC85" t="inlineStr"/>
       <c r="BD85" t="inlineStr"/>
@@ -20185,31 +20185,31 @@
         <v>0</v>
       </c>
       <c r="CB85" t="n">
-        <v>0.358974358974359</v>
+        <v>0.4871794871794872</v>
       </c>
       <c r="CC85" t="n">
         <v>0.282051282051282</v>
       </c>
       <c r="CD85" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="CE85" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CF85" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="CG85" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="CH85" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="CI85" t="n">
         <v>0.4358974358974359</v>
       </c>
-      <c r="CE85" t="n">
-        <v>0.3846153846153846</v>
-      </c>
-      <c r="CF85" t="n">
-        <v>0.2564102564102564</v>
-      </c>
-      <c r="CG85" t="n">
-        <v>0.1794871794871795</v>
-      </c>
-      <c r="CH85" t="n">
-        <v>0.2051282051282051</v>
-      </c>
-      <c r="CI85" t="n">
-        <v>0.358974358974359</v>
-      </c>
       <c r="CJ85" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CK85" t="inlineStr"/>
       <c r="CL85" t="inlineStr"/>
@@ -20240,10 +20240,10 @@
         <v>127</v>
       </c>
       <c r="DK85" t="n">
-        <v>497</v>
+        <v>586</v>
       </c>
       <c r="DL85" t="n">
-        <v>3.913385826771654</v>
+        <v>4.614173228346456</v>
       </c>
     </row>
     <row r="86">
@@ -20317,7 +20317,7 @@
         <v>10</v>
       </c>
       <c r="T86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U86" t="n">
         <v>1</v>
@@ -20377,7 +20377,7 @@
         <v>22</v>
       </c>
       <c r="BB86" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="BC86" t="n">
         <v>1</v>
@@ -20437,7 +20437,7 @@
         <v>0.4545454545454545</v>
       </c>
       <c r="CJ86" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="CK86" t="n">
         <v>1</v>
@@ -20476,10 +20476,10 @@
         <v>92</v>
       </c>
       <c r="DK86" t="n">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="DL86" t="n">
-        <v>4.760869565217392</v>
+        <v>4.565217391304348</v>
       </c>
     </row>
     <row r="87">
@@ -20532,25 +20532,25 @@
         <v>5</v>
       </c>
       <c r="M87" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N87" t="n">
+        <v>5</v>
+      </c>
+      <c r="O87" t="n">
         <v>6</v>
-      </c>
-      <c r="O87" t="n">
-        <v>1</v>
       </c>
       <c r="P87" t="n">
         <v>6</v>
       </c>
       <c r="Q87" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R87" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="S87" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T87" t="n">
         <v>0</v>
@@ -20605,7 +20605,7 @@
         <v>17</v>
       </c>
       <c r="BB87" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="BC87" t="inlineStr"/>
       <c r="BD87" t="inlineStr"/>
@@ -20638,25 +20638,25 @@
         <v>0.2941176470588235</v>
       </c>
       <c r="CC87" t="n">
-        <v>0.7058823529411765</v>
+        <v>1.058823529411765</v>
       </c>
       <c r="CD87" t="n">
+        <v>0.2941176470588235</v>
+      </c>
+      <c r="CE87" t="n">
         <v>0.3529411764705883</v>
-      </c>
-      <c r="CE87" t="n">
-        <v>0.05882352941176471</v>
       </c>
       <c r="CF87" t="n">
         <v>0.3529411764705883</v>
       </c>
       <c r="CG87" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="CH87" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="CI87" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="CJ87" t="n">
         <v>0</v>
@@ -20690,10 +20690,10 @@
         <v>73</v>
       </c>
       <c r="DK87" t="n">
-        <v>172</v>
+        <v>346</v>
       </c>
       <c r="DL87" t="n">
-        <v>2.356164383561644</v>
+        <v>4.739726027397261</v>
       </c>
     </row>
     <row r="88">
@@ -20746,28 +20746,28 @@
         <v>14</v>
       </c>
       <c r="M88" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N88" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O88" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="P88" t="n">
         <v>19</v>
       </c>
       <c r="Q88" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="R88" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="S88" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="T88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U88" t="n">
         <v>1</v>
@@ -20827,7 +20827,7 @@
         <v>39</v>
       </c>
       <c r="BB88" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="BC88" t="n">
         <v>1</v>
@@ -20866,28 +20866,28 @@
         <v>0.358974358974359</v>
       </c>
       <c r="CC88" t="n">
-        <v>0.6410256410256411</v>
+        <v>0.7948717948717948</v>
       </c>
       <c r="CD88" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.4358974358974359</v>
       </c>
       <c r="CE88" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.358974358974359</v>
       </c>
       <c r="CF88" t="n">
         <v>0.4871794871794872</v>
       </c>
       <c r="CG88" t="n">
-        <v>0.358974358974359</v>
+        <v>0.4871794871794872</v>
       </c>
       <c r="CH88" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="CI88" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.5641025641025641</v>
       </c>
       <c r="CJ88" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="CK88" t="n">
         <v>1</v>
@@ -20926,10 +20926,10 @@
         <v>165</v>
       </c>
       <c r="DK88" t="n">
-        <v>610</v>
+        <v>766</v>
       </c>
       <c r="DL88" t="n">
-        <v>3.696969696969697</v>
+        <v>4.642424242424243</v>
       </c>
     </row>
     <row r="89">
@@ -21003,7 +21003,7 @@
         <v>8</v>
       </c>
       <c r="T89" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U89" t="inlineStr"/>
       <c r="V89" t="inlineStr"/>
@@ -21055,7 +21055,7 @@
         <v>21</v>
       </c>
       <c r="BB89" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="BC89" t="inlineStr"/>
       <c r="BD89" t="inlineStr"/>
@@ -21109,7 +21109,7 @@
         <v>0.3809523809523809</v>
       </c>
       <c r="CJ89" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="CK89" t="inlineStr"/>
       <c r="CL89" t="inlineStr"/>
@@ -21140,10 +21140,10 @@
         <v>95</v>
       </c>
       <c r="DK89" t="n">
-        <v>468</v>
+        <v>441</v>
       </c>
       <c r="DL89" t="n">
-        <v>4.926315789473684</v>
+        <v>4.642105263157895</v>
       </c>
     </row>
     <row r="90">
@@ -21193,28 +21193,28 @@
         <v>12</v>
       </c>
       <c r="L90" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M90" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N90" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O90" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="P90" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Q90" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R90" t="n">
         <v>3</v>
       </c>
       <c r="S90" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T90" t="n">
         <v>8</v>
@@ -21277,7 +21277,7 @@
         <v>18</v>
       </c>
       <c r="BB90" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="BC90" t="n">
         <v>3</v>
@@ -21313,31 +21313,31 @@
         <v>5</v>
       </c>
       <c r="CB90" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="CC90" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.5</v>
       </c>
       <c r="CD90" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CE90" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="CF90" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="CG90" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="CH90" t="n">
         <v>0.1666666666666667</v>
       </c>
       <c r="CI90" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.5</v>
       </c>
       <c r="CJ90" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="CK90" t="n">
         <v>0.6666666666666666</v>
@@ -21376,10 +21376,10 @@
         <v>77</v>
       </c>
       <c r="DK90" t="n">
-        <v>199</v>
+        <v>375</v>
       </c>
       <c r="DL90" t="n">
-        <v>2.584415584415584</v>
+        <v>4.87012987012987</v>
       </c>
     </row>
     <row r="91">
@@ -21429,31 +21429,31 @@
         <v>24</v>
       </c>
       <c r="L91" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="M91" t="n">
+        <v>26</v>
+      </c>
+      <c r="N91" t="n">
+        <v>10</v>
+      </c>
+      <c r="O91" t="n">
+        <v>25</v>
+      </c>
+      <c r="P91" t="n">
         <v>24</v>
       </c>
-      <c r="N91" t="n">
-        <v>8</v>
-      </c>
-      <c r="O91" t="n">
-        <v>19</v>
-      </c>
-      <c r="P91" t="n">
-        <v>17</v>
-      </c>
       <c r="Q91" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="R91" t="n">
         <v>19</v>
       </c>
       <c r="S91" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="T91" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="U91" t="n">
         <v>2</v>
@@ -21549,31 +21549,31 @@
         <v>5</v>
       </c>
       <c r="CB91" t="n">
-        <v>0.282051282051282</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="CC91" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CD91" t="n">
+        <v>0.2564102564102564</v>
+      </c>
+      <c r="CE91" t="n">
+        <v>0.6410256410256411</v>
+      </c>
+      <c r="CF91" t="n">
         <v>0.6153846153846154</v>
       </c>
-      <c r="CD91" t="n">
-        <v>0.2051282051282051</v>
-      </c>
-      <c r="CE91" t="n">
-        <v>0.4871794871794872</v>
-      </c>
-      <c r="CF91" t="n">
-        <v>0.4358974358974359</v>
-      </c>
       <c r="CG91" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="CH91" t="n">
         <v>0.4871794871794872</v>
       </c>
       <c r="CI91" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.4358974358974359</v>
       </c>
       <c r="CJ91" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="CK91" t="n">
         <v>0.6666666666666666</v>
@@ -21612,10 +21612,10 @@
         <v>172</v>
       </c>
       <c r="DK91" t="n">
-        <v>667</v>
+        <v>816</v>
       </c>
       <c r="DL91" t="n">
-        <v>3.877906976744186</v>
+        <v>4.744186046511628</v>
       </c>
     </row>
   </sheetData>

--- a/defense.xlsx
+++ b/defense.xlsx
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
         <v>11</v>
@@ -998,7 +998,7 @@
         <v>8</v>
       </c>
       <c r="M2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N2" t="n">
         <v>8</v>
@@ -1051,28 +1051,28 @@
         <v>3</v>
       </c>
       <c r="AT2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
         <v>11</v>
@@ -1107,28 +1107,28 @@
         <v>1</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.4</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.65</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.4</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.7</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CF2" t="n">
-        <v>1.1</v>
+        <v>1.047619047619048</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.4</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.5</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.4</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.181818181818182</v>
@@ -1163,13 +1163,13 @@
         <v>3</v>
       </c>
       <c r="DJ2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="DK2" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="DL2" t="n">
-        <v>5.12037037037037</v>
+        <v>5.091743119266055</v>
       </c>
     </row>
     <row r="3">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K4" t="n">
         <v>23</v>
@@ -1466,7 +1466,7 @@
         <v>23</v>
       </c>
       <c r="M4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N4" t="n">
         <v>18</v>
@@ -1523,28 +1523,28 @@
         <v>7</v>
       </c>
       <c r="AT4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB4" t="n">
         <v>31</v>
@@ -1583,28 +1583,28 @@
         <v>4</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.575</v>
+        <v>0.5609756097560976</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.8</v>
+        <v>0.8048780487804879</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.45</v>
+        <v>0.4390243902439024</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.575</v>
+        <v>0.5609756097560976</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.8</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.45</v>
+        <v>0.4390243902439024</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.55</v>
+        <v>0.5365853658536586</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.7</v>
+        <v>0.6829268292682927</v>
       </c>
       <c r="CJ4" t="n">
         <v>0.5483870967741935</v>
@@ -1643,13 +1643,13 @@
         <v>1.75</v>
       </c>
       <c r="DJ4" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="DK4" t="n">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="DL4" t="n">
-        <v>5.018099547511312</v>
+        <v>5.004504504504505</v>
       </c>
     </row>
     <row r="5">
@@ -1700,16 +1700,16 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M5" t="n">
         <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
         <v>15</v>
@@ -1718,7 +1718,7 @@
         <v>12</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R5" t="n">
         <v>5</v>
@@ -1759,31 +1759,31 @@
         <v>2</v>
       </c>
       <c r="AT5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC5" t="n">
         <v>2</v>
@@ -1815,31 +1815,31 @@
         <v>2</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.5</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="CK5" t="n">
         <v>1</v>
@@ -1871,13 +1871,13 @@
         <v>1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="DK5" t="n">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="DL5" t="n">
-        <v>4.826086956521739</v>
+        <v>4.739726027397261</v>
       </c>
     </row>
     <row r="6">
@@ -2162,16 +2162,16 @@
         <v>17</v>
       </c>
       <c r="K7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M7" t="n">
         <v>16</v>
       </c>
       <c r="N7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O7" t="n">
         <v>22</v>
@@ -2180,7 +2180,7 @@
         <v>30</v>
       </c>
       <c r="Q7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R7" t="n">
         <v>11</v>
@@ -2223,31 +2223,31 @@
         <v>3</v>
       </c>
       <c r="AT7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AU7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AV7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AW7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AX7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AY7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AZ7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BA7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BB7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BC7" t="n">
         <v>3</v>
@@ -2281,31 +2281,31 @@
         <v>4</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.625</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.45</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.55</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.75</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.4358974358974359</v>
+        <v>0.45</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.282051282051282</v>
+        <v>0.275</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.3</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.303030303030303</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="CK7" t="n">
         <v>0.6666666666666666</v>
@@ -2339,13 +2339,13 @@
         <v>0.75</v>
       </c>
       <c r="DJ7" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="DK7" t="n">
-        <v>738</v>
+        <v>751</v>
       </c>
       <c r="DL7" t="n">
-        <v>4.5</v>
+        <v>4.470238095238095</v>
       </c>
     </row>
     <row r="8">
@@ -2606,7 +2606,7 @@
         <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L9" t="n">
         <v>6</v>
@@ -2618,7 +2618,7 @@
         <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
         <v>6</v>
@@ -2633,7 +2633,7 @@
         <v>5</v>
       </c>
       <c r="T9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U9" t="n">
         <v>4</v>
@@ -2665,31 +2665,31 @@
         <v>4</v>
       </c>
       <c r="AT9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC9" t="n">
         <v>2</v>
@@ -2721,31 +2721,31 @@
         <v>2</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.3</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.55</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.2</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.05</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.3</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.2</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.35</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.25</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.35</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CK9" t="n">
         <v>2</v>
@@ -2777,13 +2777,13 @@
         <v>2</v>
       </c>
       <c r="DJ9" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="DK9" t="n">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="DL9" t="n">
-        <v>5.272727272727272</v>
+        <v>5.271186440677966</v>
       </c>
     </row>
     <row r="10">
@@ -2830,7 +2830,7 @@
         <v>26</v>
       </c>
       <c r="K10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L10" t="n">
         <v>19</v>
@@ -2842,7 +2842,7 @@
         <v>13</v>
       </c>
       <c r="O10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P10" t="n">
         <v>11</v>
@@ -2857,7 +2857,7 @@
         <v>19</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U10" t="n">
         <v>4</v>
@@ -2889,31 +2889,31 @@
         <v>4</v>
       </c>
       <c r="AT10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC10" t="n">
         <v>2</v>
@@ -2945,31 +2945,31 @@
         <v>2</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.475</v>
+        <v>0.4634146341463415</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.325</v>
+        <v>0.3170731707317073</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.325</v>
+        <v>0.3170731707317073</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.375</v>
+        <v>0.4390243902439024</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.275</v>
+        <v>0.2682926829268293</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.45</v>
+        <v>0.4390243902439024</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.35</v>
+        <v>0.3414634146341464</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.475</v>
+        <v>0.4634146341463415</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3103448275862069</v>
       </c>
       <c r="CK10" t="n">
         <v>2</v>
@@ -3001,13 +3001,13 @@
         <v>2</v>
       </c>
       <c r="DJ10" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="DK10" t="n">
-        <v>669</v>
+        <v>690</v>
       </c>
       <c r="DL10" t="n">
-        <v>4.847826086956522</v>
+        <v>4.859154929577465</v>
       </c>
     </row>
     <row r="11">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K12" t="n">
         <v>9</v>
@@ -3304,7 +3304,7 @@
         <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R12" t="n">
         <v>7</v>
@@ -3351,31 +3351,31 @@
         <v>4</v>
       </c>
       <c r="AT12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC12" t="n">
         <v>3</v>
@@ -3413,31 +3413,31 @@
         <v>6</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.25</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.3</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.5</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.45</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.5</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.8</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.35</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.9</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.25</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="CK12" t="n">
         <v>0.6666666666666666</v>
@@ -3475,13 +3475,13 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="DJ12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="DK12" t="n">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="DL12" t="n">
-        <v>5.677777777777778</v>
+        <v>5.681318681318682</v>
       </c>
     </row>
     <row r="13">
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K13" t="n">
         <v>13</v>
@@ -3550,7 +3550,7 @@
         <v>19</v>
       </c>
       <c r="Q13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R13" t="n">
         <v>15</v>
@@ -3597,31 +3597,31 @@
         <v>5</v>
       </c>
       <c r="AT13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AU13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AV13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AW13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AX13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AY13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AZ13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="BA13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="BB13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC13" t="n">
         <v>5</v>
@@ -3659,31 +3659,31 @@
         <v>8</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.358974358974359</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.358974358974359</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.358974358974359</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.2368421052631579</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.5</v>
+        <v>0.4871794871794872</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.6578947368421053</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.3947368421052632</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.5641025641025641</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="CK13" t="n">
         <v>0.6</v>
@@ -3721,13 +3721,13 @@
         <v>0.625</v>
       </c>
       <c r="DJ13" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="DK13" t="n">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="DL13" t="n">
-        <v>5.146666666666667</v>
+        <v>5.152317880794702</v>
       </c>
     </row>
     <row r="14">
@@ -3778,7 +3778,7 @@
         <v>12</v>
       </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L14" t="n">
         <v>11</v>
@@ -3793,10 +3793,10 @@
         <v>6</v>
       </c>
       <c r="P14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R14" t="n">
         <v>11</v>
@@ -3805,7 +3805,7 @@
         <v>8</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
         <v>2</v>
@@ -3839,31 +3839,31 @@
         <v>2</v>
       </c>
       <c r="AT14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC14" t="n">
         <v>2</v>
@@ -3897,31 +3897,31 @@
         <v>3</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.55</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.15</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="CD14" t="n">
-        <v>1</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.3</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.4</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.75</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.55</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.4</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.3</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CK14" t="n">
         <v>1</v>
@@ -3955,13 +3955,13 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="DJ14" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="DK14" t="n">
-        <v>419</v>
+        <v>454</v>
       </c>
       <c r="DL14" t="n">
-        <v>4.761363636363637</v>
+        <v>4.829787234042553</v>
       </c>
     </row>
     <row r="15">
@@ -4240,7 +4240,7 @@
         <v>18</v>
       </c>
       <c r="K16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L16" t="n">
         <v>21</v>
@@ -4255,10 +4255,10 @@
         <v>18</v>
       </c>
       <c r="P16" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R16" t="n">
         <v>22</v>
@@ -4267,7 +4267,7 @@
         <v>23</v>
       </c>
       <c r="T16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U16" t="n">
         <v>5</v>
@@ -4301,31 +4301,31 @@
         <v>5</v>
       </c>
       <c r="AT16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AU16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AV16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AW16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AX16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AY16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AZ16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BA16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BB16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC16" t="n">
         <v>4</v>
@@ -4359,31 +4359,31 @@
         <v>5</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.525</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.15</v>
       </c>
       <c r="CD16" t="n">
-        <v>0.717948717948718</v>
+        <v>0.7</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.45</v>
       </c>
       <c r="CF16" t="n">
-        <v>0.4358974358974359</v>
+        <v>0.525</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.6</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.55</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.575</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0.2068965517241379</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="CK16" t="n">
         <v>1.25</v>
@@ -4417,13 +4417,13 @@
         <v>1</v>
       </c>
       <c r="DJ16" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="DK16" t="n">
-        <v>854</v>
+        <v>889</v>
       </c>
       <c r="DL16" t="n">
-        <v>5.023529411764706</v>
+        <v>5.051136363636363</v>
       </c>
     </row>
     <row r="17">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K17" t="n">
         <v>9</v>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M17" t="n">
         <v>5</v>
@@ -4529,28 +4529,28 @@
         <v>7</v>
       </c>
       <c r="AT17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB17" t="n">
         <v>11</v>
@@ -4585,28 +4585,28 @@
         <v>4</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="CF17" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="CJ17" t="n">
         <v>0.3636363636363636</v>
@@ -4641,13 +4641,13 @@
         <v>1.75</v>
       </c>
       <c r="DJ17" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="DK17" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="DL17" t="n">
-        <v>5.68</v>
+        <v>5.618421052631579</v>
       </c>
     </row>
     <row r="18">
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K19" t="n">
         <v>21</v>
       </c>
       <c r="L19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M19" t="n">
         <v>23</v>
@@ -4985,28 +4985,28 @@
         <v>8</v>
       </c>
       <c r="AT19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AU19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AV19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AW19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AX19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AY19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AZ19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BA19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BB19" t="n">
         <v>33</v>
@@ -5043,28 +5043,28 @@
         <v>6</v>
       </c>
       <c r="CB19" t="n">
-        <v>0.4358974358974359</v>
+        <v>0.45</v>
       </c>
       <c r="CC19" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.575</v>
       </c>
       <c r="CD19" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4</v>
       </c>
       <c r="CE19" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.675</v>
       </c>
       <c r="CF19" t="n">
-        <v>0.358974358974359</v>
+        <v>0.35</v>
       </c>
       <c r="CG19" t="n">
-        <v>0.4358974358974359</v>
+        <v>0.425</v>
       </c>
       <c r="CH19" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.65</v>
       </c>
       <c r="CI19" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.675</v>
       </c>
       <c r="CJ19" t="n">
         <v>0.2121212121212121</v>
@@ -5101,13 +5101,13 @@
         <v>1.333333333333333</v>
       </c>
       <c r="DJ19" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="DK19" t="n">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="DL19" t="n">
-        <v>5.070652173913044</v>
+        <v>5.048648648648649</v>
       </c>
     </row>
     <row r="20">
@@ -5158,7 +5158,7 @@
         <v>10</v>
       </c>
       <c r="K20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L20" t="n">
         <v>5</v>
@@ -5167,13 +5167,13 @@
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
         <v>7</v>
       </c>
       <c r="P20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q20" t="n">
         <v>5</v>
@@ -5219,31 +5219,31 @@
         <v>1</v>
       </c>
       <c r="AT20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC20" t="n">
         <v>1</v>
@@ -5277,31 +5277,31 @@
         <v>2</v>
       </c>
       <c r="CB20" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="CC20" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="CD20" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="CE20" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="CF20" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="CG20" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="CH20" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="CI20" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="CJ20" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1</v>
       </c>
       <c r="CK20" t="n">
         <v>0</v>
@@ -5335,13 +5335,13 @@
         <v>0.5</v>
       </c>
       <c r="DJ20" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="DK20" t="n">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="DL20" t="n">
-        <v>5.090909090909091</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="21">
@@ -5620,7 +5620,7 @@
         <v>21</v>
       </c>
       <c r="K22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L22" t="n">
         <v>18</v>
@@ -5629,13 +5629,13 @@
         <v>9</v>
       </c>
       <c r="N22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O22" t="n">
         <v>28</v>
       </c>
       <c r="P22" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q22" t="n">
         <v>33</v>
@@ -5681,31 +5681,31 @@
         <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AU22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AV22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AW22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AX22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AY22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AZ22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="BA22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="BB22" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BC22" t="n">
         <v>3</v>
@@ -5739,31 +5739,31 @@
         <v>4</v>
       </c>
       <c r="CB22" t="n">
-        <v>0.4390243902439024</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CC22" t="n">
-        <v>0.2195121951219512</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="CD22" t="n">
-        <v>0.1219512195121951</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="CE22" t="n">
-        <v>0.6829268292682927</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CF22" t="n">
-        <v>0.5609756097560976</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="CG22" t="n">
-        <v>0.8048780487804879</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="CH22" t="n">
-        <v>0.3414634146341464</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CI22" t="n">
-        <v>0.6585365853658537</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="CJ22" t="n">
-        <v>0.1875</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="CK22" t="n">
         <v>1</v>
@@ -5797,13 +5797,13 @@
         <v>1</v>
       </c>
       <c r="DJ22" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="DK22" t="n">
-        <v>885</v>
+        <v>908</v>
       </c>
       <c r="DL22" t="n">
-        <v>5.145348837209302</v>
+        <v>5.129943502824859</v>
       </c>
     </row>
     <row r="23">
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K24" t="n">
         <v>16</v>
@@ -6081,10 +6081,10 @@
         <v>10</v>
       </c>
       <c r="N24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P24" t="n">
         <v>12</v>
@@ -6131,31 +6131,31 @@
         <v>1</v>
       </c>
       <c r="AT24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC24" t="n">
         <v>1</v>
@@ -6187,31 +6187,31 @@
         <v>1</v>
       </c>
       <c r="CB24" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="CC24" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="CD24" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="CE24" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="CF24" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="CG24" t="n">
-        <v>0.3181818181818182</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="CH24" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="CI24" t="n">
-        <v>0.7727272727272727</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="CJ24" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="CK24" t="n">
         <v>1</v>
@@ -6243,13 +6243,13 @@
         <v>1</v>
       </c>
       <c r="DJ24" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="DK24" t="n">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="DL24" t="n">
-        <v>4.787878787878788</v>
+        <v>4.745098039215686</v>
       </c>
     </row>
     <row r="25">
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K25" t="n">
         <v>22</v>
@@ -6309,10 +6309,10 @@
         <v>14</v>
       </c>
       <c r="N25" t="n">
+        <v>21</v>
+      </c>
+      <c r="O25" t="n">
         <v>19</v>
-      </c>
-      <c r="O25" t="n">
-        <v>18</v>
       </c>
       <c r="P25" t="n">
         <v>17</v>
@@ -6359,31 +6359,31 @@
         <v>1</v>
       </c>
       <c r="AT25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AU25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AV25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AW25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AX25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AY25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AZ25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BA25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BB25" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BC25" t="n">
         <v>1</v>
@@ -6415,31 +6415,31 @@
         <v>1</v>
       </c>
       <c r="CB25" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.55</v>
       </c>
       <c r="CC25" t="n">
-        <v>0.358974358974359</v>
+        <v>0.35</v>
       </c>
       <c r="CD25" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.525</v>
       </c>
       <c r="CE25" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.475</v>
       </c>
       <c r="CF25" t="n">
-        <v>0.4358974358974359</v>
+        <v>0.425</v>
       </c>
       <c r="CG25" t="n">
-        <v>0.2051282051282051</v>
+        <v>0.2</v>
       </c>
       <c r="CH25" t="n">
-        <v>0.717948717948718</v>
+        <v>0.7</v>
       </c>
       <c r="CI25" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.675</v>
       </c>
       <c r="CJ25" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="CK25" t="n">
         <v>1</v>
@@ -6471,13 +6471,13 @@
         <v>1</v>
       </c>
       <c r="DJ25" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="DK25" t="n">
-        <v>797</v>
+        <v>807</v>
       </c>
       <c r="DL25" t="n">
-        <v>4.919753086419753</v>
+        <v>4.890909090909091</v>
       </c>
     </row>
     <row r="26">
@@ -6524,13 +6524,13 @@
         <v>13</v>
       </c>
       <c r="K26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L26" t="n">
         <v>12</v>
       </c>
       <c r="M26" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N26" t="n">
         <v>6</v>
@@ -6542,10 +6542,10 @@
         <v>3</v>
       </c>
       <c r="Q26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S26" t="n">
         <v>7</v>
@@ -6587,31 +6587,31 @@
         <v>7</v>
       </c>
       <c r="AT26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC26" t="n">
         <v>2</v>
@@ -6647,31 +6647,31 @@
         <v>4</v>
       </c>
       <c r="CB26" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="CC26" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="CD26" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="CE26" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="CF26" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.1304347826086956</v>
       </c>
       <c r="CG26" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="CH26" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="CI26" t="n">
-        <v>0.3181818181818182</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="CJ26" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="CK26" t="n">
         <v>0.5</v>
@@ -6707,13 +6707,13 @@
         <v>1.75</v>
       </c>
       <c r="DJ26" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="DK26" t="n">
-        <v>463</v>
+        <v>488</v>
       </c>
       <c r="DL26" t="n">
-        <v>5.087912087912088</v>
+        <v>5.030927835051546</v>
       </c>
     </row>
     <row r="27">
@@ -6984,13 +6984,13 @@
         <v>19</v>
       </c>
       <c r="K28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L28" t="n">
         <v>23</v>
       </c>
       <c r="M28" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N28" t="n">
         <v>15</v>
@@ -7002,10 +7002,10 @@
         <v>14</v>
       </c>
       <c r="Q28" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -7047,31 +7047,31 @@
         <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB28" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BC28" t="n">
         <v>4</v>
@@ -7107,31 +7107,31 @@
         <v>6</v>
       </c>
       <c r="CB28" t="n">
-        <v>0.575</v>
+        <v>0.5609756097560976</v>
       </c>
       <c r="CC28" t="n">
-        <v>0.575</v>
+        <v>0.6341463414634146</v>
       </c>
       <c r="CD28" t="n">
-        <v>0.375</v>
+        <v>0.3658536585365854</v>
       </c>
       <c r="CE28" t="n">
-        <v>0.45</v>
+        <v>0.4390243902439024</v>
       </c>
       <c r="CF28" t="n">
-        <v>0.35</v>
+        <v>0.3414634146341464</v>
       </c>
       <c r="CG28" t="n">
-        <v>0.375</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="CH28" t="n">
-        <v>0.55</v>
+        <v>0.5609756097560976</v>
       </c>
       <c r="CI28" t="n">
-        <v>0.5</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="CJ28" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="CK28" t="n">
         <v>0.25</v>
@@ -7167,13 +7167,13 @@
         <v>1.166666666666667</v>
       </c>
       <c r="DJ28" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="DK28" t="n">
-        <v>894</v>
+        <v>919</v>
       </c>
       <c r="DL28" t="n">
-        <v>5.050847457627119</v>
+        <v>5.021857923497268</v>
       </c>
     </row>
     <row r="29">
@@ -7449,7 +7449,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K30" t="n">
         <v>13</v>
@@ -7461,22 +7461,22 @@
         <v>9</v>
       </c>
       <c r="N30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O30" t="n">
         <v>16</v>
       </c>
       <c r="P30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R30" t="n">
         <v>20</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T30" t="n">
         <v>2</v>
@@ -7513,31 +7513,31 @@
         <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC30" t="n">
         <v>1</v>
@@ -7571,31 +7571,31 @@
         <v>2</v>
       </c>
       <c r="CB30" t="n">
-        <v>0.65</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CC30" t="n">
-        <v>0.45</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CD30" t="n">
-        <v>0.55</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="CE30" t="n">
-        <v>0.8</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="CF30" t="n">
-        <v>0.35</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CG30" t="n">
-        <v>0.75</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="CH30" t="n">
-        <v>1</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="CI30" t="n">
-        <v>0.75</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="CJ30" t="n">
-        <v>0.1</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="CK30" t="n">
         <v>0</v>
@@ -7629,13 +7629,13 @@
         <v>0</v>
       </c>
       <c r="DJ30" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="DK30" t="n">
-        <v>531</v>
+        <v>553</v>
       </c>
       <c r="DL30" t="n">
-        <v>4.916666666666667</v>
+        <v>4.9375</v>
       </c>
     </row>
     <row r="31">
@@ -7683,7 +7683,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K31" t="n">
         <v>23</v>
@@ -7695,22 +7695,22 @@
         <v>17</v>
       </c>
       <c r="N31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O31" t="n">
         <v>28</v>
       </c>
       <c r="P31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R31" t="n">
         <v>32</v>
       </c>
       <c r="S31" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T31" t="n">
         <v>11</v>
@@ -7747,31 +7747,31 @@
         <v>6</v>
       </c>
       <c r="AT31" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU31" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV31" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW31" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX31" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY31" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ31" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA31" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB31" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BC31" t="n">
         <v>3</v>
@@ -7805,31 +7805,31 @@
         <v>4</v>
       </c>
       <c r="CB31" t="n">
-        <v>0.375</v>
+        <v>0.3658536585365854</v>
       </c>
       <c r="CC31" t="n">
-        <v>0.425</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="CD31" t="n">
-        <v>0.525</v>
+        <v>0.5365853658536586</v>
       </c>
       <c r="CE31" t="n">
-        <v>0.7</v>
+        <v>0.6829268292682927</v>
       </c>
       <c r="CF31" t="n">
-        <v>0.375</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="CG31" t="n">
-        <v>0.575</v>
+        <v>0.5853658536585366</v>
       </c>
       <c r="CH31" t="n">
-        <v>0.8</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="CI31" t="n">
-        <v>0.775</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="CJ31" t="n">
-        <v>0.3666666666666666</v>
+        <v>0.3548387096774194</v>
       </c>
       <c r="CK31" t="n">
         <v>2</v>
@@ -7863,13 +7863,13 @@
         <v>1.5</v>
       </c>
       <c r="DJ31" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="DK31" t="n">
-        <v>1068</v>
+        <v>1090</v>
       </c>
       <c r="DL31" t="n">
-        <v>5.287128712871287</v>
+        <v>5.29126213592233</v>
       </c>
     </row>
     <row r="32">
@@ -8154,7 +8154,7 @@
         <v>13</v>
       </c>
       <c r="K33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L33" t="n">
         <v>11</v>
@@ -8163,7 +8163,7 @@
         <v>4</v>
       </c>
       <c r="N33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O33" t="n">
         <v>7</v>
@@ -8172,7 +8172,7 @@
         <v>8</v>
       </c>
       <c r="Q33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R33" t="n">
         <v>8</v>
@@ -8215,31 +8215,31 @@
         <v>2</v>
       </c>
       <c r="AT33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC33" t="n">
         <v>1</v>
@@ -8273,31 +8273,31 @@
         <v>2</v>
       </c>
       <c r="CB33" t="n">
-        <v>0.4782608695652174</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="CC33" t="n">
-        <v>0.1739130434782609</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="CD33" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.375</v>
       </c>
       <c r="CE33" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="CF33" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CG33" t="n">
-        <v>0.391304347826087</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="CH33" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CI33" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CJ33" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="CK33" t="n">
         <v>1</v>
@@ -8331,13 +8331,13 @@
         <v>1</v>
       </c>
       <c r="DJ33" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="DK33" t="n">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="DL33" t="n">
-        <v>5.32051282051282</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="34">
@@ -8388,7 +8388,7 @@
         <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L34" t="n">
         <v>21</v>
@@ -8397,7 +8397,7 @@
         <v>15</v>
       </c>
       <c r="N34" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O34" t="n">
         <v>10</v>
@@ -8406,7 +8406,7 @@
         <v>25</v>
       </c>
       <c r="Q34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R34" t="n">
         <v>24</v>
@@ -8449,31 +8449,31 @@
         <v>6</v>
       </c>
       <c r="AT34" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AU34" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AV34" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AW34" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AX34" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AY34" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AZ34" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BA34" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BB34" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BC34" t="n">
         <v>4</v>
@@ -8507,31 +8507,31 @@
         <v>6</v>
       </c>
       <c r="CB34" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.525</v>
       </c>
       <c r="CC34" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.375</v>
       </c>
       <c r="CD34" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.475</v>
       </c>
       <c r="CE34" t="n">
-        <v>0.2564102564102564</v>
+        <v>0.25</v>
       </c>
       <c r="CF34" t="n">
-        <v>0.6410256410256411</v>
+        <v>0.625</v>
       </c>
       <c r="CG34" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.4</v>
       </c>
       <c r="CH34" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.6</v>
       </c>
       <c r="CI34" t="n">
-        <v>0.8205128205128205</v>
+        <v>0.8</v>
       </c>
       <c r="CJ34" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3235294117647059</v>
       </c>
       <c r="CK34" t="n">
         <v>1.25</v>
@@ -8565,13 +8565,13 @@
         <v>1</v>
       </c>
       <c r="DJ34" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="DK34" t="n">
-        <v>944</v>
+        <v>953</v>
       </c>
       <c r="DL34" t="n">
-        <v>5.244444444444444</v>
+        <v>5.236263736263736</v>
       </c>
     </row>
     <row r="35">
@@ -8850,7 +8850,7 @@
         <v>7</v>
       </c>
       <c r="K36" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L36" t="n">
         <v>14</v>
@@ -8862,13 +8862,13 @@
         <v>11</v>
       </c>
       <c r="O36" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P36" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R36" t="n">
         <v>19</v>
@@ -8909,31 +8909,31 @@
         <v>3</v>
       </c>
       <c r="AT36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC36" t="n">
         <v>2</v>
@@ -8965,31 +8965,31 @@
         <v>2</v>
       </c>
       <c r="CB36" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="CC36" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="CD36" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5</v>
       </c>
       <c r="CE36" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="CF36" t="n">
-        <v>1.571428571428571</v>
+        <v>1.545454545454545</v>
       </c>
       <c r="CG36" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="CH36" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="CI36" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="CJ36" t="n">
-        <v>0.09523809523809523</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="CK36" t="n">
         <v>1.5</v>
@@ -9021,13 +9021,13 @@
         <v>1.5</v>
       </c>
       <c r="DJ36" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="DK36" t="n">
-        <v>543</v>
+        <v>566</v>
       </c>
       <c r="DL36" t="n">
-        <v>4.721739130434782</v>
+        <v>4.716666666666667</v>
       </c>
     </row>
     <row r="37">
@@ -9078,7 +9078,7 @@
         <v>16</v>
       </c>
       <c r="K37" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L37" t="n">
         <v>24</v>
@@ -9090,13 +9090,13 @@
         <v>31</v>
       </c>
       <c r="O37" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="P37" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R37" t="n">
         <v>33</v>
@@ -9137,31 +9137,31 @@
         <v>6</v>
       </c>
       <c r="AT37" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU37" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV37" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW37" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX37" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY37" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ37" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA37" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB37" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BC37" t="n">
         <v>3</v>
@@ -9193,31 +9193,31 @@
         <v>3</v>
       </c>
       <c r="CB37" t="n">
-        <v>0.6</v>
+        <v>0.5853658536585366</v>
       </c>
       <c r="CC37" t="n">
-        <v>0.5</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="CD37" t="n">
-        <v>0.775</v>
+        <v>0.7560975609756098</v>
       </c>
       <c r="CE37" t="n">
-        <v>0.55</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="CF37" t="n">
-        <v>1.225</v>
+        <v>1.219512195121951</v>
       </c>
       <c r="CG37" t="n">
-        <v>0.225</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="CH37" t="n">
-        <v>0.825</v>
+        <v>0.8048780487804879</v>
       </c>
       <c r="CI37" t="n">
-        <v>0.4</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="CJ37" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.21875</v>
       </c>
       <c r="CK37" t="n">
         <v>2</v>
@@ -9249,13 +9249,13 @@
         <v>2</v>
       </c>
       <c r="DJ37" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="DK37" t="n">
-        <v>1026</v>
+        <v>1049</v>
       </c>
       <c r="DL37" t="n">
-        <v>4.56</v>
+        <v>4.560869565217391</v>
       </c>
     </row>
     <row r="38">
@@ -9537,13 +9537,13 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K39" t="n">
         <v>15</v>
       </c>
       <c r="L39" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M39" t="n">
         <v>12</v>
@@ -9599,31 +9599,31 @@
         <v>4</v>
       </c>
       <c r="AT39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC39" t="n">
         <v>2</v>
@@ -9655,31 +9655,31 @@
         <v>2</v>
       </c>
       <c r="CB39" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="CC39" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="CD39" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="CE39" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="CF39" t="n">
-        <v>0.8636363636363636</v>
+        <v>0.8260869565217391</v>
       </c>
       <c r="CG39" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="CH39" t="n">
-        <v>0.7727272727272727</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="CI39" t="n">
-        <v>0.8636363636363636</v>
+        <v>0.8260869565217391</v>
       </c>
       <c r="CJ39" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="CK39" t="n">
         <v>2</v>
@@ -9711,13 +9711,13 @@
         <v>2</v>
       </c>
       <c r="DJ39" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="DK39" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="DL39" t="n">
-        <v>5.386363636363637</v>
+        <v>5.353383458646617</v>
       </c>
     </row>
     <row r="40">
@@ -9765,13 +9765,13 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K40" t="n">
         <v>25</v>
       </c>
       <c r="L40" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M40" t="n">
         <v>17</v>
@@ -9829,31 +9829,31 @@
         <v>8</v>
       </c>
       <c r="AT40" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU40" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV40" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW40" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX40" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY40" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ40" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA40" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB40" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BC40" t="n">
         <v>5</v>
@@ -9887,31 +9887,31 @@
         <v>6</v>
       </c>
       <c r="CB40" t="n">
-        <v>0.45</v>
+        <v>0.4634146341463415</v>
       </c>
       <c r="CC40" t="n">
-        <v>0.425</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="CD40" t="n">
-        <v>0.525</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="CE40" t="n">
-        <v>0.425</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="CF40" t="n">
-        <v>0.6</v>
+        <v>0.5853658536585366</v>
       </c>
       <c r="CG40" t="n">
-        <v>0.5</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="CH40" t="n">
-        <v>0.675</v>
+        <v>0.6585365853658537</v>
       </c>
       <c r="CI40" t="n">
-        <v>0.725</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="CJ40" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5142857142857142</v>
       </c>
       <c r="CK40" t="n">
         <v>1.6</v>
@@ -9945,13 +9945,13 @@
         <v>1.333333333333333</v>
       </c>
       <c r="DJ40" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="DK40" t="n">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="DL40" t="n">
-        <v>5.43</v>
+        <v>5.407960199004975</v>
       </c>
     </row>
     <row r="41">
@@ -10230,7 +10230,7 @@
         <v>7</v>
       </c>
       <c r="K42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L42" t="n">
         <v>8</v>
@@ -10254,7 +10254,7 @@
         <v>3</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T42" t="n">
         <v>6</v>
@@ -10291,31 +10291,31 @@
         <v>3</v>
       </c>
       <c r="AT42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC42" t="n">
         <v>2</v>
@@ -10349,31 +10349,31 @@
         <v>3</v>
       </c>
       <c r="CB42" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="CC42" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CD42" t="n">
-        <v>1.117647058823529</v>
+        <v>1.055555555555556</v>
       </c>
       <c r="CE42" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="CF42" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="CG42" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="CH42" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="CI42" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="CJ42" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CK42" t="n">
         <v>1</v>
@@ -10407,13 +10407,13 @@
         <v>1</v>
       </c>
       <c r="DJ42" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="DK42" t="n">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="DL42" t="n">
-        <v>4.723684210526316</v>
+        <v>4.807692307692307</v>
       </c>
     </row>
     <row r="43">
@@ -10464,7 +10464,7 @@
         <v>19</v>
       </c>
       <c r="K43" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L43" t="n">
         <v>22</v>
@@ -10488,7 +10488,7 @@
         <v>11</v>
       </c>
       <c r="S43" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T43" t="n">
         <v>14</v>
@@ -10525,31 +10525,31 @@
         <v>7</v>
       </c>
       <c r="AT43" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU43" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV43" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW43" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX43" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY43" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ43" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA43" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB43" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BC43" t="n">
         <v>4</v>
@@ -10583,31 +10583,31 @@
         <v>5</v>
       </c>
       <c r="CB43" t="n">
-        <v>0.55</v>
+        <v>0.5365853658536586</v>
       </c>
       <c r="CC43" t="n">
-        <v>0.3</v>
+        <v>0.2926829268292683</v>
       </c>
       <c r="CD43" t="n">
-        <v>0.625</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="CE43" t="n">
-        <v>0.4</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="CF43" t="n">
-        <v>0.375</v>
+        <v>0.3658536585365854</v>
       </c>
       <c r="CG43" t="n">
-        <v>0.575</v>
+        <v>0.5609756097560976</v>
       </c>
       <c r="CH43" t="n">
-        <v>0.275</v>
+        <v>0.2682926829268293</v>
       </c>
       <c r="CI43" t="n">
-        <v>0.4</v>
+        <v>0.4390243902439024</v>
       </c>
       <c r="CJ43" t="n">
-        <v>0.4516129032258064</v>
+        <v>0.4375</v>
       </c>
       <c r="CK43" t="n">
         <v>1.5</v>
@@ -10641,13 +10641,13 @@
         <v>1.4</v>
       </c>
       <c r="DJ43" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="DK43" t="n">
-        <v>800</v>
+        <v>816</v>
       </c>
       <c r="DL43" t="n">
-        <v>4.907975460122699</v>
+        <v>4.945454545454545</v>
       </c>
     </row>
     <row r="44">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K44" t="n">
         <v>9</v>
@@ -10753,28 +10753,28 @@
       <c r="AR44" t="inlineStr"/>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB44" t="n">
         <v>9</v>
@@ -10807,28 +10807,28 @@
         <v>0</v>
       </c>
       <c r="CB44" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="CC44" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="CD44" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="CE44" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="CF44" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="CG44" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="CH44" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="CI44" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="CJ44" t="n">
         <v>1</v>
@@ -11141,7 +11141,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K46" t="n">
         <v>21</v>
@@ -11203,28 +11203,28 @@
         <v>1</v>
       </c>
       <c r="AT46" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AU46" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AV46" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AW46" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AX46" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AY46" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AZ46" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BA46" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BB46" t="n">
         <v>31</v>
@@ -11259,28 +11259,28 @@
         <v>1</v>
       </c>
       <c r="CB46" t="n">
-        <v>0.7435897435897436</v>
+        <v>0.725</v>
       </c>
       <c r="CC46" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.325</v>
       </c>
       <c r="CD46" t="n">
-        <v>0.2564102564102564</v>
+        <v>0.25</v>
       </c>
       <c r="CE46" t="n">
-        <v>0.282051282051282</v>
+        <v>0.275</v>
       </c>
       <c r="CF46" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.65</v>
       </c>
       <c r="CG46" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.475</v>
       </c>
       <c r="CH46" t="n">
-        <v>0.358974358974359</v>
+        <v>0.35</v>
       </c>
       <c r="CI46" t="n">
-        <v>0.358974358974359</v>
+        <v>0.35</v>
       </c>
       <c r="CJ46" t="n">
         <v>0.4838709677419355</v>
@@ -11597,7 +11597,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K48" t="n">
         <v>7</v>
@@ -11624,7 +11624,7 @@
         <v>4</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T48" t="n">
         <v>3</v>
@@ -11659,31 +11659,31 @@
         <v>1</v>
       </c>
       <c r="AT48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC48" t="n">
         <v>1</v>
@@ -11715,31 +11715,31 @@
         <v>1</v>
       </c>
       <c r="CB48" t="n">
-        <v>1</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="CC48" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="CD48" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="CE48" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="CF48" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="CG48" t="n">
-        <v>0.5</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="CH48" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="CI48" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="CJ48" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.1304347826086956</v>
       </c>
       <c r="CK48" t="n">
         <v>1</v>
@@ -11771,13 +11771,13 @@
         <v>1</v>
       </c>
       <c r="DJ48" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="DK48" t="n">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="DL48" t="n">
-        <v>3.891891891891892</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -11825,7 +11825,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K49" t="n">
         <v>13</v>
@@ -11852,7 +11852,7 @@
         <v>5</v>
       </c>
       <c r="S49" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="T49" t="n">
         <v>8</v>
@@ -11887,31 +11887,31 @@
         <v>5</v>
       </c>
       <c r="AT49" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU49" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV49" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW49" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX49" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY49" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ49" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA49" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB49" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BC49" t="n">
         <v>2</v>
@@ -11943,31 +11943,31 @@
         <v>2</v>
       </c>
       <c r="CB49" t="n">
-        <v>0.625</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="CC49" t="n">
-        <v>0.4</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="CD49" t="n">
-        <v>0.25</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="CE49" t="n">
-        <v>0.425</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="CF49" t="n">
-        <v>0.325</v>
+        <v>0.3170731707317073</v>
       </c>
       <c r="CG49" t="n">
-        <v>0.425</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="CH49" t="n">
-        <v>0.125</v>
+        <v>0.1219512195121951</v>
       </c>
       <c r="CI49" t="n">
-        <v>0.525</v>
+        <v>0.5609756097560976</v>
       </c>
       <c r="CJ49" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2580645161290323</v>
       </c>
       <c r="CK49" t="n">
         <v>2.5</v>
@@ -11999,13 +11999,13 @@
         <v>2.5</v>
       </c>
       <c r="DJ49" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="DK49" t="n">
-        <v>647</v>
+        <v>663</v>
       </c>
       <c r="DL49" t="n">
-        <v>4.654676258992806</v>
+        <v>4.702127659574468</v>
       </c>
     </row>
     <row r="50">
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K50" t="n">
         <v>12</v>
@@ -12068,10 +12068,10 @@
         <v>13</v>
       </c>
       <c r="O50" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q50" t="n">
         <v>6</v>
@@ -12115,28 +12115,28 @@
         <v>7</v>
       </c>
       <c r="AT50" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU50" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV50" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW50" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX50" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY50" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ50" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA50" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB50" t="n">
         <v>14</v>
@@ -12171,28 +12171,28 @@
         <v>2</v>
       </c>
       <c r="CB50" t="n">
-        <v>0.96</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="CC50" t="n">
-        <v>0.04</v>
+        <v>0.03846153846153846</v>
       </c>
       <c r="CD50" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="CE50" t="n">
-        <v>0.76</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="CF50" t="n">
-        <v>0.36</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="CG50" t="n">
-        <v>0.24</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="CH50" t="n">
-        <v>0.2</v>
+        <v>0.1923076923076923</v>
       </c>
       <c r="CI50" t="n">
-        <v>0.2</v>
+        <v>0.1923076923076923</v>
       </c>
       <c r="CJ50" t="n">
         <v>0.2857142857142857</v>
@@ -12227,13 +12227,13 @@
         <v>3.5</v>
       </c>
       <c r="DJ50" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="DK50" t="n">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="DL50" t="n">
-        <v>4.112244897959184</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="51">
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K52" t="n">
         <v>22</v>
@@ -12514,10 +12514,10 @@
         <v>20</v>
       </c>
       <c r="O52" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P52" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q52" t="n">
         <v>20</v>
@@ -12561,28 +12561,28 @@
         <v>7</v>
       </c>
       <c r="AT52" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU52" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV52" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW52" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX52" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY52" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ52" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA52" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB52" t="n">
         <v>29</v>
@@ -12617,28 +12617,28 @@
         <v>2</v>
       </c>
       <c r="CB52" t="n">
-        <v>0.9</v>
+        <v>0.8780487804878049</v>
       </c>
       <c r="CC52" t="n">
-        <v>0.2</v>
+        <v>0.1951219512195122</v>
       </c>
       <c r="CD52" t="n">
-        <v>0.5</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="CE52" t="n">
-        <v>0.55</v>
+        <v>0.5609756097560976</v>
       </c>
       <c r="CF52" t="n">
-        <v>0.45</v>
+        <v>0.4634146341463415</v>
       </c>
       <c r="CG52" t="n">
-        <v>0.5</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="CH52" t="n">
-        <v>0.325</v>
+        <v>0.3170731707317073</v>
       </c>
       <c r="CI52" t="n">
-        <v>0.475</v>
+        <v>0.4634146341463415</v>
       </c>
       <c r="CJ52" t="n">
         <v>0.3103448275862069</v>
@@ -12673,13 +12673,13 @@
         <v>3.5</v>
       </c>
       <c r="DJ52" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="DK52" t="n">
-        <v>804</v>
+        <v>813</v>
       </c>
       <c r="DL52" t="n">
-        <v>4.542372881355933</v>
+        <v>4.541899441340782</v>
       </c>
     </row>
     <row r="53">
@@ -12956,13 +12956,13 @@
         <v>9</v>
       </c>
       <c r="K54" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L54" t="n">
         <v>14</v>
       </c>
       <c r="M54" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N54" t="n">
         <v>10</v>
@@ -12974,7 +12974,7 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="R54" t="n">
         <v>6</v>
@@ -13017,31 +13017,31 @@
         <v>3</v>
       </c>
       <c r="AT54" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU54" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV54" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW54" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX54" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY54" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ54" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA54" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB54" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC54" t="n">
         <v>4</v>
@@ -13075,31 +13075,31 @@
         <v>5</v>
       </c>
       <c r="CB54" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="CC54" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CD54" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="CE54" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="CF54" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.04545454545454546</v>
       </c>
       <c r="CG54" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="CH54" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="CI54" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="CJ54" t="n">
-        <v>0.09523809523809523</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="CK54" t="n">
         <v>0.5</v>
@@ -13133,13 +13133,13 @@
         <v>0.6</v>
       </c>
       <c r="DJ54" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="DK54" t="n">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="DL54" t="n">
-        <v>4.906666666666666</v>
+        <v>4.875</v>
       </c>
     </row>
     <row r="55">
@@ -13186,13 +13186,13 @@
         <v>15</v>
       </c>
       <c r="K55" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L55" t="n">
         <v>21</v>
       </c>
       <c r="M55" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N55" t="n">
         <v>22</v>
@@ -13204,7 +13204,7 @@
         <v>6</v>
       </c>
       <c r="Q55" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R55" t="n">
         <v>17</v>
@@ -13247,31 +13247,31 @@
         <v>7</v>
       </c>
       <c r="AT55" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AU55" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AV55" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AW55" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AX55" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AY55" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AZ55" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BA55" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BB55" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="BC55" t="n">
         <v>7</v>
@@ -13305,31 +13305,31 @@
         <v>9</v>
       </c>
       <c r="CB55" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.525</v>
       </c>
       <c r="CC55" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.425</v>
       </c>
       <c r="CD55" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.55</v>
       </c>
       <c r="CE55" t="n">
-        <v>0.358974358974359</v>
+        <v>0.35</v>
       </c>
       <c r="CF55" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.15</v>
       </c>
       <c r="CG55" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.675</v>
       </c>
       <c r="CH55" t="n">
-        <v>0.4358974358974359</v>
+        <v>0.425</v>
       </c>
       <c r="CI55" t="n">
-        <v>0.717948717948718</v>
+        <v>0.7</v>
       </c>
       <c r="CJ55" t="n">
-        <v>0.2285714285714286</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="CK55" t="n">
         <v>0.7142857142857143</v>
@@ -13363,13 +13363,13 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="DJ55" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="DK55" t="n">
-        <v>834</v>
+        <v>856</v>
       </c>
       <c r="DL55" t="n">
-        <v>5.054545454545455</v>
+        <v>5.035294117647059</v>
       </c>
     </row>
     <row r="56">
@@ -13413,7 +13413,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K56" t="n">
         <v>12</v>
@@ -13477,28 +13477,28 @@
         <v>4</v>
       </c>
       <c r="AT56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB56" t="n">
         <v>15</v>
@@ -13535,28 +13535,28 @@
         <v>5</v>
       </c>
       <c r="CB56" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CC56" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CD56" t="n">
-        <v>0.8695652173913043</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="CE56" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="CF56" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.625</v>
       </c>
       <c r="CG56" t="n">
-        <v>0.7391304347826086</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="CH56" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="CI56" t="n">
-        <v>0.391304347826087</v>
+        <v>0.375</v>
       </c>
       <c r="CJ56" t="n">
         <v>0.6666666666666666</v>
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K58" t="n">
         <v>22</v>
@@ -13931,28 +13931,28 @@
         <v>6</v>
       </c>
       <c r="AT58" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU58" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV58" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW58" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX58" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY58" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ58" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA58" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB58" t="n">
         <v>32</v>
@@ -13989,28 +13989,28 @@
         <v>7</v>
       </c>
       <c r="CB58" t="n">
-        <v>0.625</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="CC58" t="n">
-        <v>0.425</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="CD58" t="n">
-        <v>0.85</v>
+        <v>0.8292682926829268</v>
       </c>
       <c r="CE58" t="n">
-        <v>0.475</v>
+        <v>0.4634146341463415</v>
       </c>
       <c r="CF58" t="n">
-        <v>0.55</v>
+        <v>0.5365853658536586</v>
       </c>
       <c r="CG58" t="n">
-        <v>0.75</v>
+        <v>0.7317073170731707</v>
       </c>
       <c r="CH58" t="n">
-        <v>0.375</v>
+        <v>0.3658536585365854</v>
       </c>
       <c r="CI58" t="n">
-        <v>0.475</v>
+        <v>0.4634146341463415</v>
       </c>
       <c r="CJ58" t="n">
         <v>0.34375</v>
@@ -14344,7 +14344,7 @@
         <v>13</v>
       </c>
       <c r="K60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L60" t="n">
         <v>10</v>
@@ -14353,7 +14353,7 @@
         <v>8</v>
       </c>
       <c r="N60" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O60" t="n">
         <v>18</v>
@@ -14368,7 +14368,7 @@
         <v>8</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T60" t="n">
         <v>4</v>
@@ -14403,31 +14403,31 @@
         <v>3</v>
       </c>
       <c r="AT60" t="n">
+        <v>22</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>22</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB60" t="n">
         <v>21</v>
-      </c>
-      <c r="AU60" t="n">
-        <v>21</v>
-      </c>
-      <c r="AV60" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW60" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX60" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY60" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ60" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA60" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB60" t="n">
-        <v>20</v>
       </c>
       <c r="BC60" t="n">
         <v>4</v>
@@ -14459,31 +14459,31 @@
         <v>4</v>
       </c>
       <c r="CB60" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="CC60" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CD60" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.5</v>
       </c>
       <c r="CE60" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="CF60" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5</v>
       </c>
       <c r="CG60" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="CH60" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CI60" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="CJ60" t="n">
-        <v>0.2</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CK60" t="n">
         <v>0.75</v>
@@ -14515,13 +14515,13 @@
         <v>0.75</v>
       </c>
       <c r="DJ60" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="DK60" t="n">
-        <v>496</v>
+        <v>526</v>
       </c>
       <c r="DL60" t="n">
-        <v>4.96</v>
+        <v>5.009523809523809</v>
       </c>
     </row>
     <row r="61">
@@ -14572,7 +14572,7 @@
         <v>19</v>
       </c>
       <c r="K61" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L61" t="n">
         <v>19</v>
@@ -14581,7 +14581,7 @@
         <v>28</v>
       </c>
       <c r="N61" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O61" t="n">
         <v>33</v>
@@ -14596,7 +14596,7 @@
         <v>20</v>
       </c>
       <c r="S61" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="T61" t="n">
         <v>13</v>
@@ -14635,31 +14635,31 @@
         <v>6</v>
       </c>
       <c r="AT61" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU61" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV61" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW61" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX61" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY61" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ61" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA61" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB61" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BC61" t="n">
         <v>6</v>
@@ -14695,31 +14695,31 @@
         <v>8</v>
       </c>
       <c r="CB61" t="n">
-        <v>0.475</v>
+        <v>0.4634146341463415</v>
       </c>
       <c r="CC61" t="n">
-        <v>0.7</v>
+        <v>0.6829268292682927</v>
       </c>
       <c r="CD61" t="n">
-        <v>0.55</v>
+        <v>0.5853658536585366</v>
       </c>
       <c r="CE61" t="n">
-        <v>0.825</v>
+        <v>0.8048780487804879</v>
       </c>
       <c r="CF61" t="n">
-        <v>0.65</v>
+        <v>0.6341463414634146</v>
       </c>
       <c r="CG61" t="n">
-        <v>0.775</v>
+        <v>0.7560975609756098</v>
       </c>
       <c r="CH61" t="n">
-        <v>0.5</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="CI61" t="n">
-        <v>0.65</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="CJ61" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.3823529411764706</v>
       </c>
       <c r="CK61" t="n">
         <v>0.8333333333333334</v>
@@ -14755,13 +14755,13 @@
         <v>0.75</v>
       </c>
       <c r="DJ61" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="DK61" t="n">
-        <v>1116</v>
+        <v>1146</v>
       </c>
       <c r="DL61" t="n">
-        <v>4.96</v>
+        <v>4.982608695652174</v>
       </c>
     </row>
     <row r="62">
@@ -15046,7 +15046,7 @@
         <v>9</v>
       </c>
       <c r="K63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L63" t="n">
         <v>8</v>
@@ -15058,7 +15058,7 @@
         <v>10</v>
       </c>
       <c r="O63" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P63" t="n">
         <v>13</v>
@@ -15070,7 +15070,7 @@
         <v>9</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
@@ -15101,31 +15101,31 @@
       <c r="AR63" t="inlineStr"/>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC63" t="inlineStr"/>
       <c r="BD63" t="inlineStr"/>
@@ -15155,31 +15155,31 @@
         <v>0</v>
       </c>
       <c r="CB63" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="CC63" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="CD63" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="CE63" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="CF63" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="CG63" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="CH63" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5</v>
       </c>
       <c r="CI63" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="CJ63" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="CK63" t="inlineStr"/>
       <c r="CL63" t="inlineStr"/>
@@ -15207,13 +15207,13 @@
       <c r="DH63" t="inlineStr"/>
       <c r="DI63" t="inlineStr"/>
       <c r="DJ63" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="DK63" t="n">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="DL63" t="n">
-        <v>4.654761904761905</v>
+        <v>4.724137931034483</v>
       </c>
     </row>
     <row r="64">
@@ -15264,7 +15264,7 @@
         <v>27</v>
       </c>
       <c r="K64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L64" t="n">
         <v>14</v>
@@ -15276,7 +15276,7 @@
         <v>14</v>
       </c>
       <c r="O64" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P64" t="n">
         <v>17</v>
@@ -15288,7 +15288,7 @@
         <v>16</v>
       </c>
       <c r="S64" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T64" t="n">
         <v>8</v>
@@ -15325,31 +15325,31 @@
         <v>1</v>
       </c>
       <c r="AT64" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU64" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV64" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW64" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX64" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY64" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ64" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA64" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB64" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC64" t="n">
         <v>5</v>
@@ -15383,31 +15383,31 @@
         <v>6</v>
       </c>
       <c r="CB64" t="n">
-        <v>0.35</v>
+        <v>0.3414634146341464</v>
       </c>
       <c r="CC64" t="n">
-        <v>0.625</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="CD64" t="n">
-        <v>0.35</v>
+        <v>0.3414634146341464</v>
       </c>
       <c r="CE64" t="n">
-        <v>0.525</v>
+        <v>0.5365853658536586</v>
       </c>
       <c r="CF64" t="n">
-        <v>0.425</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="CG64" t="n">
-        <v>0.675</v>
+        <v>0.6585365853658537</v>
       </c>
       <c r="CH64" t="n">
-        <v>0.4</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="CI64" t="n">
-        <v>0.45</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="CJ64" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2758620689655172</v>
       </c>
       <c r="CK64" t="n">
         <v>0</v>
@@ -15441,13 +15441,13 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="DJ64" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="DK64" t="n">
-        <v>776</v>
+        <v>796</v>
       </c>
       <c r="DL64" t="n">
-        <v>4.703030303030303</v>
+        <v>4.738095238095238</v>
       </c>
     </row>
     <row r="65">
@@ -15495,7 +15495,7 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K65" t="n">
         <v>9</v>
@@ -15559,28 +15559,28 @@
         <v>0</v>
       </c>
       <c r="AT65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB65" t="n">
         <v>11</v>
@@ -15617,28 +15617,28 @@
         <v>2</v>
       </c>
       <c r="CB65" t="n">
-        <v>0.7</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CC65" t="n">
-        <v>0.65</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CD65" t="n">
-        <v>0.4</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CE65" t="n">
-        <v>0.65</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CF65" t="n">
-        <v>0.2</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CG65" t="n">
-        <v>0.2</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CH65" t="n">
-        <v>0.7</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CI65" t="n">
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="CJ65" t="n">
         <v>1.727272727272727</v>
@@ -15957,7 +15957,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K67" t="n">
         <v>19</v>
@@ -16021,28 +16021,28 @@
         <v>3</v>
       </c>
       <c r="AT67" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU67" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV67" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW67" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX67" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY67" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ67" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA67" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB67" t="n">
         <v>31</v>
@@ -16079,28 +16079,28 @@
         <v>6</v>
       </c>
       <c r="CB67" t="n">
-        <v>0.725</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="CC67" t="n">
-        <v>0.65</v>
+        <v>0.6341463414634146</v>
       </c>
       <c r="CD67" t="n">
-        <v>0.4</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="CE67" t="n">
-        <v>0.9</v>
+        <v>0.8780487804878049</v>
       </c>
       <c r="CF67" t="n">
-        <v>0.275</v>
+        <v>0.2682926829268293</v>
       </c>
       <c r="CG67" t="n">
-        <v>0.2</v>
+        <v>0.1951219512195122</v>
       </c>
       <c r="CH67" t="n">
-        <v>0.5</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="CI67" t="n">
-        <v>0.45</v>
+        <v>0.4390243902439024</v>
       </c>
       <c r="CJ67" t="n">
         <v>0.9032258064516129</v>
@@ -16191,16 +16191,16 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K68" t="n">
         <v>8</v>
       </c>
       <c r="L68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N68" t="n">
         <v>5</v>
@@ -16212,7 +16212,7 @@
         <v>7</v>
       </c>
       <c r="Q68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R68" t="n">
         <v>6</v>
@@ -16253,31 +16253,31 @@
         <v>7</v>
       </c>
       <c r="AT68" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU68" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV68" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW68" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX68" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY68" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ68" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA68" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC68" t="n">
         <v>3</v>
@@ -16309,31 +16309,31 @@
         <v>3</v>
       </c>
       <c r="CB68" t="n">
-        <v>0.55</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="CC68" t="n">
-        <v>0.1</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="CD68" t="n">
-        <v>0.25</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="CE68" t="n">
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="CF68" t="n">
-        <v>0.35</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CG68" t="n">
-        <v>0.15</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CH68" t="n">
-        <v>0.3</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CI68" t="n">
-        <v>0.25</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="CJ68" t="n">
-        <v>1.222222222222222</v>
+        <v>1.1</v>
       </c>
       <c r="CK68" t="n">
         <v>2.333333333333333</v>
@@ -16365,13 +16365,13 @@
         <v>2.333333333333333</v>
       </c>
       <c r="DJ68" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="DK68" t="n">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="DL68" t="n">
-        <v>5.457142857142857</v>
+        <v>5.356164383561643</v>
       </c>
     </row>
     <row r="69">
@@ -16647,16 +16647,16 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K70" t="n">
         <v>16</v>
       </c>
       <c r="L70" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M70" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N70" t="n">
         <v>12</v>
@@ -16668,7 +16668,7 @@
         <v>11</v>
       </c>
       <c r="Q70" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R70" t="n">
         <v>16</v>
@@ -16709,31 +16709,31 @@
         <v>8</v>
       </c>
       <c r="AT70" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AU70" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AV70" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AW70" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AX70" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AY70" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AZ70" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BA70" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BB70" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC70" t="n">
         <v>4</v>
@@ -16765,31 +16765,31 @@
         <v>4</v>
       </c>
       <c r="CB70" t="n">
-        <v>0.4594594594594595</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="CC70" t="n">
-        <v>0.1621621621621622</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="CD70" t="n">
-        <v>0.3243243243243243</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="CE70" t="n">
-        <v>0.5945945945945946</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="CF70" t="n">
-        <v>0.2972972972972973</v>
+        <v>0.2894736842105263</v>
       </c>
       <c r="CG70" t="n">
-        <v>0.4594594594594595</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="CH70" t="n">
-        <v>0.4324324324324325</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="CI70" t="n">
-        <v>0.2702702702702703</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="CJ70" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CK70" t="n">
         <v>2</v>
@@ -16821,13 +16821,13 @@
         <v>2</v>
       </c>
       <c r="DJ70" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="DK70" t="n">
-        <v>744</v>
+        <v>753</v>
       </c>
       <c r="DL70" t="n">
-        <v>5.391304347826087</v>
+        <v>5.340425531914893</v>
       </c>
     </row>
     <row r="71">
@@ -17116,7 +17116,7 @@
         <v>11</v>
       </c>
       <c r="K72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L72" t="n">
         <v>8</v>
@@ -17125,16 +17125,16 @@
         <v>6</v>
       </c>
       <c r="N72" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O72" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P72" t="n">
         <v>10</v>
       </c>
       <c r="Q72" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R72" t="n">
         <v>5</v>
@@ -17146,12 +17146,14 @@
         <v>4</v>
       </c>
       <c r="U72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V72" t="n">
         <v>3</v>
       </c>
-      <c r="W72" t="inlineStr"/>
+      <c r="W72" t="n">
+        <v>1</v>
+      </c>
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="inlineStr"/>
@@ -17174,42 +17176,44 @@
       <c r="AQ72" t="inlineStr"/>
       <c r="AR72" t="inlineStr"/>
       <c r="AS72" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>21</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY72" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ72" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB72" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC72" t="n">
         <v>5</v>
       </c>
-      <c r="AT72" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU72" t="n">
-        <v>20</v>
-      </c>
-      <c r="AV72" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW72" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX72" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY72" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ72" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA72" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB72" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC72" t="n">
-        <v>4</v>
-      </c>
       <c r="BD72" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE72" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="BE72" t="n">
+        <v>1</v>
+      </c>
       <c r="BF72" t="inlineStr"/>
       <c r="BG72" t="inlineStr"/>
       <c r="BH72" t="inlineStr"/>
@@ -17232,42 +17236,44 @@
       <c r="BY72" t="inlineStr"/>
       <c r="BZ72" t="inlineStr"/>
       <c r="CA72" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="CB72" t="n">
-        <v>0.4</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CC72" t="n">
-        <v>0.3</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CD72" t="n">
-        <v>0.3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CE72" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="CF72" t="n">
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="CG72" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="CH72" t="n">
+        <v>0.2380952380952381</v>
+      </c>
+      <c r="CI72" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="CJ72" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="CK72" t="n">
         <v>0.8</v>
       </c>
-      <c r="CF72" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="CG72" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="CH72" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="CI72" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="CJ72" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="CK72" t="n">
-        <v>0.5</v>
-      </c>
       <c r="CL72" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="CM72" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="CM72" t="n">
+        <v>1</v>
+      </c>
       <c r="CN72" t="inlineStr"/>
       <c r="CO72" t="inlineStr"/>
       <c r="CP72" t="inlineStr"/>
@@ -17290,16 +17296,16 @@
       <c r="DG72" t="inlineStr"/>
       <c r="DH72" t="inlineStr"/>
       <c r="DI72" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="DJ72" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="DK72" t="n">
-        <v>400</v>
+        <v>451</v>
       </c>
       <c r="DL72" t="n">
-        <v>5.128205128205129</v>
+        <v>5.305882352941176</v>
       </c>
     </row>
     <row r="73">
@@ -17346,7 +17352,7 @@
         <v>22</v>
       </c>
       <c r="K73" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L73" t="n">
         <v>17</v>
@@ -17355,16 +17361,16 @@
         <v>8</v>
       </c>
       <c r="N73" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O73" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P73" t="n">
         <v>32</v>
       </c>
       <c r="Q73" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R73" t="n">
         <v>23</v>
@@ -17376,13 +17382,13 @@
         <v>12</v>
       </c>
       <c r="U73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V73" t="n">
         <v>4</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X73" t="n">
         <v>2</v>
@@ -17408,43 +17414,43 @@
       <c r="AQ73" t="inlineStr"/>
       <c r="AR73" t="inlineStr"/>
       <c r="AS73" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AT73" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU73" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV73" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW73" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX73" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY73" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ73" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA73" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB73" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BC73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BE73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BF73" t="n">
         <v>1</v>
@@ -17470,43 +17476,43 @@
       <c r="BY73" t="inlineStr"/>
       <c r="BZ73" t="inlineStr"/>
       <c r="CA73" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="CB73" t="n">
-        <v>0.425</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="CC73" t="n">
-        <v>0.2</v>
+        <v>0.1951219512195122</v>
       </c>
       <c r="CD73" t="n">
-        <v>0.275</v>
+        <v>0.2926829268292683</v>
       </c>
       <c r="CE73" t="n">
-        <v>0.525</v>
+        <v>0.5365853658536586</v>
       </c>
       <c r="CF73" t="n">
-        <v>0.8</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="CG73" t="n">
-        <v>0.4</v>
+        <v>0.4390243902439024</v>
       </c>
       <c r="CH73" t="n">
-        <v>0.575</v>
+        <v>0.5609756097560976</v>
       </c>
       <c r="CI73" t="n">
-        <v>0.425</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="CJ73" t="n">
-        <v>0.3870967741935484</v>
+        <v>0.375</v>
       </c>
       <c r="CK73" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CL73" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM73" t="n">
         <v>0.5</v>
-      </c>
-      <c r="CL73" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="CM73" t="n">
-        <v>0</v>
       </c>
       <c r="CN73" t="n">
         <v>2</v>
@@ -17532,16 +17538,16 @@
       <c r="DG73" t="inlineStr"/>
       <c r="DH73" t="inlineStr"/>
       <c r="DI73" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="DJ73" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="DK73" t="n">
-        <v>911</v>
+        <v>962</v>
       </c>
       <c r="DL73" t="n">
-        <v>5.422619047619047</v>
+        <v>5.497142857142857</v>
       </c>
     </row>
     <row r="74">
@@ -17826,7 +17832,7 @@
         <v>13</v>
       </c>
       <c r="K75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L75" t="n">
         <v>7</v>
@@ -17853,10 +17859,10 @@
         <v>19</v>
       </c>
       <c r="T75" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr"/>
@@ -17882,37 +17888,37 @@
       <c r="AQ75" t="inlineStr"/>
       <c r="AR75" t="inlineStr"/>
       <c r="AS75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD75" t="inlineStr"/>
       <c r="BE75" t="inlineStr"/>
@@ -17938,34 +17944,34 @@
       <c r="BY75" t="inlineStr"/>
       <c r="BZ75" t="inlineStr"/>
       <c r="CA75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CB75" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="CC75" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="CD75" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="CE75" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="CF75" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="CG75" t="n">
-        <v>0.5</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="CH75" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="CI75" t="n">
-        <v>1.055555555555556</v>
+        <v>1</v>
       </c>
       <c r="CJ75" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="CK75" t="n">
         <v>1</v>
@@ -17997,13 +18003,13 @@
         <v>1</v>
       </c>
       <c r="DJ75" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="DK75" t="n">
-        <v>406</v>
+        <v>434</v>
       </c>
       <c r="DL75" t="n">
-        <v>5.638888888888889</v>
+        <v>5.786666666666667</v>
       </c>
     </row>
     <row r="76">
@@ -18054,7 +18060,7 @@
         <v>23</v>
       </c>
       <c r="K76" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L76" t="n">
         <v>19</v>
@@ -18081,10 +18087,10 @@
         <v>30</v>
       </c>
       <c r="T76" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="U76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V76" t="n">
         <v>0</v>
@@ -18112,37 +18118,37 @@
       <c r="AQ76" t="inlineStr"/>
       <c r="AR76" t="inlineStr"/>
       <c r="AS76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT76" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AU76" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AV76" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AW76" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AX76" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AY76" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AZ76" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="BA76" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="BB76" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BC76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD76" t="n">
         <v>1</v>
@@ -18170,37 +18176,37 @@
       <c r="BY76" t="inlineStr"/>
       <c r="BZ76" t="inlineStr"/>
       <c r="CA76" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CB76" t="n">
-        <v>0.5</v>
+        <v>0.4871794871794872</v>
       </c>
       <c r="CC76" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.358974358974359</v>
       </c>
       <c r="CD76" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.1794871794871795</v>
       </c>
       <c r="CE76" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.5641025641025641</v>
       </c>
       <c r="CF76" t="n">
-        <v>0.4473684210526316</v>
+        <v>0.4358974358974359</v>
       </c>
       <c r="CG76" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="CH76" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="CI76" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="CJ76" t="n">
-        <v>0.7419354838709677</v>
+        <v>0.78125</v>
       </c>
       <c r="CK76" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CL76" t="n">
         <v>0</v>
@@ -18228,16 +18234,16 @@
       <c r="DG76" t="inlineStr"/>
       <c r="DH76" t="inlineStr"/>
       <c r="DI76" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="DJ76" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="DK76" t="n">
-        <v>904</v>
+        <v>932</v>
       </c>
       <c r="DL76" t="n">
-        <v>5.349112426035503</v>
+        <v>5.418604651162791</v>
       </c>
     </row>
     <row r="77">
@@ -18281,7 +18287,7 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K77" t="n">
         <v>9</v>
@@ -18302,7 +18308,7 @@
         <v>17</v>
       </c>
       <c r="Q77" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R77" t="n">
         <v>13</v>
@@ -18343,28 +18349,28 @@
         <v>2</v>
       </c>
       <c r="AT77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB77" t="n">
         <v>10</v>
@@ -18399,28 +18405,28 @@
         <v>2</v>
       </c>
       <c r="CB77" t="n">
-        <v>0.95</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="CC77" t="n">
-        <v>0.35</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CD77" t="n">
-        <v>0.55</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CE77" t="n">
-        <v>0.15</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="CF77" t="n">
-        <v>0.85</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="CG77" t="n">
-        <v>0.35</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CH77" t="n">
-        <v>0.65</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CI77" t="n">
-        <v>0.05</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="CJ77" t="n">
         <v>1.5</v>
@@ -18455,13 +18461,13 @@
         <v>1</v>
       </c>
       <c r="DJ77" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="DK77" t="n">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="DL77" t="n">
-        <v>4.831578947368421</v>
+        <v>4.84375</v>
       </c>
     </row>
     <row r="78">
@@ -18729,7 +18735,7 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K79" t="n">
         <v>20</v>
@@ -18750,7 +18756,7 @@
         <v>28</v>
       </c>
       <c r="Q79" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R79" t="n">
         <v>23</v>
@@ -18791,28 +18797,28 @@
         <v>3</v>
       </c>
       <c r="AT79" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AU79" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AV79" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AW79" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AX79" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AY79" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AZ79" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="BA79" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="BB79" t="n">
         <v>28</v>
@@ -18847,28 +18853,28 @@
         <v>4</v>
       </c>
       <c r="CB79" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.8205128205128205</v>
       </c>
       <c r="CC79" t="n">
-        <v>0.3421052631578947</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CD79" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.717948717948718</v>
       </c>
       <c r="CE79" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2564102564102564</v>
       </c>
       <c r="CF79" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.717948717948718</v>
       </c>
       <c r="CG79" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="CH79" t="n">
-        <v>0.6052631578947368</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="CI79" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2564102564102564</v>
       </c>
       <c r="CJ79" t="n">
         <v>0.5357142857142857</v>
@@ -18903,13 +18909,13 @@
         <v>0.75</v>
       </c>
       <c r="DJ79" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="DK79" t="n">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="DL79" t="n">
-        <v>4.71578947368421</v>
+        <v>4.722513089005235</v>
       </c>
     </row>
     <row r="80">
@@ -19174,13 +19180,13 @@
         <v>8</v>
       </c>
       <c r="K81" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L81" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M81" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N81" t="n">
         <v>20</v>
@@ -19192,7 +19198,7 @@
         <v>11</v>
       </c>
       <c r="Q81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R81" t="n">
         <v>4</v>
@@ -19237,31 +19243,31 @@
         <v>6</v>
       </c>
       <c r="AT81" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU81" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV81" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW81" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX81" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY81" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ81" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA81" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB81" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC81" t="n">
         <v>3</v>
@@ -19297,31 +19303,31 @@
         <v>6</v>
       </c>
       <c r="CB81" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.5</v>
       </c>
       <c r="CC81" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="CD81" t="n">
-        <v>0.9523809523809523</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="CE81" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="CF81" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5</v>
       </c>
       <c r="CG81" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="CH81" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="CI81" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="CJ81" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CK81" t="n">
         <v>0.3333333333333333</v>
@@ -19357,13 +19363,13 @@
         <v>1</v>
       </c>
       <c r="DJ81" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="DK81" t="n">
-        <v>519</v>
+        <v>533</v>
       </c>
       <c r="DL81" t="n">
-        <v>5.40625</v>
+        <v>5.225490196078431</v>
       </c>
     </row>
     <row r="82">
@@ -19412,13 +19418,13 @@
         <v>16</v>
       </c>
       <c r="K82" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L82" t="n">
+        <v>28</v>
+      </c>
+      <c r="M82" t="n">
         <v>26</v>
-      </c>
-      <c r="M82" t="n">
-        <v>23</v>
       </c>
       <c r="N82" t="n">
         <v>27</v>
@@ -19430,7 +19436,7 @@
         <v>21</v>
       </c>
       <c r="Q82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R82" t="n">
         <v>8</v>
@@ -19475,31 +19481,31 @@
         <v>6</v>
       </c>
       <c r="AT82" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU82" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV82" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW82" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX82" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY82" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ82" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA82" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB82" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BC82" t="n">
         <v>3</v>
@@ -19535,31 +19541,31 @@
         <v>6</v>
       </c>
       <c r="CB82" t="n">
-        <v>0.65</v>
+        <v>0.6829268292682927</v>
       </c>
       <c r="CC82" t="n">
-        <v>0.575</v>
+        <v>0.6341463414634146</v>
       </c>
       <c r="CD82" t="n">
-        <v>0.675</v>
+        <v>0.6585365853658537</v>
       </c>
       <c r="CE82" t="n">
-        <v>0.425</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="CF82" t="n">
-        <v>0.525</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="CG82" t="n">
-        <v>0.55</v>
+        <v>0.5609756097560976</v>
       </c>
       <c r="CH82" t="n">
-        <v>0.2</v>
+        <v>0.1951219512195122</v>
       </c>
       <c r="CI82" t="n">
-        <v>0.675</v>
+        <v>0.6585365853658537</v>
       </c>
       <c r="CJ82" t="n">
-        <v>0.75</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="CK82" t="n">
         <v>0.3333333333333333</v>
@@ -19595,13 +19601,13 @@
         <v>1</v>
       </c>
       <c r="DJ82" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="DK82" t="n">
-        <v>1015</v>
+        <v>1029</v>
       </c>
       <c r="DL82" t="n">
-        <v>4.975490196078431</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="83">
@@ -19648,13 +19654,13 @@
         <v>13</v>
       </c>
       <c r="K83" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L83" t="n">
         <v>4</v>
       </c>
       <c r="M83" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="N83" t="n">
         <v>11</v>
@@ -19672,10 +19678,10 @@
         <v>6</v>
       </c>
       <c r="S83" t="n">
+        <v>8</v>
+      </c>
+      <c r="T83" t="n">
         <v>7</v>
-      </c>
-      <c r="T83" t="n">
-        <v>5</v>
       </c>
       <c r="U83" t="inlineStr"/>
       <c r="V83" t="inlineStr"/>
@@ -19703,31 +19709,31 @@
       <c r="AR83" t="inlineStr"/>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB83" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC83" t="inlineStr"/>
       <c r="BD83" t="inlineStr"/>
@@ -19757,31 +19763,31 @@
         <v>0</v>
       </c>
       <c r="CB83" t="n">
-        <v>0.2</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CC83" t="n">
-        <v>0.45</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CD83" t="n">
-        <v>0.55</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CE83" t="n">
-        <v>0.3</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CF83" t="n">
-        <v>0.45</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CG83" t="n">
-        <v>0.15</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="CH83" t="n">
-        <v>0.3</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CI83" t="n">
-        <v>0.35</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CJ83" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.7</v>
       </c>
       <c r="CK83" t="inlineStr"/>
       <c r="CL83" t="inlineStr"/>
@@ -19809,13 +19815,13 @@
       <c r="DH83" t="inlineStr"/>
       <c r="DI83" t="inlineStr"/>
       <c r="DJ83" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="DK83" t="n">
-        <v>285</v>
+        <v>319</v>
       </c>
       <c r="DL83" t="n">
-        <v>4.596774193548387</v>
+        <v>4.623188405797102</v>
       </c>
     </row>
     <row r="84">
@@ -20076,13 +20082,13 @@
         <v>24</v>
       </c>
       <c r="K85" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L85" t="n">
         <v>19</v>
       </c>
       <c r="M85" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N85" t="n">
         <v>21</v>
@@ -20100,10 +20106,10 @@
         <v>18</v>
       </c>
       <c r="S85" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T85" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U85" t="inlineStr"/>
       <c r="V85" t="inlineStr"/>
@@ -20131,31 +20137,31 @@
       <c r="AR85" t="inlineStr"/>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AU85" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AV85" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AW85" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AX85" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AY85" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AZ85" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BA85" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BB85" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC85" t="inlineStr"/>
       <c r="BD85" t="inlineStr"/>
@@ -20185,31 +20191,31 @@
         <v>0</v>
       </c>
       <c r="CB85" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.475</v>
       </c>
       <c r="CC85" t="n">
-        <v>0.282051282051282</v>
+        <v>0.375</v>
       </c>
       <c r="CD85" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.525</v>
       </c>
       <c r="CE85" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.325</v>
       </c>
       <c r="CF85" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.3</v>
       </c>
       <c r="CG85" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.15</v>
       </c>
       <c r="CH85" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.45</v>
       </c>
       <c r="CI85" t="n">
-        <v>0.4358974358974359</v>
+        <v>0.45</v>
       </c>
       <c r="CJ85" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3448275862068966</v>
       </c>
       <c r="CK85" t="inlineStr"/>
       <c r="CL85" t="inlineStr"/>
@@ -20237,13 +20243,13 @@
       <c r="DH85" t="inlineStr"/>
       <c r="DI85" t="inlineStr"/>
       <c r="DJ85" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="DK85" t="n">
-        <v>586</v>
+        <v>620</v>
       </c>
       <c r="DL85" t="n">
-        <v>4.614173228346456</v>
+        <v>4.626865671641791</v>
       </c>
     </row>
     <row r="86">
@@ -20287,7 +20293,7 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K86" t="n">
         <v>10</v>
@@ -20302,7 +20308,7 @@
         <v>12</v>
       </c>
       <c r="O86" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P86" t="n">
         <v>13</v>
@@ -20353,34 +20359,34 @@
         <v>2</v>
       </c>
       <c r="AT86" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU86" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV86" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW86" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX86" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY86" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ86" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA86" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB86" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD86" t="n">
         <v>1</v>
@@ -20410,37 +20416,37 @@
       <c r="BY86" t="inlineStr"/>
       <c r="BZ86" t="inlineStr"/>
       <c r="CA86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CB86" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="CC86" t="n">
-        <v>0.5909090909090909</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="CD86" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="CE86" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="CF86" t="n">
-        <v>0.5909090909090909</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="CG86" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="CH86" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="CI86" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="CJ86" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="CK86" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="CL86" t="n">
         <v>1</v>
@@ -20470,16 +20476,16 @@
       <c r="DG86" t="inlineStr"/>
       <c r="DH86" t="inlineStr"/>
       <c r="DI86" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="DJ86" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="DK86" t="n">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="DL86" t="n">
-        <v>4.565217391304348</v>
+        <v>4.553191489361702</v>
       </c>
     </row>
     <row r="87">
@@ -20737,7 +20743,7 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K88" t="n">
         <v>16</v>
@@ -20752,7 +20758,7 @@
         <v>17</v>
       </c>
       <c r="O88" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P88" t="n">
         <v>19</v>
@@ -20803,34 +20809,34 @@
         <v>2</v>
       </c>
       <c r="AT88" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AU88" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AV88" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AW88" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AX88" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AY88" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AZ88" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BA88" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BB88" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BC88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD88" t="n">
         <v>1</v>
@@ -20860,37 +20866,37 @@
       <c r="BY88" t="inlineStr"/>
       <c r="BZ88" t="inlineStr"/>
       <c r="CA88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CB88" t="n">
-        <v>0.358974358974359</v>
+        <v>0.35</v>
       </c>
       <c r="CC88" t="n">
-        <v>0.7948717948717948</v>
+        <v>0.775</v>
       </c>
       <c r="CD88" t="n">
-        <v>0.4358974358974359</v>
+        <v>0.425</v>
       </c>
       <c r="CE88" t="n">
-        <v>0.358974358974359</v>
+        <v>0.4</v>
       </c>
       <c r="CF88" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.475</v>
       </c>
       <c r="CG88" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.475</v>
       </c>
       <c r="CH88" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.6</v>
       </c>
       <c r="CI88" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.55</v>
       </c>
       <c r="CJ88" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="CK88" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="CL88" t="n">
         <v>1</v>
@@ -20920,16 +20926,16 @@
       <c r="DG88" t="inlineStr"/>
       <c r="DH88" t="inlineStr"/>
       <c r="DI88" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="DJ88" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="DK88" t="n">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="DL88" t="n">
-        <v>4.642424242424243</v>
+        <v>4.634730538922156</v>
       </c>
     </row>
     <row r="89">
@@ -20973,16 +20979,16 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K89" t="n">
         <v>12</v>
       </c>
       <c r="L89" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M89" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N89" t="n">
         <v>4</v>
@@ -20991,10 +20997,10 @@
         <v>15</v>
       </c>
       <c r="P89" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q89" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R89" t="n">
         <v>16</v>
@@ -21005,9 +21011,15 @@
       <c r="T89" t="n">
         <v>5</v>
       </c>
-      <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
+      <c r="U89" t="n">
+        <v>2</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" t="n">
+        <v>0</v>
+      </c>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="inlineStr"/>
@@ -21029,37 +21041,45 @@
       <c r="AP89" t="inlineStr"/>
       <c r="AQ89" t="inlineStr"/>
       <c r="AR89" t="inlineStr"/>
-      <c r="AS89" t="inlineStr"/>
+      <c r="AS89" t="n">
+        <v>2</v>
+      </c>
       <c r="AT89" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU89" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV89" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW89" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX89" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY89" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ89" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA89" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB89" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC89" t="inlineStr"/>
-      <c r="BD89" t="inlineStr"/>
-      <c r="BE89" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="BC89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE89" t="n">
+        <v>1</v>
+      </c>
       <c r="BF89" t="inlineStr"/>
       <c r="BG89" t="inlineStr"/>
       <c r="BH89" t="inlineStr"/>
@@ -21082,38 +21102,44 @@
       <c r="BY89" t="inlineStr"/>
       <c r="BZ89" t="inlineStr"/>
       <c r="CA89" t="n">
+        <v>3</v>
+      </c>
+      <c r="CB89" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="CC89" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CD89" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="CE89" t="n">
+        <v>0.6818181818181818</v>
+      </c>
+      <c r="CF89" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="CG89" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="CH89" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CI89" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="CJ89" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="CK89" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL89" t="n">
         <v>0</v>
       </c>
-      <c r="CB89" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="CC89" t="n">
-        <v>0.8095238095238095</v>
-      </c>
-      <c r="CD89" t="n">
-        <v>0.1904761904761905</v>
-      </c>
-      <c r="CE89" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="CF89" t="n">
-        <v>0.6190476190476191</v>
-      </c>
-      <c r="CG89" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="CH89" t="n">
-        <v>0.7619047619047619</v>
-      </c>
-      <c r="CI89" t="n">
-        <v>0.3809523809523809</v>
-      </c>
-      <c r="CJ89" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="CK89" t="inlineStr"/>
-      <c r="CL89" t="inlineStr"/>
-      <c r="CM89" t="inlineStr"/>
+      <c r="CM89" t="n">
+        <v>0</v>
+      </c>
       <c r="CN89" t="inlineStr"/>
       <c r="CO89" t="inlineStr"/>
       <c r="CP89" t="inlineStr"/>
@@ -21135,15 +21161,17 @@
       <c r="DF89" t="inlineStr"/>
       <c r="DG89" t="inlineStr"/>
       <c r="DH89" t="inlineStr"/>
-      <c r="DI89" t="inlineStr"/>
+      <c r="DI89" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="DJ89" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="DK89" t="n">
-        <v>441</v>
+        <v>475</v>
       </c>
       <c r="DL89" t="n">
-        <v>4.642105263157895</v>
+        <v>4.702970297029703</v>
       </c>
     </row>
     <row r="90">
@@ -21423,16 +21451,16 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K91" t="n">
         <v>24</v>
       </c>
       <c r="L91" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M91" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N91" t="n">
         <v>10</v>
@@ -21441,10 +21469,10 @@
         <v>25</v>
       </c>
       <c r="P91" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q91" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R91" t="n">
         <v>19</v>
@@ -21456,7 +21484,7 @@
         <v>13</v>
       </c>
       <c r="U91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
@@ -21486,43 +21514,43 @@
       <c r="AQ91" t="inlineStr"/>
       <c r="AR91" t="inlineStr"/>
       <c r="AS91" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT91" t="n">
+        <v>40</v>
+      </c>
+      <c r="AU91" t="n">
+        <v>40</v>
+      </c>
+      <c r="AV91" t="n">
+        <v>40</v>
+      </c>
+      <c r="AW91" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX91" t="n">
+        <v>40</v>
+      </c>
+      <c r="AY91" t="n">
+        <v>40</v>
+      </c>
+      <c r="AZ91" t="n">
+        <v>40</v>
+      </c>
+      <c r="BA91" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB91" t="n">
+        <v>31</v>
+      </c>
+      <c r="BC91" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD91" t="n">
         <v>2</v>
       </c>
-      <c r="AT91" t="n">
-        <v>39</v>
-      </c>
-      <c r="AU91" t="n">
-        <v>39</v>
-      </c>
-      <c r="AV91" t="n">
-        <v>39</v>
-      </c>
-      <c r="AW91" t="n">
-        <v>39</v>
-      </c>
-      <c r="AX91" t="n">
-        <v>39</v>
-      </c>
-      <c r="AY91" t="n">
-        <v>39</v>
-      </c>
-      <c r="AZ91" t="n">
-        <v>39</v>
-      </c>
-      <c r="BA91" t="n">
-        <v>39</v>
-      </c>
-      <c r="BB91" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC91" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD91" t="n">
-        <v>1</v>
-      </c>
       <c r="BE91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BF91" t="inlineStr"/>
       <c r="BG91" t="inlineStr"/>
@@ -21546,37 +21574,37 @@
       <c r="BY91" t="inlineStr"/>
       <c r="BZ91" t="inlineStr"/>
       <c r="CA91" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="CB91" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.475</v>
       </c>
       <c r="CC91" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.675</v>
       </c>
       <c r="CD91" t="n">
-        <v>0.2564102564102564</v>
+        <v>0.25</v>
       </c>
       <c r="CE91" t="n">
-        <v>0.6410256410256411</v>
+        <v>0.625</v>
       </c>
       <c r="CF91" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.625</v>
       </c>
       <c r="CG91" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.4</v>
       </c>
       <c r="CH91" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.475</v>
       </c>
       <c r="CI91" t="n">
-        <v>0.4358974358974359</v>
+        <v>0.425</v>
       </c>
       <c r="CJ91" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.4193548387096774</v>
       </c>
       <c r="CK91" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="CL91" t="n">
         <v>0</v>
@@ -21606,16 +21634,16 @@
       <c r="DG91" t="inlineStr"/>
       <c r="DH91" t="inlineStr"/>
       <c r="DI91" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="DJ91" t="n">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="DK91" t="n">
-        <v>816</v>
+        <v>850</v>
       </c>
       <c r="DL91" t="n">
-        <v>4.744186046511628</v>
+        <v>4.775280898876405</v>
       </c>
     </row>
   </sheetData>

--- a/defense.xlsx
+++ b/defense.xlsx
@@ -989,19 +989,19 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
         <v>14</v>
       </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="O2" t="n">
         <v>14</v>
@@ -1051,31 +1051,31 @@
         <v>3</v>
       </c>
       <c r="AT2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AU2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AV2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AW2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AX2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AY2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AZ2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC2" t="n">
         <v>1</v>
@@ -1107,31 +1107,31 @@
         <v>1</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.375</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.625</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="CF2" t="n">
-        <v>1.047619047619048</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.181818181818182</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="CK2" t="n">
         <v>3</v>
@@ -1163,13 +1163,13 @@
         <v>3</v>
       </c>
       <c r="DJ2" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="DK2" t="n">
-        <v>555</v>
+        <v>577</v>
       </c>
       <c r="DL2" t="n">
-        <v>5.091743119266055</v>
+        <v>4.931623931623932</v>
       </c>
     </row>
     <row r="3">
@@ -1457,19 +1457,19 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M4" t="n">
         <v>33</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="O4" t="n">
         <v>23</v>
@@ -1523,31 +1523,31 @@
         <v>7</v>
       </c>
       <c r="AT4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AU4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AV4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AW4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AX4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AY4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AZ4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="BA4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="BB4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BC4" t="n">
         <v>2</v>
@@ -1583,31 +1583,31 @@
         <v>4</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.5609756097560976</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.8048780487804879</v>
+        <v>0.75</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.4390243902439024</v>
+        <v>0.5681818181818182</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.5609756097560976</v>
+        <v>0.5227272727272727</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.7804878048780488</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.4390243902439024</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.5365853658536586</v>
+        <v>0.5</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.6829268292682927</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.53125</v>
       </c>
       <c r="CK4" t="n">
         <v>1.5</v>
@@ -1643,13 +1643,13 @@
         <v>1.75</v>
       </c>
       <c r="DJ4" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="DK4" t="n">
-        <v>1111</v>
+        <v>1133</v>
       </c>
       <c r="DL4" t="n">
-        <v>5.004504504504505</v>
+        <v>4.926086956521739</v>
       </c>
     </row>
     <row r="5">
@@ -1697,19 +1697,19 @@
         </is>
       </c>
       <c r="J5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>13</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6</v>
+      </c>
+      <c r="N5" t="n">
         <v>7</v>
-      </c>
-      <c r="K5" t="n">
-        <v>12</v>
-      </c>
-      <c r="L5" t="n">
-        <v>7</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>6</v>
       </c>
       <c r="O5" t="n">
         <v>15</v>
@@ -1759,31 +1759,31 @@
         <v>2</v>
       </c>
       <c r="AT5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AU5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AV5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AY5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BB5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC5" t="n">
         <v>2</v>
@@ -1815,31 +1815,31 @@
         <v>2</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.631578947368421</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CK5" t="n">
         <v>1</v>
@@ -1871,13 +1871,13 @@
         <v>1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="DK5" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="DL5" t="n">
-        <v>4.739726027397261</v>
+        <v>4.631578947368421</v>
       </c>
     </row>
     <row r="6">
@@ -2159,19 +2159,19 @@
         </is>
       </c>
       <c r="J7" t="n">
+        <v>18</v>
+      </c>
+      <c r="K7" t="n">
+        <v>24</v>
+      </c>
+      <c r="L7" t="n">
+        <v>26</v>
+      </c>
+      <c r="M7" t="n">
         <v>17</v>
       </c>
-      <c r="K7" t="n">
-        <v>23</v>
-      </c>
-      <c r="L7" t="n">
-        <v>25</v>
-      </c>
-      <c r="M7" t="n">
-        <v>16</v>
-      </c>
       <c r="N7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O7" t="n">
         <v>22</v>
@@ -2223,31 +2223,31 @@
         <v>3</v>
       </c>
       <c r="AT7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AU7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AV7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AW7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AY7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AZ7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BA7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BC7" t="n">
         <v>3</v>
@@ -2281,31 +2281,31 @@
         <v>4</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.625</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.4</v>
+        <v>0.4047619047619048</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.45</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.55</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.75</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.45</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.275</v>
+        <v>0.2619047619047619</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.3</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CK7" t="n">
         <v>0.6666666666666666</v>
@@ -2339,13 +2339,13 @@
         <v>0.75</v>
       </c>
       <c r="DJ7" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="DK7" t="n">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="DL7" t="n">
-        <v>4.470238095238095</v>
+        <v>4.426900584795321</v>
       </c>
     </row>
     <row r="8">
@@ -2603,31 +2603,31 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L9" t="n">
         <v>6</v>
       </c>
       <c r="M9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
         <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -2665,31 +2665,31 @@
         <v>4</v>
       </c>
       <c r="AT9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AU9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AV9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AW9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AX9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AY9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AZ9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BB9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BC9" t="n">
         <v>2</v>
@@ -2721,31 +2721,31 @@
         <v>2</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.25</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CH9" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.2083333333333333</v>
+      </c>
+      <c r="CJ9" t="n">
         <v>0.3333333333333333</v>
-      </c>
-      <c r="CI9" t="n">
-        <v>0.2380952380952381</v>
-      </c>
-      <c r="CJ9" t="n">
-        <v>0.3809523809523809</v>
       </c>
       <c r="CK9" t="n">
         <v>2</v>
@@ -2777,13 +2777,13 @@
         <v>2</v>
       </c>
       <c r="DJ9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="DK9" t="n">
-        <v>311</v>
+        <v>374</v>
       </c>
       <c r="DL9" t="n">
-        <v>5.271186440677966</v>
+        <v>5.267605633802817</v>
       </c>
     </row>
     <row r="10">
@@ -2827,31 +2827,31 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L10" t="n">
         <v>19</v>
       </c>
       <c r="M10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O10" t="n">
         <v>18</v>
       </c>
       <c r="P10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q10" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="R10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="S10" t="n">
         <v>19</v>
@@ -2889,31 +2889,31 @@
         <v>4</v>
       </c>
       <c r="AT10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AU10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AV10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AW10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AX10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AY10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AZ10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="BA10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="BB10" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BC10" t="n">
         <v>2</v>
@@ -2945,31 +2945,31 @@
         <v>2</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.4634146341463415</v>
+        <v>0.4318181818181818</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.3170731707317073</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.3170731707317073</v>
+        <v>0.3409090909090909</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.4390243902439024</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.2682926829268293</v>
+        <v>0.2954545454545455</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.4390243902439024</v>
+        <v>0.5</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.3414634146341464</v>
+        <v>0.3863636363636364</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.4634146341463415</v>
+        <v>0.4318181818181818</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.3103448275862069</v>
+        <v>0.28125</v>
       </c>
       <c r="CK10" t="n">
         <v>2</v>
@@ -3001,13 +3001,13 @@
         <v>2</v>
       </c>
       <c r="DJ10" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="DK10" t="n">
-        <v>690</v>
+        <v>753</v>
       </c>
       <c r="DL10" t="n">
-        <v>4.859154929577465</v>
+        <v>4.88961038961039</v>
       </c>
     </row>
     <row r="11">
@@ -3283,16 +3283,16 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L12" t="n">
         <v>5</v>
       </c>
       <c r="M12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N12" t="n">
         <v>10</v>
@@ -3307,16 +3307,16 @@
         <v>17</v>
       </c>
       <c r="R12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="S12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T12" t="n">
         <v>5</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V12" t="n">
         <v>1</v>
@@ -3348,37 +3348,37 @@
       <c r="AQ12" t="inlineStr"/>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AT12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AU12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AV12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AW12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AX12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AY12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BB12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BC12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BD12" t="n">
         <v>1</v>
@@ -3410,37 +3410,37 @@
       <c r="BY12" t="inlineStr"/>
       <c r="BZ12" t="inlineStr"/>
       <c r="CA12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.375</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.375</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.6666666666666666</v>
+        <v>1.4</v>
       </c>
       <c r="CL12" t="n">
         <v>1</v>
@@ -3472,16 +3472,16 @@
       <c r="DG12" t="inlineStr"/>
       <c r="DH12" t="inlineStr"/>
       <c r="DI12" t="n">
-        <v>0.6666666666666666</v>
+        <v>1.125</v>
       </c>
       <c r="DJ12" t="n">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="DK12" t="n">
-        <v>517</v>
+        <v>630</v>
       </c>
       <c r="DL12" t="n">
-        <v>5.681318681318682</v>
+        <v>5.88785046728972</v>
       </c>
     </row>
     <row r="13">
@@ -3529,16 +3529,16 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L13" t="n">
         <v>14</v>
       </c>
       <c r="M13" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N13" t="n">
         <v>14</v>
@@ -3553,16 +3553,16 @@
         <v>26</v>
       </c>
       <c r="R13" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="S13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T13" t="n">
         <v>8</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V13" t="n">
         <v>1</v>
@@ -3594,37 +3594,37 @@
       <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AT13" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AU13" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AV13" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AW13" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AX13" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AY13" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AZ13" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="BA13" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="BB13" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BC13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD13" t="n">
         <v>1</v>
@@ -3656,37 +3656,37 @@
       <c r="BY13" t="inlineStr"/>
       <c r="BZ13" t="inlineStr"/>
       <c r="CA13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.358974358974359</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.358974358974359</v>
+        <v>0.4047619047619048</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.358974358974359</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.5476190476190477</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.2962962962962963</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.6</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="CL13" t="n">
         <v>1</v>
@@ -3718,16 +3718,16 @@
       <c r="DG13" t="inlineStr"/>
       <c r="DH13" t="inlineStr"/>
       <c r="DI13" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="DJ13" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="DK13" t="n">
-        <v>778</v>
+        <v>891</v>
       </c>
       <c r="DL13" t="n">
-        <v>5.152317880794702</v>
+        <v>5.335329341317365</v>
       </c>
     </row>
     <row r="14">
@@ -3775,31 +3775,31 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L14" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S14" t="n">
         <v>8</v>
@@ -3808,7 +3808,7 @@
         <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3836,37 +3836,37 @@
       <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AU14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AV14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AW14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AX14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AY14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AZ14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BB14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BC14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BD14" t="n">
         <v>1</v>
@@ -3894,37 +3894,37 @@
       <c r="BY14" t="inlineStr"/>
       <c r="BZ14" t="inlineStr"/>
       <c r="CA14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.625</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.9523809523809523</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="CE14" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CJ14" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="CF14" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="CG14" t="n">
-        <v>0.7619047619047619</v>
-      </c>
-      <c r="CH14" t="n">
-        <v>0.5238095238095238</v>
-      </c>
-      <c r="CI14" t="n">
-        <v>0.3809523809523809</v>
-      </c>
-      <c r="CJ14" t="n">
-        <v>0.3636363636363636</v>
-      </c>
       <c r="CK14" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="CL14" t="n">
         <v>0</v>
@@ -3952,16 +3952,16 @@
       <c r="DG14" t="inlineStr"/>
       <c r="DH14" t="inlineStr"/>
       <c r="DI14" t="n">
-        <v>0.6666666666666666</v>
+        <v>1.2</v>
       </c>
       <c r="DJ14" t="n">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="DK14" t="n">
-        <v>454</v>
+        <v>544</v>
       </c>
       <c r="DL14" t="n">
-        <v>4.829787234042553</v>
+        <v>4.857142857142857</v>
       </c>
     </row>
     <row r="15">
@@ -4237,31 +4237,31 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K16" t="n">
+        <v>24</v>
+      </c>
+      <c r="L16" t="n">
+        <v>25</v>
+      </c>
+      <c r="M16" t="n">
+        <v>8</v>
+      </c>
+      <c r="N16" t="n">
+        <v>30</v>
+      </c>
+      <c r="O16" t="n">
+        <v>19</v>
+      </c>
+      <c r="P16" t="n">
         <v>22</v>
       </c>
-      <c r="L16" t="n">
-        <v>21</v>
-      </c>
-      <c r="M16" t="n">
-        <v>6</v>
-      </c>
-      <c r="N16" t="n">
-        <v>28</v>
-      </c>
-      <c r="O16" t="n">
-        <v>18</v>
-      </c>
-      <c r="P16" t="n">
-        <v>21</v>
-      </c>
       <c r="Q16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="S16" t="n">
         <v>23</v>
@@ -4270,7 +4270,7 @@
         <v>7</v>
       </c>
       <c r="U16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -4298,37 +4298,37 @@
       <c r="AQ16" t="inlineStr"/>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AT16" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AU16" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AV16" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AW16" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AX16" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AY16" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AZ16" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="BA16" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="BB16" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="BC16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BD16" t="n">
         <v>1</v>
@@ -4356,37 +4356,37 @@
       <c r="BY16" t="inlineStr"/>
       <c r="BZ16" t="inlineStr"/>
       <c r="CA16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.525</v>
+        <v>0.5813953488372093</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.15</v>
+        <v>0.186046511627907</v>
       </c>
       <c r="CD16" t="n">
-        <v>0.7</v>
+        <v>0.6976744186046512</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.45</v>
+        <v>0.4418604651162791</v>
       </c>
       <c r="CF16" t="n">
-        <v>0.525</v>
+        <v>0.5116279069767442</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.6</v>
+        <v>0.5813953488372093</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.55</v>
+        <v>0.5813953488372093</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.575</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="CL16" t="n">
         <v>0</v>
@@ -4414,16 +4414,16 @@
       <c r="DG16" t="inlineStr"/>
       <c r="DH16" t="inlineStr"/>
       <c r="DI16" t="n">
-        <v>1</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="DJ16" t="n">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="DK16" t="n">
-        <v>889</v>
+        <v>979</v>
       </c>
       <c r="DL16" t="n">
-        <v>5.051136363636363</v>
+        <v>5.046391752577319</v>
       </c>
     </row>
     <row r="17">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K17" t="n">
         <v>9</v>
       </c>
       <c r="L17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M17" t="n">
         <v>5</v>
@@ -4482,13 +4482,13 @@
         <v>8</v>
       </c>
       <c r="O17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P17" t="n">
         <v>7</v>
       </c>
       <c r="Q17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R17" t="n">
         <v>13</v>
@@ -4529,28 +4529,28 @@
         <v>7</v>
       </c>
       <c r="AT17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AU17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BB17" t="n">
         <v>11</v>
@@ -4585,28 +4585,28 @@
         <v>4</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.35</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.25</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.5</v>
       </c>
       <c r="CF17" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.35</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.55</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.65</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5</v>
       </c>
       <c r="CJ17" t="n">
         <v>0.3636363636363636</v>
@@ -4641,13 +4641,13 @@
         <v>1.75</v>
       </c>
       <c r="DJ17" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="DK17" t="n">
-        <v>427</v>
+        <v>459</v>
       </c>
       <c r="DL17" t="n">
-        <v>5.618421052631579</v>
+        <v>5.337209302325581</v>
       </c>
     </row>
     <row r="18">
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K19" t="n">
         <v>21</v>
       </c>
       <c r="L19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M19" t="n">
         <v>23</v>
@@ -4936,13 +4936,13 @@
         <v>16</v>
       </c>
       <c r="O19" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="P19" t="n">
         <v>14</v>
       </c>
       <c r="Q19" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R19" t="n">
         <v>26</v>
@@ -4985,28 +4985,28 @@
         <v>8</v>
       </c>
       <c r="AT19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AU19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AV19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AW19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AY19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AZ19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BA19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB19" t="n">
         <v>33</v>
@@ -5043,28 +5043,28 @@
         <v>6</v>
       </c>
       <c r="CB19" t="n">
-        <v>0.45</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="CC19" t="n">
-        <v>0.575</v>
+        <v>0.5476190476190477</v>
       </c>
       <c r="CD19" t="n">
-        <v>0.4</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CE19" t="n">
-        <v>0.675</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="CF19" t="n">
-        <v>0.35</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CG19" t="n">
-        <v>0.425</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="CH19" t="n">
-        <v>0.65</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CI19" t="n">
-        <v>0.675</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="CJ19" t="n">
         <v>0.2121212121212121</v>
@@ -5101,13 +5101,13 @@
         <v>1.333333333333333</v>
       </c>
       <c r="DJ19" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="DK19" t="n">
-        <v>934</v>
+        <v>966</v>
       </c>
       <c r="DL19" t="n">
-        <v>5.048648648648649</v>
+        <v>4.953846153846154</v>
       </c>
     </row>
     <row r="20">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K20" t="n">
         <v>9</v>
@@ -5173,16 +5173,16 @@
         <v>7</v>
       </c>
       <c r="P20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R20" t="n">
         <v>5</v>
       </c>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
@@ -5219,28 +5219,28 @@
         <v>1</v>
       </c>
       <c r="AT20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AU20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AV20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AW20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AX20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AY20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AZ20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BA20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BB20" t="n">
         <v>10</v>
@@ -5277,28 +5277,28 @@
         <v>2</v>
       </c>
       <c r="CB20" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="CC20" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04545454545454546</v>
       </c>
       <c r="CD20" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="CE20" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="CF20" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="CG20" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="CH20" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="CI20" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="CJ20" t="n">
         <v>0.1</v>
@@ -5335,13 +5335,13 @@
         <v>0.5</v>
       </c>
       <c r="DJ20" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="DK20" t="n">
-        <v>303</v>
+        <v>335</v>
       </c>
       <c r="DL20" t="n">
-        <v>5.05</v>
+        <v>5.075757575757576</v>
       </c>
     </row>
     <row r="21">
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K22" t="n">
         <v>21</v>
@@ -5635,16 +5635,16 @@
         <v>28</v>
       </c>
       <c r="P22" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Q22" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R22" t="n">
         <v>14</v>
       </c>
       <c r="S22" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="T22" t="n">
         <v>6</v>
@@ -5681,28 +5681,28 @@
         <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AU22" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AV22" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AW22" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AX22" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AY22" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AZ22" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BA22" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BB22" t="n">
         <v>33</v>
@@ -5739,28 +5739,28 @@
         <v>4</v>
       </c>
       <c r="CB22" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4</v>
       </c>
       <c r="CC22" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.2</v>
       </c>
       <c r="CD22" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="CE22" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="CF22" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.6444444444444445</v>
       </c>
       <c r="CG22" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="CH22" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3111111111111111</v>
       </c>
       <c r="CI22" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.6444444444444445</v>
       </c>
       <c r="CJ22" t="n">
         <v>0.1818181818181818</v>
@@ -5797,13 +5797,13 @@
         <v>1</v>
       </c>
       <c r="DJ22" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="DK22" t="n">
-        <v>908</v>
+        <v>940</v>
       </c>
       <c r="DL22" t="n">
-        <v>5.129943502824859</v>
+        <v>5.136612021857924</v>
       </c>
     </row>
     <row r="23">
@@ -6072,37 +6072,37 @@
         <v>7</v>
       </c>
       <c r="K24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L24" t="n">
         <v>18</v>
       </c>
       <c r="M24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P24" t="n">
         <v>12</v>
       </c>
       <c r="Q24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R24" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="S24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T24" t="n">
         <v>6</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
@@ -6128,37 +6128,37 @@
       <c r="AQ24" t="inlineStr"/>
       <c r="AR24" t="inlineStr"/>
       <c r="AS24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AU24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AV24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AW24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AY24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AZ24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BA24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BB24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BC24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD24" t="inlineStr"/>
       <c r="BE24" t="inlineStr"/>
@@ -6184,34 +6184,34 @@
       <c r="BY24" t="inlineStr"/>
       <c r="BZ24" t="inlineStr"/>
       <c r="CA24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CB24" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.72</v>
       </c>
       <c r="CC24" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.48</v>
       </c>
       <c r="CD24" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.44</v>
       </c>
       <c r="CE24" t="n">
-        <v>0.4782608695652174</v>
+        <v>0.48</v>
       </c>
       <c r="CF24" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.48</v>
       </c>
       <c r="CG24" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.4</v>
       </c>
       <c r="CH24" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.52</v>
       </c>
       <c r="CI24" t="n">
-        <v>0.7391304347826086</v>
+        <v>0.76</v>
       </c>
       <c r="CJ24" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.24</v>
       </c>
       <c r="CK24" t="n">
         <v>1</v>
@@ -6243,13 +6243,13 @@
         <v>1</v>
       </c>
       <c r="DJ24" t="n">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="DK24" t="n">
-        <v>484</v>
+        <v>560</v>
       </c>
       <c r="DL24" t="n">
-        <v>4.745098039215686</v>
+        <v>4.869565217391305</v>
       </c>
     </row>
     <row r="25">
@@ -6300,37 +6300,37 @@
         <v>18</v>
       </c>
       <c r="K25" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L25" t="n">
         <v>22</v>
       </c>
       <c r="M25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P25" t="n">
         <v>17</v>
       </c>
       <c r="Q25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R25" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="S25" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="T25" t="n">
         <v>7</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
@@ -6356,37 +6356,37 @@
       <c r="AQ25" t="inlineStr"/>
       <c r="AR25" t="inlineStr"/>
       <c r="AS25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AU25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AV25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AW25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AY25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AZ25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BA25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB25" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="BC25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD25" t="inlineStr"/>
       <c r="BE25" t="inlineStr"/>
@@ -6412,34 +6412,34 @@
       <c r="BY25" t="inlineStr"/>
       <c r="BZ25" t="inlineStr"/>
       <c r="CA25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CB25" t="n">
-        <v>0.55</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CC25" t="n">
-        <v>0.35</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CD25" t="n">
-        <v>0.525</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CE25" t="n">
-        <v>0.475</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="CF25" t="n">
-        <v>0.425</v>
+        <v>0.4047619047619048</v>
       </c>
       <c r="CG25" t="n">
-        <v>0.2</v>
+        <v>0.2619047619047619</v>
       </c>
       <c r="CH25" t="n">
-        <v>0.7</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="CI25" t="n">
-        <v>0.675</v>
+        <v>0.6904761904761905</v>
       </c>
       <c r="CJ25" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="CK25" t="n">
         <v>1</v>
@@ -6471,13 +6471,13 @@
         <v>1</v>
       </c>
       <c r="DJ25" t="n">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="DK25" t="n">
-        <v>807</v>
+        <v>883</v>
       </c>
       <c r="DL25" t="n">
-        <v>4.890909090909091</v>
+        <v>4.96067415730337</v>
       </c>
     </row>
     <row r="26">
@@ -6760,31 +6760,31 @@
         <v>6</v>
       </c>
       <c r="K27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L27" t="n">
         <v>11</v>
       </c>
       <c r="M27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O27" t="n">
         <v>10</v>
       </c>
       <c r="P27" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q27" t="n">
         <v>5</v>
       </c>
       <c r="R27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T27" t="n">
         <v>10</v>
@@ -6819,31 +6819,31 @@
         <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AU27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BB27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BC27" t="n">
         <v>2</v>
@@ -6875,31 +6875,31 @@
         <v>2</v>
       </c>
       <c r="CB27" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.55</v>
       </c>
       <c r="CC27" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="CD27" t="n">
         <v>0.5</v>
       </c>
       <c r="CE27" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5</v>
       </c>
       <c r="CF27" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.9</v>
       </c>
       <c r="CG27" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.25</v>
       </c>
       <c r="CH27" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.45</v>
       </c>
       <c r="CI27" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7</v>
       </c>
       <c r="CJ27" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5</v>
       </c>
       <c r="CK27" t="n">
         <v>0</v>
@@ -6931,13 +6931,13 @@
         <v>0</v>
       </c>
       <c r="DJ27" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="DK27" t="n">
-        <v>431</v>
+        <v>488</v>
       </c>
       <c r="DL27" t="n">
-        <v>5.011627906976744</v>
+        <v>4.979591836734694</v>
       </c>
     </row>
     <row r="28">
@@ -6984,31 +6984,31 @@
         <v>19</v>
       </c>
       <c r="K28" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L28" t="n">
         <v>23</v>
       </c>
       <c r="M28" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O28" t="n">
         <v>18</v>
       </c>
       <c r="P28" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="Q28" t="n">
         <v>17</v>
       </c>
       <c r="R28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T28" t="n">
         <v>17</v>
@@ -7047,31 +7047,31 @@
         <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AU28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AV28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AW28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AX28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AY28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AZ28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BA28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BB28" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="BC28" t="n">
         <v>4</v>
@@ -7107,31 +7107,31 @@
         <v>6</v>
       </c>
       <c r="CB28" t="n">
-        <v>0.5609756097560976</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="CC28" t="n">
-        <v>0.6341463414634146</v>
+        <v>0.6511627906976745</v>
       </c>
       <c r="CD28" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.3720930232558139</v>
       </c>
       <c r="CE28" t="n">
-        <v>0.4390243902439024</v>
+        <v>0.4186046511627907</v>
       </c>
       <c r="CF28" t="n">
-        <v>0.3414634146341464</v>
+        <v>0.4883720930232558</v>
       </c>
       <c r="CG28" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.3953488372093023</v>
       </c>
       <c r="CH28" t="n">
-        <v>0.5609756097560976</v>
+        <v>0.5581395348837209</v>
       </c>
       <c r="CI28" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.4883720930232558</v>
       </c>
       <c r="CJ28" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.5151515151515151</v>
       </c>
       <c r="CK28" t="n">
         <v>0.25</v>
@@ -7167,13 +7167,13 @@
         <v>1.166666666666667</v>
       </c>
       <c r="DJ28" t="n">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="DK28" t="n">
-        <v>919</v>
+        <v>976</v>
       </c>
       <c r="DL28" t="n">
-        <v>5.021857923497268</v>
+        <v>5.005128205128205</v>
       </c>
     </row>
     <row r="29">
@@ -7221,28 +7221,28 @@
         </is>
       </c>
       <c r="J29" t="n">
+        <v>11</v>
+      </c>
+      <c r="K29" t="n">
+        <v>11</v>
+      </c>
+      <c r="L29" t="n">
+        <v>4</v>
+      </c>
+      <c r="M29" t="n">
         <v>10</v>
-      </c>
-      <c r="K29" t="n">
-        <v>10</v>
-      </c>
-      <c r="L29" t="n">
-        <v>2</v>
-      </c>
-      <c r="M29" t="n">
-        <v>8</v>
       </c>
       <c r="N29" t="n">
         <v>10</v>
       </c>
       <c r="O29" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P29" t="n">
         <v>8</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R29" t="n">
         <v>12</v>
@@ -7283,31 +7283,31 @@
         <v>6</v>
       </c>
       <c r="AT29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AU29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AV29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AZ29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC29" t="n">
         <v>2</v>
@@ -7339,31 +7339,31 @@
         <v>2</v>
       </c>
       <c r="CB29" t="n">
-        <v>0.1</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="CC29" t="n">
-        <v>0.4</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="CD29" t="n">
-        <v>0.5</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="CE29" t="n">
-        <v>0.6</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="CF29" t="n">
-        <v>0.4</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CG29" t="n">
-        <v>0.4</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="CH29" t="n">
-        <v>0.6</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="CI29" t="n">
-        <v>0.8</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="CJ29" t="n">
-        <v>0.9</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="CK29" t="n">
         <v>3</v>
@@ -7395,13 +7395,13 @@
         <v>3</v>
       </c>
       <c r="DJ29" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="DK29" t="n">
-        <v>537</v>
+        <v>565</v>
       </c>
       <c r="DL29" t="n">
-        <v>5.712765957446808</v>
+        <v>5.485436893203883</v>
       </c>
     </row>
     <row r="30">
@@ -7683,28 +7683,28 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L31" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N31" t="n">
         <v>22</v>
       </c>
       <c r="O31" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="P31" t="n">
         <v>16</v>
       </c>
       <c r="Q31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R31" t="n">
         <v>32</v>
@@ -7747,31 +7747,31 @@
         <v>6</v>
       </c>
       <c r="AT31" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AU31" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AV31" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AW31" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AX31" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AY31" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AZ31" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BA31" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BB31" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BC31" t="n">
         <v>3</v>
@@ -7805,31 +7805,31 @@
         <v>4</v>
       </c>
       <c r="CB31" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.3953488372093023</v>
       </c>
       <c r="CC31" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.4418604651162791</v>
       </c>
       <c r="CD31" t="n">
-        <v>0.5365853658536586</v>
+        <v>0.5116279069767442</v>
       </c>
       <c r="CE31" t="n">
-        <v>0.6829268292682927</v>
+        <v>0.7441860465116279</v>
       </c>
       <c r="CF31" t="n">
-        <v>0.3902439024390244</v>
+        <v>0.3720930232558139</v>
       </c>
       <c r="CG31" t="n">
-        <v>0.5853658536585366</v>
+        <v>0.5813953488372093</v>
       </c>
       <c r="CH31" t="n">
-        <v>0.7804878048780488</v>
+        <v>0.7441860465116279</v>
       </c>
       <c r="CI31" t="n">
-        <v>0.7804878048780488</v>
+        <v>0.7441860465116279</v>
       </c>
       <c r="CJ31" t="n">
-        <v>0.3548387096774194</v>
+        <v>0.34375</v>
       </c>
       <c r="CK31" t="n">
         <v>2</v>
@@ -7863,13 +7863,13 @@
         <v>1.5</v>
       </c>
       <c r="DJ31" t="n">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="DK31" t="n">
-        <v>1090</v>
+        <v>1118</v>
       </c>
       <c r="DL31" t="n">
-        <v>5.29126213592233</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="32">
@@ -7917,13 +7917,13 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L32" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M32" t="n">
         <v>11</v>
@@ -7932,16 +7932,16 @@
         <v>10</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P32" t="n">
         <v>17</v>
       </c>
       <c r="Q32" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S32" t="n">
         <v>16</v>
@@ -7981,31 +7981,31 @@
         <v>4</v>
       </c>
       <c r="AT32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AU32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AV32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AW32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AX32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AY32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AZ32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC32" t="n">
         <v>3</v>
@@ -8039,31 +8039,31 @@
         <v>4</v>
       </c>
       <c r="CB32" t="n">
-        <v>0.625</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="CC32" t="n">
-        <v>0.6875</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="CD32" t="n">
-        <v>0.625</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="CE32" t="n">
-        <v>0.1875</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="CF32" t="n">
-        <v>1.0625</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="CG32" t="n">
-        <v>0.375</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="CH32" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="CI32" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="CJ32" t="n">
-        <v>0.6</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="CK32" t="n">
         <v>1.333333333333333</v>
@@ -8097,13 +8097,13 @@
         <v>1</v>
       </c>
       <c r="DJ32" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="DK32" t="n">
-        <v>529</v>
+        <v>556</v>
       </c>
       <c r="DL32" t="n">
-        <v>5.186274509803922</v>
+        <v>5.054545454545455</v>
       </c>
     </row>
     <row r="33">
@@ -8385,13 +8385,13 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K34" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L34" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M34" t="n">
         <v>15</v>
@@ -8400,16 +8400,16 @@
         <v>19</v>
       </c>
       <c r="O34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P34" t="n">
         <v>25</v>
       </c>
       <c r="Q34" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R34" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S34" t="n">
         <v>32</v>
@@ -8449,31 +8449,31 @@
         <v>6</v>
       </c>
       <c r="AT34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AU34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AV34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AW34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AY34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AZ34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BA34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB34" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BC34" t="n">
         <v>4</v>
@@ -8507,31 +8507,31 @@
         <v>6</v>
       </c>
       <c r="CB34" t="n">
-        <v>0.525</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="CC34" t="n">
-        <v>0.375</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="CD34" t="n">
-        <v>0.475</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="CE34" t="n">
-        <v>0.25</v>
+        <v>0.2619047619047619</v>
       </c>
       <c r="CF34" t="n">
-        <v>0.625</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="CG34" t="n">
-        <v>0.4</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CH34" t="n">
-        <v>0.6</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="CI34" t="n">
-        <v>0.8</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="CJ34" t="n">
-        <v>0.3235294117647059</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="CK34" t="n">
         <v>1.25</v>
@@ -8565,13 +8565,13 @@
         <v>1</v>
       </c>
       <c r="DJ34" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="DK34" t="n">
-        <v>953</v>
+        <v>980</v>
       </c>
       <c r="DL34" t="n">
-        <v>5.236263736263736</v>
+        <v>5.157894736842105</v>
       </c>
     </row>
     <row r="35">
@@ -8619,37 +8619,37 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K35" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M35" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N35" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O35" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R35" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S35" t="n">
         <v>9</v>
       </c>
       <c r="T35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U35" t="n">
         <v>3</v>
@@ -8681,34 +8681,34 @@
         <v>3</v>
       </c>
       <c r="AT35" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AU35" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AV35" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AW35" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AX35" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AY35" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AZ35" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BA35" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BB35" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BC35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD35" t="inlineStr"/>
       <c r="BE35" t="inlineStr"/>
@@ -8734,37 +8734,37 @@
       <c r="BY35" t="inlineStr"/>
       <c r="BZ35" t="inlineStr"/>
       <c r="CA35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CB35" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.5</v>
       </c>
       <c r="CC35" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="CD35" t="n">
-        <v>1.052631578947368</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="CE35" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="CF35" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="CG35" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="CH35" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="CI35" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="CJ35" t="n">
-        <v>0.5</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="CK35" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="CL35" t="inlineStr"/>
       <c r="CM35" t="inlineStr"/>
@@ -8790,16 +8790,16 @@
       <c r="DG35" t="inlineStr"/>
       <c r="DH35" t="inlineStr"/>
       <c r="DI35" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="DJ35" t="n">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="DK35" t="n">
-        <v>483</v>
+        <v>556</v>
       </c>
       <c r="DL35" t="n">
-        <v>4.390909090909091</v>
+        <v>4.412698412698413</v>
       </c>
     </row>
     <row r="36">
@@ -9075,37 +9075,37 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K37" t="n">
+        <v>27</v>
+      </c>
+      <c r="L37" t="n">
         <v>25</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>24</v>
       </c>
-      <c r="M37" t="n">
-        <v>20</v>
-      </c>
       <c r="N37" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O37" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="P37" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R37" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S37" t="n">
         <v>16</v>
       </c>
       <c r="T37" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U37" t="n">
         <v>6</v>
@@ -9137,34 +9137,34 @@
         <v>6</v>
       </c>
       <c r="AT37" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AU37" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AV37" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AW37" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AX37" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AY37" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AZ37" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="BA37" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="BB37" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="BC37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD37" t="inlineStr"/>
       <c r="BE37" t="inlineStr"/>
@@ -9190,37 +9190,37 @@
       <c r="BY37" t="inlineStr"/>
       <c r="BZ37" t="inlineStr"/>
       <c r="CA37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CB37" t="n">
-        <v>0.5853658536585366</v>
+        <v>0.5681818181818182</v>
       </c>
       <c r="CC37" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="CD37" t="n">
-        <v>0.7560975609756098</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="CE37" t="n">
-        <v>0.6097560975609756</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="CF37" t="n">
-        <v>1.219512195121951</v>
+        <v>1.159090909090909</v>
       </c>
       <c r="CG37" t="n">
-        <v>0.2439024390243902</v>
+        <v>0.25</v>
       </c>
       <c r="CH37" t="n">
-        <v>0.8048780487804879</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="CI37" t="n">
-        <v>0.3902439024390244</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CJ37" t="n">
-        <v>0.21875</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CK37" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="CL37" t="inlineStr"/>
       <c r="CM37" t="inlineStr"/>
@@ -9246,16 +9246,16 @@
       <c r="DG37" t="inlineStr"/>
       <c r="DH37" t="inlineStr"/>
       <c r="DI37" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="DJ37" t="n">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="DK37" t="n">
-        <v>1049</v>
+        <v>1122</v>
       </c>
       <c r="DL37" t="n">
-        <v>4.560869565217391</v>
+        <v>4.560975609756097</v>
       </c>
     </row>
     <row r="38">
@@ -9540,28 +9540,28 @@
         <v>8</v>
       </c>
       <c r="K39" t="n">
+        <v>18</v>
+      </c>
+      <c r="L39" t="n">
         <v>15</v>
       </c>
-      <c r="L39" t="n">
-        <v>13</v>
-      </c>
       <c r="M39" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N39" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="O39" t="n">
         <v>8</v>
       </c>
       <c r="P39" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q39" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R39" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S39" t="n">
         <v>19</v>
@@ -9599,31 +9599,31 @@
         <v>4</v>
       </c>
       <c r="AT39" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AU39" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AV39" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AW39" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AX39" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AY39" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AZ39" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BA39" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BB39" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BC39" t="n">
         <v>2</v>
@@ -9655,31 +9655,31 @@
         <v>2</v>
       </c>
       <c r="CB39" t="n">
-        <v>0.5652173913043478</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="CC39" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="CD39" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="CE39" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="CF39" t="n">
-        <v>0.8260869565217391</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="CG39" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="CH39" t="n">
-        <v>0.7391304347826086</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="CI39" t="n">
-        <v>0.8260869565217391</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="CJ39" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="CK39" t="n">
         <v>2</v>
@@ -9711,13 +9711,13 @@
         <v>2</v>
       </c>
       <c r="DJ39" t="n">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="DK39" t="n">
-        <v>712</v>
+        <v>757</v>
       </c>
       <c r="DL39" t="n">
-        <v>5.353383458646617</v>
+        <v>5.149659863945578</v>
       </c>
     </row>
     <row r="40">
@@ -9768,28 +9768,28 @@
         <v>16</v>
       </c>
       <c r="K40" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L40" t="n">
+        <v>21</v>
+      </c>
+      <c r="M40" t="n">
         <v>19</v>
       </c>
-      <c r="M40" t="n">
-        <v>17</v>
-      </c>
       <c r="N40" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="O40" t="n">
         <v>17</v>
       </c>
       <c r="P40" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q40" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R40" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S40" t="n">
         <v>29</v>
@@ -9829,31 +9829,31 @@
         <v>8</v>
       </c>
       <c r="AT40" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AU40" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AV40" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AW40" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AX40" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AY40" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AZ40" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="BA40" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="BB40" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="BC40" t="n">
         <v>5</v>
@@ -9887,31 +9887,31 @@
         <v>6</v>
       </c>
       <c r="CB40" t="n">
-        <v>0.4634146341463415</v>
+        <v>0.4772727272727273</v>
       </c>
       <c r="CC40" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.4318181818181818</v>
       </c>
       <c r="CD40" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="CE40" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.3863636363636364</v>
       </c>
       <c r="CF40" t="n">
-        <v>0.5853658536585366</v>
+        <v>0.5681818181818182</v>
       </c>
       <c r="CG40" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.4772727272727273</v>
       </c>
       <c r="CH40" t="n">
-        <v>0.6585365853658537</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="CI40" t="n">
-        <v>0.7073170731707317</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="CJ40" t="n">
-        <v>0.5142857142857142</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="CK40" t="n">
         <v>1.6</v>
@@ -9945,13 +9945,13 @@
         <v>1.333333333333333</v>
       </c>
       <c r="DJ40" t="n">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="DK40" t="n">
-        <v>1087</v>
+        <v>1132</v>
       </c>
       <c r="DL40" t="n">
-        <v>5.407960199004975</v>
+        <v>5.265116279069767</v>
       </c>
     </row>
     <row r="41">
@@ -10227,40 +10227,40 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L42" t="n">
         <v>8</v>
       </c>
       <c r="M42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N42" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O42" t="n">
         <v>8</v>
       </c>
       <c r="P42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R42" t="n">
         <v>3</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T42" t="n">
         <v>6</v>
       </c>
       <c r="U42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V42" t="n">
         <v>1</v>
@@ -10288,37 +10288,37 @@
       <c r="AQ42" t="inlineStr"/>
       <c r="AR42" t="inlineStr"/>
       <c r="AS42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>21</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC42" t="n">
         <v>3</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>18</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>18</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>2</v>
       </c>
       <c r="BD42" t="n">
         <v>1</v>
@@ -10346,34 +10346,34 @@
       <c r="BY42" t="inlineStr"/>
       <c r="BZ42" t="inlineStr"/>
       <c r="CA42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CB42" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CC42" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="CD42" t="n">
-        <v>1.055555555555556</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="CE42" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CF42" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CG42" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CH42" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="CI42" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CJ42" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CK42" t="n">
         <v>1</v>
@@ -10407,13 +10407,13 @@
         <v>1</v>
       </c>
       <c r="DJ42" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="DK42" t="n">
-        <v>375</v>
+        <v>415</v>
       </c>
       <c r="DL42" t="n">
-        <v>4.807692307692307</v>
+        <v>4.882352941176471</v>
       </c>
     </row>
     <row r="43">
@@ -10461,40 +10461,40 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K43" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L43" t="n">
         <v>22</v>
       </c>
       <c r="M43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N43" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O43" t="n">
         <v>16</v>
       </c>
       <c r="P43" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q43" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R43" t="n">
         <v>11</v>
       </c>
       <c r="S43" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T43" t="n">
         <v>14</v>
       </c>
       <c r="U43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V43" t="n">
         <v>1</v>
@@ -10522,37 +10522,37 @@
       <c r="AQ43" t="inlineStr"/>
       <c r="AR43" t="inlineStr"/>
       <c r="AS43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT43" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AU43" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AV43" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AW43" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AX43" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AY43" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AZ43" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="BA43" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="BB43" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="BC43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD43" t="n">
         <v>1</v>
@@ -10580,37 +10580,37 @@
       <c r="BY43" t="inlineStr"/>
       <c r="BZ43" t="inlineStr"/>
       <c r="CA43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CB43" t="n">
-        <v>0.5365853658536586</v>
+        <v>0.5</v>
       </c>
       <c r="CC43" t="n">
-        <v>0.2926829268292683</v>
+        <v>0.2954545454545455</v>
       </c>
       <c r="CD43" t="n">
-        <v>0.6097560975609756</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="CE43" t="n">
-        <v>0.3902439024390244</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CF43" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CG43" t="n">
-        <v>0.5609756097560976</v>
+        <v>0.5681818181818182</v>
       </c>
       <c r="CH43" t="n">
-        <v>0.2682926829268293</v>
+        <v>0.25</v>
       </c>
       <c r="CI43" t="n">
-        <v>0.4390243902439024</v>
+        <v>0.4318181818181818</v>
       </c>
       <c r="CJ43" t="n">
-        <v>0.4375</v>
+        <v>0.4</v>
       </c>
       <c r="CK43" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="CL43" t="n">
         <v>1</v>
@@ -10638,16 +10638,16 @@
       <c r="DG43" t="inlineStr"/>
       <c r="DH43" t="inlineStr"/>
       <c r="DI43" t="n">
-        <v>1.4</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="DJ43" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="DK43" t="n">
-        <v>816</v>
+        <v>856</v>
       </c>
       <c r="DL43" t="n">
-        <v>4.945454545454545</v>
+        <v>4.976744186046512</v>
       </c>
     </row>
     <row r="44">
@@ -10695,16 +10695,16 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L44" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N44" t="n">
         <v>5</v>
@@ -10716,16 +10716,16 @@
         <v>8</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
@@ -10753,31 +10753,31 @@
       <c r="AR44" t="inlineStr"/>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AU44" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AV44" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AW44" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX44" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AY44" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AZ44" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA44" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BB44" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BC44" t="inlineStr"/>
       <c r="BD44" t="inlineStr"/>
@@ -10807,31 +10807,31 @@
         <v>0</v>
       </c>
       <c r="CB44" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CC44" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CD44" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="CE44" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CF44" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CG44" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="CH44" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="CI44" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="CJ44" t="n">
-        <v>1</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="CK44" t="inlineStr"/>
       <c r="CL44" t="inlineStr"/>
@@ -10859,13 +10859,13 @@
       <c r="DH44" t="inlineStr"/>
       <c r="DI44" t="inlineStr"/>
       <c r="DJ44" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="DK44" t="n">
-        <v>219</v>
+        <v>262</v>
       </c>
       <c r="DL44" t="n">
-        <v>4.469387755102041</v>
+        <v>4.440677966101695</v>
       </c>
     </row>
     <row r="45">
@@ -11141,16 +11141,16 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K46" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L46" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M46" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N46" t="n">
         <v>10</v>
@@ -11162,16 +11162,16 @@
         <v>26</v>
       </c>
       <c r="Q46" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R46" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S46" t="n">
         <v>14</v>
       </c>
       <c r="T46" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="U46" t="n">
         <v>1</v>
@@ -11203,31 +11203,31 @@
         <v>1</v>
       </c>
       <c r="AT46" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AU46" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AV46" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AW46" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AX46" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AY46" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AZ46" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="BA46" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="BB46" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="BC46" t="n">
         <v>1</v>
@@ -11259,31 +11259,31 @@
         <v>1</v>
       </c>
       <c r="CB46" t="n">
-        <v>0.725</v>
+        <v>0.6976744186046512</v>
       </c>
       <c r="CC46" t="n">
-        <v>0.325</v>
+        <v>0.3255813953488372</v>
       </c>
       <c r="CD46" t="n">
-        <v>0.25</v>
+        <v>0.2325581395348837</v>
       </c>
       <c r="CE46" t="n">
-        <v>0.275</v>
+        <v>0.2558139534883721</v>
       </c>
       <c r="CF46" t="n">
-        <v>0.65</v>
+        <v>0.6046511627906976</v>
       </c>
       <c r="CG46" t="n">
-        <v>0.475</v>
+        <v>0.4651162790697674</v>
       </c>
       <c r="CH46" t="n">
-        <v>0.35</v>
+        <v>0.3488372093023256</v>
       </c>
       <c r="CI46" t="n">
-        <v>0.35</v>
+        <v>0.3255813953488372</v>
       </c>
       <c r="CJ46" t="n">
-        <v>0.4838709677419355</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="CK46" t="n">
         <v>1</v>
@@ -11315,13 +11315,13 @@
         <v>1</v>
       </c>
       <c r="DJ46" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="DK46" t="n">
-        <v>728</v>
+        <v>771</v>
       </c>
       <c r="DL46" t="n">
-        <v>4.789473684210527</v>
+        <v>4.75925925925926</v>
       </c>
     </row>
     <row r="47">
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K47" t="n">
         <v>6</v>
@@ -11384,10 +11384,10 @@
         <v>4</v>
       </c>
       <c r="O47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q47" t="n">
         <v>6</v>
@@ -11431,28 +11431,28 @@
         <v>4</v>
       </c>
       <c r="AT47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AU47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BB47" t="n">
         <v>8</v>
@@ -11487,28 +11487,28 @@
         <v>1</v>
       </c>
       <c r="CB47" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.15</v>
       </c>
       <c r="CC47" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4</v>
       </c>
       <c r="CD47" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2</v>
       </c>
       <c r="CE47" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.5</v>
       </c>
       <c r="CF47" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.45</v>
       </c>
       <c r="CG47" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="CH47" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.05</v>
       </c>
       <c r="CI47" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8</v>
       </c>
       <c r="CJ47" t="n">
         <v>0.625</v>
@@ -11543,13 +11543,13 @@
         <v>4</v>
       </c>
       <c r="DJ47" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="DK47" t="n">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="DL47" t="n">
-        <v>5.523076923076923</v>
+        <v>5.470588235294118</v>
       </c>
     </row>
     <row r="48">
@@ -11825,7 +11825,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K49" t="n">
         <v>13</v>
@@ -11840,10 +11840,10 @@
         <v>10</v>
       </c>
       <c r="O49" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q49" t="n">
         <v>17</v>
@@ -11887,28 +11887,28 @@
         <v>5</v>
       </c>
       <c r="AT49" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AU49" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AV49" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AW49" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AX49" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AY49" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AZ49" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BA49" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BB49" t="n">
         <v>31</v>
@@ -11943,28 +11943,28 @@
         <v>2</v>
       </c>
       <c r="CB49" t="n">
-        <v>0.6097560975609756</v>
+        <v>0.5813953488372093</v>
       </c>
       <c r="CC49" t="n">
-        <v>0.3902439024390244</v>
+        <v>0.3720930232558139</v>
       </c>
       <c r="CD49" t="n">
-        <v>0.2439024390243902</v>
+        <v>0.2325581395348837</v>
       </c>
       <c r="CE49" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.4418604651162791</v>
       </c>
       <c r="CF49" t="n">
-        <v>0.3170731707317073</v>
+        <v>0.3255813953488372</v>
       </c>
       <c r="CG49" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.3953488372093023</v>
       </c>
       <c r="CH49" t="n">
-        <v>0.1219512195121951</v>
+        <v>0.1162790697674419</v>
       </c>
       <c r="CI49" t="n">
-        <v>0.5609756097560976</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="CJ49" t="n">
         <v>0.2580645161290323</v>
@@ -11999,13 +11999,13 @@
         <v>2.5</v>
       </c>
       <c r="DJ49" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="DK49" t="n">
-        <v>663</v>
+        <v>676</v>
       </c>
       <c r="DL49" t="n">
-        <v>4.702127659574468</v>
+        <v>4.694444444444445</v>
       </c>
     </row>
     <row r="50">
@@ -12281,25 +12281,25 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L51" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M51" t="n">
         <v>7</v>
       </c>
       <c r="N51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
       </c>
       <c r="P51" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Q51" t="n">
         <v>14</v>
@@ -12308,7 +12308,7 @@
         <v>8</v>
       </c>
       <c r="S51" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T51" t="n">
         <v>5</v>
@@ -12339,31 +12339,31 @@
       <c r="AR51" t="inlineStr"/>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AU51" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AV51" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AW51" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX51" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY51" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AZ51" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA51" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BB51" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC51" t="inlineStr"/>
       <c r="BD51" t="inlineStr"/>
@@ -12393,31 +12393,31 @@
         <v>0</v>
       </c>
       <c r="CB51" t="n">
-        <v>0.8</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="CC51" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="CD51" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="CE51" t="n">
-        <v>0.2</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="CF51" t="n">
-        <v>0.6</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="CG51" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="CH51" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="CI51" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="CJ51" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="CK51" t="inlineStr"/>
       <c r="CL51" t="inlineStr"/>
@@ -12445,13 +12445,13 @@
       <c r="DH51" t="inlineStr"/>
       <c r="DI51" t="inlineStr"/>
       <c r="DJ51" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="DK51" t="n">
-        <v>401</v>
+        <v>438</v>
       </c>
       <c r="DL51" t="n">
-        <v>5.075949367088608</v>
+        <v>5.03448275862069</v>
       </c>
     </row>
     <row r="52">
@@ -12499,25 +12499,25 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K52" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L52" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M52" t="n">
         <v>8</v>
       </c>
       <c r="N52" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O52" t="n">
         <v>23</v>
       </c>
       <c r="P52" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Q52" t="n">
         <v>20</v>
@@ -12526,7 +12526,7 @@
         <v>13</v>
       </c>
       <c r="S52" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T52" t="n">
         <v>9</v>
@@ -12561,31 +12561,31 @@
         <v>7</v>
       </c>
       <c r="AT52" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AU52" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AV52" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AW52" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AX52" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AY52" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AZ52" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BA52" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BB52" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="BC52" t="n">
         <v>2</v>
@@ -12617,31 +12617,31 @@
         <v>2</v>
       </c>
       <c r="CB52" t="n">
-        <v>0.8780487804878049</v>
+        <v>0.8604651162790697</v>
       </c>
       <c r="CC52" t="n">
-        <v>0.1951219512195122</v>
+        <v>0.186046511627907</v>
       </c>
       <c r="CD52" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.4883720930232558</v>
       </c>
       <c r="CE52" t="n">
-        <v>0.5609756097560976</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="CF52" t="n">
-        <v>0.4634146341463415</v>
+        <v>0.5581395348837209</v>
       </c>
       <c r="CG52" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.4651162790697674</v>
       </c>
       <c r="CH52" t="n">
-        <v>0.3170731707317073</v>
+        <v>0.3023255813953488</v>
       </c>
       <c r="CI52" t="n">
-        <v>0.4634146341463415</v>
+        <v>0.4651162790697674</v>
       </c>
       <c r="CJ52" t="n">
-        <v>0.3103448275862069</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="CK52" t="n">
         <v>3.5</v>
@@ -12673,13 +12673,13 @@
         <v>3.5</v>
       </c>
       <c r="DJ52" t="n">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="DK52" t="n">
-        <v>813</v>
+        <v>850</v>
       </c>
       <c r="DL52" t="n">
-        <v>4.541899441340782</v>
+        <v>4.545454545454546</v>
       </c>
     </row>
     <row r="53">
@@ -12723,16 +12723,16 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K53" t="n">
         <v>12</v>
       </c>
       <c r="L53" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M53" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N53" t="n">
         <v>12</v>
@@ -12787,34 +12787,34 @@
         <v>4</v>
       </c>
       <c r="AT53" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AU53" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV53" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW53" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX53" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY53" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ53" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA53" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BB53" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD53" t="n">
         <v>1</v>
@@ -12842,37 +12842,37 @@
       <c r="BY53" t="inlineStr"/>
       <c r="BZ53" t="inlineStr"/>
       <c r="CA53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CB53" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.45</v>
       </c>
       <c r="CC53" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="CD53" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="CE53" t="n">
         <v>0.5</v>
       </c>
-      <c r="CD53" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="CE53" t="n">
-        <v>0.5555555555555556</v>
-      </c>
       <c r="CF53" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.25</v>
       </c>
       <c r="CG53" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4</v>
       </c>
       <c r="CH53" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.55</v>
       </c>
       <c r="CI53" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="CJ53" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4</v>
       </c>
       <c r="CK53" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="CL53" t="n">
         <v>1</v>
@@ -12900,16 +12900,16 @@
       <c r="DG53" t="inlineStr"/>
       <c r="DH53" t="inlineStr"/>
       <c r="DI53" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="DJ53" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="DK53" t="n">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="DL53" t="n">
-        <v>5.177777777777778</v>
+        <v>5.021276595744681</v>
       </c>
     </row>
     <row r="54">
@@ -13183,16 +13183,16 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K55" t="n">
         <v>25</v>
       </c>
       <c r="L55" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M55" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N55" t="n">
         <v>22</v>
@@ -13247,34 +13247,34 @@
         <v>7</v>
       </c>
       <c r="AT55" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AU55" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AV55" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AW55" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX55" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AY55" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AZ55" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BA55" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB55" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="BC55" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD55" t="n">
         <v>2</v>
@@ -13302,37 +13302,37 @@
       <c r="BY55" t="inlineStr"/>
       <c r="BZ55" t="inlineStr"/>
       <c r="CA55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CB55" t="n">
-        <v>0.525</v>
+        <v>0.5476190476190477</v>
       </c>
       <c r="CC55" t="n">
-        <v>0.425</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="CD55" t="n">
-        <v>0.55</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CE55" t="n">
-        <v>0.35</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CF55" t="n">
-        <v>0.15</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="CG55" t="n">
-        <v>0.675</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="CH55" t="n">
-        <v>0.425</v>
+        <v>0.4047619047619048</v>
       </c>
       <c r="CI55" t="n">
-        <v>0.7</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CJ55" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2162162162162162</v>
       </c>
       <c r="CK55" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.625</v>
       </c>
       <c r="CL55" t="n">
         <v>1</v>
@@ -13360,16 +13360,16 @@
       <c r="DG55" t="inlineStr"/>
       <c r="DH55" t="inlineStr"/>
       <c r="DI55" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7</v>
       </c>
       <c r="DJ55" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="DK55" t="n">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="DL55" t="n">
-        <v>5.035294117647059</v>
+        <v>4.954022988505747</v>
       </c>
     </row>
     <row r="56">
@@ -13643,16 +13643,16 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L57" t="n">
         <v>9</v>
       </c>
       <c r="M57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N57" t="n">
         <v>14</v>
@@ -13664,10 +13664,10 @@
         <v>7</v>
       </c>
       <c r="Q57" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -13705,31 +13705,31 @@
         <v>2</v>
       </c>
       <c r="AT57" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AU57" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV57" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW57" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX57" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY57" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ57" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA57" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB57" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BC57" t="n">
         <v>2</v>
@@ -13761,31 +13761,31 @@
         <v>2</v>
       </c>
       <c r="CB57" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="CC57" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="CD57" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="CE57" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="CF57" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="CG57" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="CH57" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="CI57" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="CJ57" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="CK57" t="n">
         <v>1</v>
@@ -13817,13 +13817,13 @@
         <v>1</v>
       </c>
       <c r="DJ57" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="DK57" t="n">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="DL57" t="n">
-        <v>4.613333333333333</v>
+        <v>4.645569620253164</v>
       </c>
     </row>
     <row r="58">
@@ -13867,16 +13867,16 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K58" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L58" t="n">
         <v>25</v>
       </c>
       <c r="M58" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N58" t="n">
         <v>34</v>
@@ -13888,10 +13888,10 @@
         <v>22</v>
       </c>
       <c r="Q58" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R58" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S58" t="n">
         <v>19</v>
@@ -13931,31 +13931,31 @@
         <v>6</v>
       </c>
       <c r="AT58" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AU58" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AV58" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AW58" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AX58" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AY58" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AZ58" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BA58" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BB58" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC58" t="n">
         <v>6</v>
@@ -13989,31 +13989,31 @@
         <v>7</v>
       </c>
       <c r="CB58" t="n">
-        <v>0.6097560975609756</v>
+        <v>0.5813953488372093</v>
       </c>
       <c r="CC58" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.4186046511627907</v>
       </c>
       <c r="CD58" t="n">
-        <v>0.8292682926829268</v>
+        <v>0.7906976744186046</v>
       </c>
       <c r="CE58" t="n">
-        <v>0.4634146341463415</v>
+        <v>0.4418604651162791</v>
       </c>
       <c r="CF58" t="n">
-        <v>0.5365853658536586</v>
+        <v>0.5116279069767442</v>
       </c>
       <c r="CG58" t="n">
-        <v>0.7317073170731707</v>
+        <v>0.7441860465116279</v>
       </c>
       <c r="CH58" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.3720930232558139</v>
       </c>
       <c r="CI58" t="n">
-        <v>0.4634146341463415</v>
+        <v>0.4418604651162791</v>
       </c>
       <c r="CJ58" t="n">
-        <v>0.34375</v>
+        <v>0.3235294117647059</v>
       </c>
       <c r="CK58" t="n">
         <v>0.6666666666666666</v>
@@ -14047,13 +14047,13 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="DJ58" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="DK58" t="n">
-        <v>945</v>
+        <v>966</v>
       </c>
       <c r="DL58" t="n">
-        <v>4.678217821782178</v>
+        <v>4.689320388349515</v>
       </c>
     </row>
     <row r="59">
@@ -14341,22 +14341,22 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K60" t="n">
         <v>9</v>
       </c>
       <c r="L60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M60" t="n">
         <v>8</v>
       </c>
       <c r="N60" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O60" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P60" t="n">
         <v>11</v>
@@ -14371,10 +14371,10 @@
         <v>13</v>
       </c>
       <c r="T60" t="n">
+        <v>6</v>
+      </c>
+      <c r="U60" t="n">
         <v>4</v>
-      </c>
-      <c r="U60" t="n">
-        <v>3</v>
       </c>
       <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr"/>
@@ -14400,37 +14400,37 @@
       <c r="AQ60" t="inlineStr"/>
       <c r="AR60" t="inlineStr"/>
       <c r="AS60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AU60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AV60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AW60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AX60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AY60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AZ60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BB60" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD60" t="inlineStr"/>
       <c r="BE60" t="inlineStr"/>
@@ -14456,37 +14456,37 @@
       <c r="BY60" t="inlineStr"/>
       <c r="BZ60" t="inlineStr"/>
       <c r="CA60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CB60" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.625</v>
       </c>
       <c r="CC60" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CD60" t="n">
         <v>0.5</v>
       </c>
       <c r="CE60" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="CF60" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="CG60" t="n">
-        <v>0.8636363636363636</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="CH60" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CI60" t="n">
-        <v>0.5909090909090909</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="CJ60" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="CK60" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="CL60" t="inlineStr"/>
       <c r="CM60" t="inlineStr"/>
@@ -14512,16 +14512,16 @@
       <c r="DG60" t="inlineStr"/>
       <c r="DH60" t="inlineStr"/>
       <c r="DI60" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="DJ60" t="n">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="DK60" t="n">
-        <v>526</v>
+        <v>570</v>
       </c>
       <c r="DL60" t="n">
-        <v>5.009523809523809</v>
+        <v>4.913793103448276</v>
       </c>
     </row>
     <row r="61">
@@ -14569,22 +14569,22 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K61" t="n">
         <v>22</v>
       </c>
       <c r="L61" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M61" t="n">
         <v>28</v>
       </c>
       <c r="N61" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O61" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P61" t="n">
         <v>26</v>
@@ -14599,10 +14599,10 @@
         <v>29</v>
       </c>
       <c r="T61" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="U61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V61" t="n">
         <v>0</v>
@@ -14632,37 +14632,37 @@
       <c r="AQ61" t="inlineStr"/>
       <c r="AR61" t="inlineStr"/>
       <c r="AS61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT61" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AU61" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AV61" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AW61" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AX61" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AY61" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AZ61" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BA61" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BB61" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD61" t="n">
         <v>1</v>
@@ -14692,37 +14692,37 @@
       <c r="BY61" t="inlineStr"/>
       <c r="BZ61" t="inlineStr"/>
       <c r="CA61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CB61" t="n">
-        <v>0.4634146341463415</v>
+        <v>0.5581395348837209</v>
       </c>
       <c r="CC61" t="n">
-        <v>0.6829268292682927</v>
+        <v>0.6511627906976745</v>
       </c>
       <c r="CD61" t="n">
-        <v>0.5853658536585366</v>
+        <v>0.5813953488372093</v>
       </c>
       <c r="CE61" t="n">
-        <v>0.8048780487804879</v>
+        <v>0.813953488372093</v>
       </c>
       <c r="CF61" t="n">
-        <v>0.6341463414634146</v>
+        <v>0.6046511627906976</v>
       </c>
       <c r="CG61" t="n">
-        <v>0.7560975609756098</v>
+        <v>0.7209302325581395</v>
       </c>
       <c r="CH61" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.4651162790697674</v>
       </c>
       <c r="CI61" t="n">
-        <v>0.7073170731707317</v>
+        <v>0.6744186046511628</v>
       </c>
       <c r="CJ61" t="n">
-        <v>0.3823529411764706</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="CK61" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="CL61" t="n">
         <v>0</v>
@@ -14752,16 +14752,16 @@
       <c r="DG61" t="inlineStr"/>
       <c r="DH61" t="inlineStr"/>
       <c r="DI61" t="n">
-        <v>0.75</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="DJ61" t="n">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="DK61" t="n">
-        <v>1146</v>
+        <v>1190</v>
       </c>
       <c r="DL61" t="n">
-        <v>4.982608695652174</v>
+        <v>4.937759336099585</v>
       </c>
     </row>
     <row r="62">
@@ -15046,7 +15046,7 @@
         <v>9</v>
       </c>
       <c r="K63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L63" t="n">
         <v>8</v>
@@ -15055,13 +15055,13 @@
         <v>10</v>
       </c>
       <c r="N63" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P63" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q63" t="n">
         <v>14</v>
@@ -15070,7 +15070,7 @@
         <v>9</v>
       </c>
       <c r="S63" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
@@ -15101,31 +15101,31 @@
       <c r="AR63" t="inlineStr"/>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AU63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BB63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BC63" t="inlineStr"/>
       <c r="BD63" t="inlineStr"/>
@@ -15155,31 +15155,31 @@
         <v>0</v>
       </c>
       <c r="CB63" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4</v>
       </c>
       <c r="CC63" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5</v>
       </c>
       <c r="CD63" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.55</v>
       </c>
       <c r="CE63" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.6</v>
       </c>
       <c r="CF63" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.85</v>
       </c>
       <c r="CG63" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7</v>
       </c>
       <c r="CH63" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="CI63" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.7</v>
       </c>
       <c r="CJ63" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.05</v>
       </c>
       <c r="CK63" t="inlineStr"/>
       <c r="CL63" t="inlineStr"/>
@@ -15207,13 +15207,13 @@
       <c r="DH63" t="inlineStr"/>
       <c r="DI63" t="inlineStr"/>
       <c r="DJ63" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="DK63" t="n">
-        <v>411</v>
+        <v>462</v>
       </c>
       <c r="DL63" t="n">
-        <v>4.724137931034483</v>
+        <v>4.8125</v>
       </c>
     </row>
     <row r="64">
@@ -15264,7 +15264,7 @@
         <v>27</v>
       </c>
       <c r="K64" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L64" t="n">
         <v>14</v>
@@ -15273,13 +15273,13 @@
         <v>25</v>
       </c>
       <c r="N64" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P64" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q64" t="n">
         <v>27</v>
@@ -15288,7 +15288,7 @@
         <v>16</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="T64" t="n">
         <v>8</v>
@@ -15325,31 +15325,31 @@
         <v>1</v>
       </c>
       <c r="AT64" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AU64" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AV64" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AW64" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AX64" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AY64" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AZ64" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BA64" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BB64" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="BC64" t="n">
         <v>5</v>
@@ -15383,31 +15383,31 @@
         <v>6</v>
       </c>
       <c r="CB64" t="n">
-        <v>0.3414634146341464</v>
+        <v>0.3255813953488372</v>
       </c>
       <c r="CC64" t="n">
-        <v>0.6097560975609756</v>
+        <v>0.5813953488372093</v>
       </c>
       <c r="CD64" t="n">
-        <v>0.3414634146341464</v>
+        <v>0.3488372093023256</v>
       </c>
       <c r="CE64" t="n">
-        <v>0.5365853658536586</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="CF64" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.4883720930232558</v>
       </c>
       <c r="CG64" t="n">
-        <v>0.6585365853658537</v>
+        <v>0.6279069767441861</v>
       </c>
       <c r="CH64" t="n">
-        <v>0.3902439024390244</v>
+        <v>0.3720930232558139</v>
       </c>
       <c r="CI64" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="CJ64" t="n">
-        <v>0.2758620689655172</v>
+        <v>0.2580645161290323</v>
       </c>
       <c r="CK64" t="n">
         <v>0</v>
@@ -15441,13 +15441,13 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="DJ64" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="DK64" t="n">
-        <v>796</v>
+        <v>847</v>
       </c>
       <c r="DL64" t="n">
-        <v>4.738095238095238</v>
+        <v>4.785310734463277</v>
       </c>
     </row>
     <row r="65">
@@ -15498,22 +15498,22 @@
         <v>12</v>
       </c>
       <c r="K65" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L65" t="n">
         <v>14</v>
       </c>
       <c r="M65" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N65" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O65" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P65" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q65" t="n">
         <v>4</v>
@@ -15522,13 +15522,13 @@
         <v>14</v>
       </c>
       <c r="S65" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T65" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V65" t="n">
         <v>0</v>
@@ -15556,37 +15556,37 @@
       <c r="AQ65" t="inlineStr"/>
       <c r="AR65" t="inlineStr"/>
       <c r="AS65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT65" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AU65" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AV65" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW65" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX65" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AY65" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AZ65" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA65" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB65" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BC65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD65" t="n">
         <v>1</v>
@@ -15614,37 +15614,37 @@
       <c r="BY65" t="inlineStr"/>
       <c r="BZ65" t="inlineStr"/>
       <c r="CA65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CB65" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="CC65" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="CD65" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="CE65" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="CF65" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="CG65" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="CH65" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="CI65" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="CJ65" t="n">
-        <v>1.727272727272727</v>
+        <v>1.538461538461539</v>
       </c>
       <c r="CK65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL65" t="n">
         <v>0</v>
@@ -15672,16 +15672,16 @@
       <c r="DG65" t="inlineStr"/>
       <c r="DH65" t="inlineStr"/>
       <c r="DI65" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="DJ65" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="DK65" t="n">
-        <v>525</v>
+        <v>616</v>
       </c>
       <c r="DL65" t="n">
-        <v>5.097087378640777</v>
+        <v>5.090909090909091</v>
       </c>
     </row>
     <row r="66">
@@ -15960,22 +15960,22 @@
         <v>22</v>
       </c>
       <c r="K67" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L67" t="n">
         <v>29</v>
       </c>
       <c r="M67" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="N67" t="n">
+        <v>19</v>
+      </c>
+      <c r="O67" t="n">
+        <v>37</v>
+      </c>
+      <c r="P67" t="n">
         <v>16</v>
-      </c>
-      <c r="O67" t="n">
-        <v>36</v>
-      </c>
-      <c r="P67" t="n">
-        <v>11</v>
       </c>
       <c r="Q67" t="n">
         <v>8</v>
@@ -15984,13 +15984,13 @@
         <v>20</v>
       </c>
       <c r="S67" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T67" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="U67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V67" t="n">
         <v>0</v>
@@ -16018,37 +16018,37 @@
       <c r="AQ67" t="inlineStr"/>
       <c r="AR67" t="inlineStr"/>
       <c r="AS67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AT67" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AU67" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AV67" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AW67" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AX67" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AY67" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AZ67" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BA67" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BB67" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="BC67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD67" t="n">
         <v>1</v>
@@ -16076,37 +16076,37 @@
       <c r="BY67" t="inlineStr"/>
       <c r="BZ67" t="inlineStr"/>
       <c r="CA67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CB67" t="n">
-        <v>0.7073170731707317</v>
+        <v>0.6744186046511628</v>
       </c>
       <c r="CC67" t="n">
-        <v>0.6341463414634146</v>
+        <v>0.6976744186046512</v>
       </c>
       <c r="CD67" t="n">
-        <v>0.3902439024390244</v>
+        <v>0.4418604651162791</v>
       </c>
       <c r="CE67" t="n">
-        <v>0.8780487804878049</v>
+        <v>0.8604651162790697</v>
       </c>
       <c r="CF67" t="n">
-        <v>0.2682926829268293</v>
+        <v>0.3720930232558139</v>
       </c>
       <c r="CG67" t="n">
-        <v>0.1951219512195122</v>
+        <v>0.186046511627907</v>
       </c>
       <c r="CH67" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.4651162790697674</v>
       </c>
       <c r="CI67" t="n">
-        <v>0.4390243902439024</v>
+        <v>0.4651162790697674</v>
       </c>
       <c r="CJ67" t="n">
-        <v>0.9032258064516129</v>
+        <v>0.8787878787878788</v>
       </c>
       <c r="CK67" t="n">
-        <v>0.6</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="CL67" t="n">
         <v>0</v>
@@ -16134,16 +16134,16 @@
       <c r="DG67" t="inlineStr"/>
       <c r="DH67" t="inlineStr"/>
       <c r="DI67" t="n">
-        <v>0.5</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="DJ67" t="n">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="DK67" t="n">
-        <v>942</v>
+        <v>1033</v>
       </c>
       <c r="DL67" t="n">
-        <v>4.781725888324873</v>
+        <v>4.804651162790698</v>
       </c>
     </row>
     <row r="68">
@@ -16191,10 +16191,10 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L68" t="n">
         <v>12</v>
@@ -16206,22 +16206,22 @@
         <v>5</v>
       </c>
       <c r="O68" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P68" t="n">
         <v>7</v>
       </c>
       <c r="Q68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R68" t="n">
         <v>6</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T68" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="U68" t="n">
         <v>7</v>
@@ -16253,31 +16253,31 @@
         <v>7</v>
       </c>
       <c r="AT68" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AU68" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AV68" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW68" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX68" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AY68" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AZ68" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA68" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC68" t="n">
         <v>3</v>
@@ -16309,31 +16309,31 @@
         <v>3</v>
       </c>
       <c r="CB68" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="CC68" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1304347826086956</v>
       </c>
       <c r="CD68" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="CE68" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="CF68" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="CG68" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="CH68" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="CI68" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="CJ68" t="n">
-        <v>1.1</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="CK68" t="n">
         <v>2.333333333333333</v>
@@ -16365,13 +16365,13 @@
         <v>2.333333333333333</v>
       </c>
       <c r="DJ68" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="DK68" t="n">
-        <v>391</v>
+        <v>440</v>
       </c>
       <c r="DL68" t="n">
-        <v>5.356164383561643</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="69">
@@ -16647,10 +16647,10 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K70" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L70" t="n">
         <v>18</v>
@@ -16662,22 +16662,22 @@
         <v>12</v>
       </c>
       <c r="O70" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P70" t="n">
         <v>11</v>
       </c>
       <c r="Q70" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R70" t="n">
         <v>16</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T70" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="U70" t="n">
         <v>8</v>
@@ -16709,31 +16709,31 @@
         <v>8</v>
       </c>
       <c r="AT70" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AU70" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AV70" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AW70" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX70" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AY70" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AZ70" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BA70" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB70" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC70" t="n">
         <v>4</v>
@@ -16765,31 +16765,31 @@
         <v>4</v>
       </c>
       <c r="CB70" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.45</v>
       </c>
       <c r="CC70" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.175</v>
       </c>
       <c r="CD70" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.3</v>
       </c>
       <c r="CE70" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.6</v>
       </c>
       <c r="CF70" t="n">
-        <v>0.2894736842105263</v>
+        <v>0.275</v>
       </c>
       <c r="CG70" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.475</v>
       </c>
       <c r="CH70" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.4</v>
       </c>
       <c r="CI70" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.275</v>
       </c>
       <c r="CJ70" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="CK70" t="n">
         <v>2</v>
@@ -16821,13 +16821,13 @@
         <v>2</v>
       </c>
       <c r="DJ70" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="DK70" t="n">
-        <v>753</v>
+        <v>802</v>
       </c>
       <c r="DL70" t="n">
-        <v>5.340425531914893</v>
+        <v>5.418918918918919</v>
       </c>
     </row>
     <row r="71">
@@ -16871,10 +16871,10 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L71" t="n">
         <v>9</v>
@@ -16889,7 +16889,7 @@
         <v>5</v>
       </c>
       <c r="P71" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="Q71" t="n">
         <v>6</v>
@@ -16898,10 +16898,10 @@
         <v>18</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T71" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U71" t="n">
         <v>1</v>
@@ -16939,31 +16939,31 @@
         <v>4</v>
       </c>
       <c r="AT71" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AU71" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AV71" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW71" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX71" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY71" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AZ71" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA71" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB71" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC71" t="n">
         <v>2</v>
@@ -17001,31 +17001,31 @@
         <v>5</v>
       </c>
       <c r="CB71" t="n">
-        <v>0.45</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="CC71" t="n">
-        <v>0.1</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="CD71" t="n">
-        <v>0.25</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="CE71" t="n">
-        <v>0.25</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="CF71" t="n">
-        <v>1.1</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="CG71" t="n">
-        <v>0.3</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="CH71" t="n">
-        <v>0.9</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="CI71" t="n">
-        <v>0.45</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="CJ71" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="CK71" t="n">
         <v>0.5</v>
@@ -17063,13 +17063,13 @@
         <v>0.8</v>
       </c>
       <c r="DJ71" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="DK71" t="n">
-        <v>511</v>
+        <v>576</v>
       </c>
       <c r="DL71" t="n">
-        <v>5.677777777777778</v>
+        <v>5.702970297029703</v>
       </c>
     </row>
     <row r="72">
@@ -17349,10 +17349,10 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K73" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L73" t="n">
         <v>17</v>
@@ -17367,7 +17367,7 @@
         <v>22</v>
       </c>
       <c r="P73" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Q73" t="n">
         <v>18</v>
@@ -17376,10 +17376,10 @@
         <v>23</v>
       </c>
       <c r="S73" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T73" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="U73" t="n">
         <v>5</v>
@@ -17417,31 +17417,31 @@
         <v>12</v>
       </c>
       <c r="AT73" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AU73" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AV73" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AW73" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AX73" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AY73" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AZ73" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BA73" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BB73" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BC73" t="n">
         <v>7</v>
@@ -17479,31 +17479,31 @@
         <v>14</v>
       </c>
       <c r="CB73" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.3953488372093023</v>
       </c>
       <c r="CC73" t="n">
-        <v>0.1951219512195122</v>
+        <v>0.186046511627907</v>
       </c>
       <c r="CD73" t="n">
-        <v>0.2926829268292683</v>
+        <v>0.2790697674418605</v>
       </c>
       <c r="CE73" t="n">
-        <v>0.5365853658536586</v>
+        <v>0.5116279069767442</v>
       </c>
       <c r="CF73" t="n">
-        <v>0.7804878048780488</v>
+        <v>0.8837209302325582</v>
       </c>
       <c r="CG73" t="n">
-        <v>0.4390243902439024</v>
+        <v>0.4186046511627907</v>
       </c>
       <c r="CH73" t="n">
-        <v>0.5609756097560976</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="CI73" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.4186046511627907</v>
       </c>
       <c r="CJ73" t="n">
-        <v>0.375</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="CK73" t="n">
         <v>0.7142857142857143</v>
@@ -17541,13 +17541,13 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="DJ73" t="n">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="DK73" t="n">
-        <v>962</v>
+        <v>1027</v>
       </c>
       <c r="DL73" t="n">
-        <v>5.497142857142857</v>
+        <v>5.521505376344086</v>
       </c>
     </row>
     <row r="74">
@@ -17829,16 +17829,16 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K75" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L75" t="n">
         <v>7</v>
       </c>
       <c r="M75" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N75" t="n">
         <v>7</v>
@@ -17847,16 +17847,16 @@
         <v>5</v>
       </c>
       <c r="P75" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q75" t="n">
         <v>9</v>
       </c>
       <c r="R75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="T75" t="n">
         <v>7</v>
@@ -17891,31 +17891,31 @@
         <v>3</v>
       </c>
       <c r="AT75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AU75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AV75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AY75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AZ75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BB75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BC75" t="n">
         <v>3</v>
@@ -17947,31 +17947,31 @@
         <v>3</v>
       </c>
       <c r="CB75" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CC75" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CD75" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CE75" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="CF75" t="n">
-        <v>0.631578947368421</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="CG75" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CH75" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CI75" t="n">
         <v>1</v>
       </c>
       <c r="CJ75" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CK75" t="n">
         <v>1</v>
@@ -18003,13 +18003,13 @@
         <v>1</v>
       </c>
       <c r="DJ75" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="DK75" t="n">
-        <v>434</v>
+        <v>483</v>
       </c>
       <c r="DL75" t="n">
-        <v>5.786666666666667</v>
+        <v>5.682352941176471</v>
       </c>
     </row>
     <row r="76">
@@ -18057,16 +18057,16 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K76" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L76" t="n">
         <v>19</v>
       </c>
       <c r="M76" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N76" t="n">
         <v>7</v>
@@ -18075,16 +18075,16 @@
         <v>22</v>
       </c>
       <c r="P76" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q76" t="n">
         <v>24</v>
       </c>
       <c r="R76" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S76" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T76" t="n">
         <v>25</v>
@@ -18121,31 +18121,31 @@
         <v>4</v>
       </c>
       <c r="AT76" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AU76" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AV76" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AW76" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AX76" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AY76" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AZ76" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="BA76" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="BB76" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC76" t="n">
         <v>6</v>
@@ -18179,31 +18179,31 @@
         <v>7</v>
       </c>
       <c r="CB76" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.4634146341463415</v>
       </c>
       <c r="CC76" t="n">
-        <v>0.358974358974359</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="CD76" t="n">
-        <v>0.1794871794871795</v>
+        <v>0.1707317073170732</v>
       </c>
       <c r="CE76" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.5365853658536586</v>
       </c>
       <c r="CF76" t="n">
-        <v>0.4358974358974359</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="CG76" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.5853658536585366</v>
       </c>
       <c r="CH76" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.1707317073170732</v>
       </c>
       <c r="CI76" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="CJ76" t="n">
-        <v>0.78125</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="CK76" t="n">
         <v>0.6666666666666666</v>
@@ -18237,13 +18237,13 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="DJ76" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="DK76" t="n">
-        <v>932</v>
+        <v>981</v>
       </c>
       <c r="DL76" t="n">
-        <v>5.418604651162791</v>
+        <v>5.390109890109891</v>
       </c>
     </row>
     <row r="77">
@@ -18511,25 +18511,25 @@
         </is>
       </c>
       <c r="J78" t="n">
+        <v>8</v>
+      </c>
+      <c r="K78" t="n">
+        <v>13</v>
+      </c>
+      <c r="L78" t="n">
+        <v>14</v>
+      </c>
+      <c r="M78" t="n">
         <v>7</v>
-      </c>
-      <c r="K78" t="n">
-        <v>11</v>
-      </c>
-      <c r="L78" t="n">
-        <v>13</v>
-      </c>
-      <c r="M78" t="n">
-        <v>6</v>
       </c>
       <c r="N78" t="n">
         <v>17</v>
       </c>
       <c r="O78" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P78" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q78" t="n">
         <v>21</v>
@@ -18541,7 +18541,7 @@
         <v>9</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U78" t="n">
         <v>1</v>
@@ -18573,31 +18573,31 @@
         <v>1</v>
       </c>
       <c r="AT78" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AU78" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AV78" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AW78" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX78" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AY78" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AZ78" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA78" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BB78" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BC78" t="n">
         <v>2</v>
@@ -18629,31 +18629,31 @@
         <v>2</v>
       </c>
       <c r="CB78" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CC78" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="CD78" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="CE78" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CF78" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="CG78" t="n">
-        <v>1.166666666666667</v>
+        <v>1</v>
       </c>
       <c r="CH78" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="CI78" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CJ78" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="CK78" t="n">
         <v>0.5</v>
@@ -18685,13 +18685,13 @@
         <v>0.5</v>
       </c>
       <c r="DJ78" t="n">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="DK78" t="n">
-        <v>437</v>
+        <v>506</v>
       </c>
       <c r="DL78" t="n">
-        <v>4.6</v>
+        <v>4.685185185185185</v>
       </c>
     </row>
     <row r="79">
@@ -18735,25 +18735,25 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K79" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L79" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M79" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N79" t="n">
         <v>28</v>
       </c>
       <c r="O79" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P79" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q79" t="n">
         <v>29</v>
@@ -18765,7 +18765,7 @@
         <v>10</v>
       </c>
       <c r="T79" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="U79" t="n">
         <v>3</v>
@@ -18797,31 +18797,31 @@
         <v>3</v>
       </c>
       <c r="AT79" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AU79" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AV79" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AW79" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AX79" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AY79" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AZ79" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="BA79" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="BB79" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="BC79" t="n">
         <v>4</v>
@@ -18853,31 +18853,31 @@
         <v>4</v>
       </c>
       <c r="CB79" t="n">
-        <v>0.8205128205128205</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="CC79" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="CD79" t="n">
-        <v>0.717948717948718</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CE79" t="n">
-        <v>0.2564102564102564</v>
+        <v>0.2619047619047619</v>
       </c>
       <c r="CF79" t="n">
-        <v>0.717948717948718</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="CG79" t="n">
-        <v>0.7435897435897436</v>
+        <v>0.6904761904761905</v>
       </c>
       <c r="CH79" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.5476190476190477</v>
       </c>
       <c r="CI79" t="n">
-        <v>0.2564102564102564</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="CJ79" t="n">
-        <v>0.5357142857142857</v>
+        <v>0.5806451612903226</v>
       </c>
       <c r="CK79" t="n">
         <v>0.75</v>
@@ -18909,13 +18909,13 @@
         <v>0.75</v>
       </c>
       <c r="DJ79" t="n">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="DK79" t="n">
-        <v>902</v>
+        <v>971</v>
       </c>
       <c r="DL79" t="n">
-        <v>4.722513089005235</v>
+        <v>4.759803921568627</v>
       </c>
     </row>
     <row r="80">
@@ -19177,31 +19177,31 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K81" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L81" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M81" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N81" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O81" t="n">
         <v>5</v>
       </c>
       <c r="P81" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S81" t="n">
         <v>18</v>
@@ -19243,31 +19243,31 @@
         <v>6</v>
       </c>
       <c r="AT81" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AU81" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AV81" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AW81" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AX81" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AY81" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AZ81" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA81" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BB81" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC81" t="n">
         <v>3</v>
@@ -19306,28 +19306,28 @@
         <v>0.5</v>
       </c>
       <c r="CC81" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5</v>
       </c>
       <c r="CD81" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.875</v>
       </c>
       <c r="CE81" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="CF81" t="n">
         <v>0.5</v>
       </c>
       <c r="CG81" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="CH81" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="CI81" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.75</v>
       </c>
       <c r="CJ81" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CK81" t="n">
         <v>0.3333333333333333</v>
@@ -19363,13 +19363,13 @@
         <v>1</v>
       </c>
       <c r="DJ81" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="DK81" t="n">
-        <v>533</v>
+        <v>559</v>
       </c>
       <c r="DL81" t="n">
-        <v>5.225490196078431</v>
+        <v>5.128440366972477</v>
       </c>
     </row>
     <row r="82">
@@ -19415,31 +19415,31 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K82" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L82" t="n">
+        <v>29</v>
+      </c>
+      <c r="M82" t="n">
         <v>28</v>
       </c>
-      <c r="M82" t="n">
-        <v>26</v>
-      </c>
       <c r="N82" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O82" t="n">
         <v>17</v>
       </c>
       <c r="P82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q82" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S82" t="n">
         <v>27</v>
@@ -19481,31 +19481,31 @@
         <v>6</v>
       </c>
       <c r="AT82" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AU82" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AV82" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AW82" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AX82" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AY82" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AZ82" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BA82" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BB82" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="BC82" t="n">
         <v>3</v>
@@ -19541,31 +19541,31 @@
         <v>6</v>
       </c>
       <c r="CB82" t="n">
-        <v>0.6829268292682927</v>
+        <v>0.6744186046511628</v>
       </c>
       <c r="CC82" t="n">
-        <v>0.6341463414634146</v>
+        <v>0.6511627906976745</v>
       </c>
       <c r="CD82" t="n">
-        <v>0.6585365853658537</v>
+        <v>0.6511627906976745</v>
       </c>
       <c r="CE82" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.3953488372093023</v>
       </c>
       <c r="CF82" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5116279069767442</v>
       </c>
       <c r="CG82" t="n">
-        <v>0.5609756097560976</v>
+        <v>0.5581395348837209</v>
       </c>
       <c r="CH82" t="n">
-        <v>0.1951219512195122</v>
+        <v>0.2093023255813954</v>
       </c>
       <c r="CI82" t="n">
-        <v>0.6585365853658537</v>
+        <v>0.6279069767441861</v>
       </c>
       <c r="CJ82" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="CK82" t="n">
         <v>0.3333333333333333</v>
@@ -19601,13 +19601,13 @@
         <v>1</v>
       </c>
       <c r="DJ82" t="n">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DK82" t="n">
-        <v>1029</v>
+        <v>1055</v>
       </c>
       <c r="DL82" t="n">
-        <v>4.9</v>
+        <v>4.861751152073733</v>
       </c>
     </row>
     <row r="83">
@@ -19651,37 +19651,37 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K83" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L83" t="n">
         <v>4</v>
       </c>
       <c r="M83" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O83" t="n">
         <v>6</v>
       </c>
       <c r="P83" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R83" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="S83" t="n">
         <v>8</v>
       </c>
       <c r="T83" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U83" t="inlineStr"/>
       <c r="V83" t="inlineStr"/>
@@ -19709,31 +19709,31 @@
       <c r="AR83" t="inlineStr"/>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AU83" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AV83" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AW83" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AX83" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AY83" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AZ83" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA83" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BB83" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BC83" t="inlineStr"/>
       <c r="BD83" t="inlineStr"/>
@@ -19763,31 +19763,31 @@
         <v>0</v>
       </c>
       <c r="CB83" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="CC83" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="CD83" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5</v>
       </c>
       <c r="CE83" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
       <c r="CF83" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="CG83" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="CH83" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.5</v>
       </c>
       <c r="CI83" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CJ83" t="n">
-        <v>0.7</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="CK83" t="inlineStr"/>
       <c r="CL83" t="inlineStr"/>
@@ -19815,13 +19815,13 @@
       <c r="DH83" t="inlineStr"/>
       <c r="DI83" t="inlineStr"/>
       <c r="DJ83" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="DK83" t="n">
-        <v>319</v>
+        <v>415</v>
       </c>
       <c r="DL83" t="n">
-        <v>4.623188405797102</v>
+        <v>4.940476190476191</v>
       </c>
     </row>
     <row r="84">
@@ -20079,37 +20079,37 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K85" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L85" t="n">
         <v>19</v>
       </c>
       <c r="M85" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N85" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O85" t="n">
         <v>13</v>
       </c>
       <c r="P85" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q85" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R85" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="S85" t="n">
         <v>18</v>
       </c>
       <c r="T85" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="U85" t="inlineStr"/>
       <c r="V85" t="inlineStr"/>
@@ -20137,31 +20137,31 @@
       <c r="AR85" t="inlineStr"/>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AU85" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AV85" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AW85" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AX85" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AY85" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AZ85" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="BA85" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="BB85" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="BC85" t="inlineStr"/>
       <c r="BD85" t="inlineStr"/>
@@ -20191,31 +20191,31 @@
         <v>0</v>
       </c>
       <c r="CB85" t="n">
-        <v>0.475</v>
+        <v>0.4418604651162791</v>
       </c>
       <c r="CC85" t="n">
-        <v>0.375</v>
+        <v>0.3720930232558139</v>
       </c>
       <c r="CD85" t="n">
-        <v>0.525</v>
+        <v>0.5116279069767442</v>
       </c>
       <c r="CE85" t="n">
-        <v>0.325</v>
+        <v>0.3023255813953488</v>
       </c>
       <c r="CF85" t="n">
-        <v>0.3</v>
+        <v>0.3255813953488372</v>
       </c>
       <c r="CG85" t="n">
-        <v>0.15</v>
+        <v>0.186046511627907</v>
       </c>
       <c r="CH85" t="n">
-        <v>0.45</v>
+        <v>0.5581395348837209</v>
       </c>
       <c r="CI85" t="n">
-        <v>0.45</v>
+        <v>0.4186046511627907</v>
       </c>
       <c r="CJ85" t="n">
-        <v>0.3448275862068966</v>
+        <v>0.4193548387096774</v>
       </c>
       <c r="CK85" t="inlineStr"/>
       <c r="CL85" t="inlineStr"/>
@@ -20243,13 +20243,13 @@
       <c r="DH85" t="inlineStr"/>
       <c r="DI85" t="inlineStr"/>
       <c r="DJ85" t="n">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="DK85" t="n">
-        <v>620</v>
+        <v>716</v>
       </c>
       <c r="DL85" t="n">
-        <v>4.626865671641791</v>
+        <v>4.805369127516778</v>
       </c>
     </row>
     <row r="86">
@@ -20529,10 +20529,10 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K87" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L87" t="n">
         <v>5</v>
@@ -20541,13 +20541,13 @@
         <v>18</v>
       </c>
       <c r="N87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O87" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P87" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q87" t="n">
         <v>7</v>
@@ -20587,31 +20587,31 @@
       <c r="AR87" t="inlineStr"/>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AU87" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV87" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW87" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX87" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY87" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ87" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA87" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB87" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BC87" t="inlineStr"/>
       <c r="BD87" t="inlineStr"/>
@@ -20641,28 +20641,28 @@
         <v>0</v>
       </c>
       <c r="CB87" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="CC87" t="n">
-        <v>1.058823529411765</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="CD87" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="CE87" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="CF87" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="CG87" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="CH87" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="CI87" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="CJ87" t="n">
         <v>0</v>
@@ -20693,13 +20693,13 @@
       <c r="DH87" t="inlineStr"/>
       <c r="DI87" t="inlineStr"/>
       <c r="DJ87" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="DK87" t="n">
-        <v>346</v>
+        <v>374</v>
       </c>
       <c r="DL87" t="n">
-        <v>4.739726027397261</v>
+        <v>4.675</v>
       </c>
     </row>
     <row r="88">
@@ -20743,10 +20743,10 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K88" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L88" t="n">
         <v>14</v>
@@ -20755,13 +20755,13 @@
         <v>31</v>
       </c>
       <c r="N88" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O88" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="P88" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q88" t="n">
         <v>19</v>
@@ -20809,31 +20809,31 @@
         <v>2</v>
       </c>
       <c r="AT88" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AU88" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AV88" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AW88" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX88" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AY88" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AZ88" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BA88" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB88" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="BC88" t="n">
         <v>2</v>
@@ -20869,31 +20869,31 @@
         <v>4</v>
       </c>
       <c r="CB88" t="n">
-        <v>0.35</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CC88" t="n">
-        <v>0.775</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="CD88" t="n">
-        <v>0.425</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CE88" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="CF88" t="n">
-        <v>0.475</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="CG88" t="n">
-        <v>0.475</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="CH88" t="n">
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="CI88" t="n">
-        <v>0.55</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CJ88" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.0303030303030303</v>
       </c>
       <c r="CK88" t="n">
         <v>0.5</v>
@@ -20929,13 +20929,13 @@
         <v>0.5</v>
       </c>
       <c r="DJ88" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="DK88" t="n">
-        <v>774</v>
+        <v>802</v>
       </c>
       <c r="DL88" t="n">
-        <v>4.634730538922156</v>
+        <v>4.609195402298851</v>
       </c>
     </row>
     <row r="89">
@@ -21215,28 +21215,28 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K90" t="n">
+        <v>13</v>
+      </c>
+      <c r="L90" t="n">
         <v>12</v>
-      </c>
-      <c r="L90" t="n">
-        <v>11</v>
       </c>
       <c r="M90" t="n">
         <v>9</v>
       </c>
       <c r="N90" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O90" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="P90" t="n">
         <v>11</v>
       </c>
       <c r="Q90" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R90" t="n">
         <v>3</v>
@@ -21281,31 +21281,31 @@
         <v>2</v>
       </c>
       <c r="AT90" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AU90" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AV90" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AW90" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX90" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AY90" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AZ90" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA90" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BB90" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BC90" t="n">
         <v>3</v>
@@ -21341,31 +21341,31 @@
         <v>5</v>
       </c>
       <c r="CB90" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="CC90" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CD90" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CE90" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CF90" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CG90" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CH90" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="CI90" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CJ90" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CK90" t="n">
         <v>0.6666666666666666</v>
@@ -21401,13 +21401,13 @@
         <v>0.4</v>
       </c>
       <c r="DJ90" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="DK90" t="n">
-        <v>375</v>
+        <v>407</v>
       </c>
       <c r="DL90" t="n">
-        <v>4.87012987012987</v>
+        <v>4.732558139534884</v>
       </c>
     </row>
     <row r="91">
@@ -21451,28 +21451,28 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K91" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L91" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M91" t="n">
         <v>27</v>
       </c>
       <c r="N91" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O91" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="P91" t="n">
         <v>25</v>
       </c>
       <c r="Q91" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R91" t="n">
         <v>19</v>
@@ -21517,31 +21517,31 @@
         <v>4</v>
       </c>
       <c r="AT91" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AU91" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AV91" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AW91" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AX91" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AY91" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AZ91" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="BA91" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="BB91" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="BC91" t="n">
         <v>4</v>
@@ -21577,31 +21577,31 @@
         <v>8</v>
       </c>
       <c r="CB91" t="n">
-        <v>0.475</v>
+        <v>0.4651162790697674</v>
       </c>
       <c r="CC91" t="n">
-        <v>0.675</v>
+        <v>0.6279069767441861</v>
       </c>
       <c r="CD91" t="n">
-        <v>0.25</v>
+        <v>0.3023255813953488</v>
       </c>
       <c r="CE91" t="n">
-        <v>0.625</v>
+        <v>0.6744186046511628</v>
       </c>
       <c r="CF91" t="n">
-        <v>0.625</v>
+        <v>0.5813953488372093</v>
       </c>
       <c r="CG91" t="n">
-        <v>0.4</v>
+        <v>0.3953488372093023</v>
       </c>
       <c r="CH91" t="n">
-        <v>0.475</v>
+        <v>0.4418604651162791</v>
       </c>
       <c r="CI91" t="n">
-        <v>0.425</v>
+        <v>0.3953488372093023</v>
       </c>
       <c r="CJ91" t="n">
-        <v>0.4193548387096774</v>
+        <v>0.3823529411764706</v>
       </c>
       <c r="CK91" t="n">
         <v>1</v>
@@ -21637,13 +21637,13 @@
         <v>0.5</v>
       </c>
       <c r="DJ91" t="n">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="DK91" t="n">
-        <v>850</v>
+        <v>882</v>
       </c>
       <c r="DL91" t="n">
-        <v>4.775280898876405</v>
+        <v>4.716577540106952</v>
       </c>
     </row>
   </sheetData>
